--- a/workspaces/nasdaq_hourly_24hrs/ma/ma_cross_10_50.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/ma/ma_cross_10_50.xlsx
@@ -618,83 +618,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.0304</t>
+          <t>X ≈ -0.03039</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1695339367039281</v>
+        <v>0.2025730435486466</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.657685958724855</v>
+        <v>3.691158387635518</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.048750023799052</v>
+        <v>6.083923345154474</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.340270275208397</v>
+        <v>5.376283239906499</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.803615853889781</v>
+        <v>8.868963897790977</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.992163519031209</v>
+        <v>9.057333405432914</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.22580911725526</v>
+        <v>8.29190436324135</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.2960665803191702</v>
+        <v>0.3624742972535344</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.319490089821343</v>
+        <v>-7.253133364021856</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.092381317937722</v>
+        <v>-8.025089050958442</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.820963201342728</v>
+        <v>-7.753945338786544</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-11.93381131950905</v>
+        <v>-11.86644391898818</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-9.224687160217584</v>
+        <v>-9.155959020369352</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.779085944309067</v>
+        <v>-1.710028535356322</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1.399337156708931</v>
+        <v>1.469212137588286</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.830308725933882</v>
+        <v>5.899546548278209</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>1.860517557787411</v>
+        <v>1.929940391503301</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-2.082934142839854</v>
+        <v>-2.013356229358131</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-5.707887207660221</v>
+        <v>-5.638525189119427</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-5.522862607367294</v>
+        <v>-5.453673942773818</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-6.067015628130363</v>
+        <v>-5.997150650344466</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-6.144709507171378</v>
+        <v>-6.074711430435038</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-2.026658533516581</v>
+        <v>-1.956935532216548</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-2.103013945119216</v>
+        <v>-2.033159597411938</v>
       </c>
     </row>
     <row r="7">
@@ -707,76 +707,76 @@
         <v>38</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.189521802932397</v>
+        <v>4.222591322715388</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-11.824699209936</v>
+        <v>-11.79135893250025</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-8.030810355934058</v>
+        <v>-7.995751468087263</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.743505965909279</v>
+        <v>-8.707602294850957</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-6.492319483694288</v>
+        <v>-6.427086559132668</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.691405594870425</v>
+        <v>-3.626326898640613</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.843688316012482</v>
+        <v>-1.777662651546315</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.4974235236221816</v>
+        <v>0.5638261244434233</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.079978014661343</v>
+        <v>-2.013599126146936</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-10.71200010408172</v>
+        <v>-10.64472908554292</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-23.54674093737813</v>
+        <v>-23.47980739153338</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-21.21035979780957</v>
+        <v>-21.14304161346315</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-22.33747296717753</v>
+        <v>-22.26880562730092</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-22.56503881183433</v>
+        <v>-22.49606474755571</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-23.22868511628288</v>
+        <v>-23.15889794648356</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-22.64217792613524</v>
+        <v>-22.57302931248959</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-20.15677093057666</v>
+        <v>-20.08740943159547</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-20.26781372668987</v>
+        <v>-20.1982800011444</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-20.05804657089261</v>
+        <v>-19.98871436002793</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-22.50581987327558</v>
+        <v>-22.43665903839881</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-25.68437392270833</v>
+        <v>-25.6145328704139</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-17.87828995892936</v>
+        <v>-17.80830183283672</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-17.60888407250825</v>
+        <v>-17.53916745241995</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-15.05847953216374</v>
+        <v>-14.98862518445647</v>
       </c>
     </row>
     <row r="8">
@@ -789,76 +789,76 @@
         <v>42</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.013542152589459</v>
+        <v>-5.980567819803859</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.7474132387193109</v>
+        <v>0.7808501646591353</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.049752576345213</v>
+        <v>-3.014661953139999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.9714275979025615</v>
+        <v>1.007397958311898</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.6092270230330286</v>
+        <v>0.6745003308604751</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.530304769354771</v>
+        <v>5.595437587309235</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>14.23639268303834</v>
+        <v>14.30251530810022</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>11.59464253306234</v>
+        <v>11.66110607286231</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.270467414256643</v>
+        <v>9.336904155678369</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.87377790179996</v>
+        <v>10.94115631478438</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>13.52289488298919</v>
+        <v>13.59000335184275</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.504590421103728</v>
+        <v>8.572036280891808</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.759462898884046</v>
+        <v>9.828257165423373</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.421166130454289</v>
+        <v>2.49022785800063</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>4.139464230752175</v>
+        <v>4.20933848210209</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>4.734297137150541</v>
+        <v>4.803523343394787</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.1493836338617029</v>
+        <v>-0.07997403103988887</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-2.630823596696629</v>
+        <v>-2.561254181282422</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-9.547410524645549</v>
+        <v>-9.478062447730416</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-6.985713586280305</v>
+        <v>-6.916532395808808</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-7.530400127719361</v>
+        <v>-7.460540922006565</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.608759907681204</v>
+        <v>-7.538765528225518</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-2.575861366021442</v>
+        <v>-2.50613975099477</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>2.109440267335003</v>
+        <v>2.179294615041741</v>
       </c>
     </row>
     <row r="9">
@@ -871,76 +871,76 @@
         <v>57</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.930355325121617</v>
+        <v>5.963429125809604</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7.342644840807729</v>
+        <v>7.376132972510646</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.913435660907837</v>
+        <v>5.948593063378212</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.204842429993271</v>
+        <v>5.240840235043265</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.100244051013078</v>
+        <v>3.165524131543648</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.51962917000516</v>
+        <v>8.584774303221934</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.752732201619445</v>
+        <v>7.818805097431714</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.241891100126125</v>
+        <v>2.308288222606024</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.030907903061724</v>
+        <v>4.097306313793538</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.262053876499188</v>
+        <v>3.32938350342944</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.031731716369436</v>
+        <v>7.098801511416504</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.755856351995334</v>
+        <v>6.823287986706276</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.637483355309108</v>
+        <v>5.70625422542664</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.670057482297551</v>
+        <v>3.739117798470517</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.4842560482754266</v>
+        <v>-0.4144041466016049</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-3.390754167002648</v>
+        <v>-3.321558972494849</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-8.77676745710837</v>
+        <v>-8.707387290760607</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-12.38647686676138</v>
+        <v>-12.31693578843252</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-13.92594188576938</v>
+        <v>-13.8566074102603</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-15.49591306507592</v>
+        <v>-15.42674916587356</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-17.79606548510629</v>
+        <v>-17.72622145563182</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-16.12449904076602</v>
+        <v>-16.05451335132416</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-15.85481955316535</v>
+        <v>-15.78510408769255</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-14.18128654970761</v>
+        <v>-14.11143220199993</v>
       </c>
     </row>
     <row r="10">
@@ -953,76 +953,76 @@
         <v>58</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.360312595469082</v>
+        <v>-5.327352473714384</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5581148352312368</v>
+        <v>-0.5247036513332475</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.701950945663057</v>
+        <v>-3.66688320987393</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.7256137644922163</v>
+        <v>0.76156860642147</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-6.490530083993946</v>
+        <v>-6.425339724515176</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-14.87861810134665</v>
+        <v>-14.81365878686626</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-8.794124098337882</v>
+        <v>-8.728178483285355</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.357951289509572</v>
+        <v>-7.291630249089586</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-10.74975314793762</v>
+        <v>-10.68345790054283</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.657830491060615</v>
+        <v>-4.590557473478917</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.668349421693051</v>
+        <v>-2.601340504893635</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.664691189618679</v>
+        <v>-4.597324549660641</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.504535267935495</v>
+        <v>-7.435832483547856</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-7.72719012895702</v>
+        <v>-7.658185070494447</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-3.228783841069848</v>
+        <v>-3.158950290025004</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.636213952520635</v>
+        <v>-2.567023958767443</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-7.931026120639729</v>
+        <v>-7.861651434906335</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-4.596780763899687</v>
+        <v>-4.527227553119971</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.9395320829068226</v>
+        <v>-0.8701768368878504</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-2.475184236269691</v>
+        <v>-2.406003809640602</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-3.018531736565805</v>
+        <v>-2.948673342830652</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-4.818697629132821</v>
+        <v>-4.748705155358714</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-7.992698455692683</v>
+        <v>-7.92298103224195</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-6.347045775357941</v>
+        <v>-6.277191427650664</v>
       </c>
     </row>
     <row r="11">
@@ -1035,76 +1035,76 @@
         <v>62</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.046997477947741</v>
+        <v>-2.01401858241875</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.8223778896632084</v>
+        <v>0.8557918133494553</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.9937818517553154</v>
+        <v>1.028879986939501</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.090156631339802</v>
+        <v>5.126140463708843</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.73068671146266</v>
+        <v>4.795948875966104</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.711005848331659</v>
+        <v>1.776070518734642</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.9414664059531646</v>
+        <v>1.007464201831681</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.6654224102965856</v>
+        <v>0.7317812350365358</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.127815740507231</v>
+        <v>7.194209049585112</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>9.570605769527425</v>
+        <v>9.637950717040454</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>8.241683346363416</v>
+        <v>8.308741072965667</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>7.966526734269053</v>
+        <v>8.0339466131107</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>6.84907855769854</v>
+        <v>6.917837170917288</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>8.238689567886091</v>
+        <v>8.307752276532426</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.976613627527648</v>
+        <v>6.046473699388521</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>9.789408767733782</v>
+        <v>9.858633824440645</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>16.09631106407677</v>
+        <v>16.16575059177099</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>15.99669937621246</v>
+        <v>16.06629983393726</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>19.43837047680316</v>
+        <v>19.50776522397567</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>18.0206018387161</v>
+        <v>18.08981391452254</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>15.87272585452495</v>
+        <v>15.94260578174798</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>10.96629782919818</v>
+        <v>11.03630185013413</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>9.632267324139455</v>
+        <v>9.701991226733995</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>7.946613846444059</v>
+        <v>8.016468194151336</v>
       </c>
     </row>
     <row r="12">
@@ -1117,76 +1117,76 @@
         <v>67</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.05568664878976648</v>
+        <v>0.08867390590761914</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.611895758743103</v>
+        <v>8.645376797741442</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.666324917028319</v>
+        <v>8.701485756315698</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.475386650752178</v>
+        <v>6.511376187887222</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.599630088611008</v>
+        <v>7.66490110810291</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>10.75499019954962</v>
+        <v>10.82011195673982</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11.47263453289083</v>
+        <v>11.53869731522418</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>11.20024666453597</v>
+        <v>11.26666635205231</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>11.24584653912827</v>
+        <v>11.31225661860958</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>10.47904008303281</v>
+        <v>10.54638136758723</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>9.270680758867414</v>
+        <v>9.337735094471064</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>10.48253918709989</v>
+        <v>10.54996388068055</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>12.34024281147284</v>
+        <v>12.40902003063251</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>10.63666299637827</v>
+        <v>10.70572894005186</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>11.47182633200277</v>
+        <v>11.54170111012954</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>9.092025113675625</v>
+        <v>9.161241872379875</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>11.93988872911051</v>
+        <v>12.00931148518615</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>11.83910655480052</v>
+        <v>11.90869260852982</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>9.078978207835085</v>
+        <v>9.148347417415842</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>9.268780603133564</v>
+        <v>9.337975003142901</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>5.747524171840247</v>
+        <v>5.817388644295256</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>4.181936865452435</v>
+        <v>4.251933287673602</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>5.950177902679719</v>
+        <v>6.019899376163437</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.09382910011347434</v>
+        <v>-0.02397475240619684</v>
       </c>
     </row>
     <row r="13">
@@ -1199,76 +1199,76 @@
         <v>101</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-5.119162926031571</v>
+        <v>-5.086250274960221</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.472639263471059</v>
+        <v>-4.439304359803735</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.97285122599326</v>
+        <v>-1.937805384751513</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2651625575285834</v>
+        <v>0.3010835618688645</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.079140526889027</v>
+        <v>-1.013969227389836</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.08974400082362877</v>
+        <v>0.154757046998121</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.6801411794565979</v>
+        <v>-0.614192739526608</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.981896596470463</v>
+        <v>3.048238873888586</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.024869240486574</v>
+        <v>3.091206671181638</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.226131395542524</v>
+        <v>4.293417582532015</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10.41556868986771</v>
+        <v>10.48261791517744</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>10.14145023021301</v>
+        <v>10.20886217658308</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>10.99784998591027</v>
+        <v>11.0666108384411</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>9.795089336720359</v>
+        <v>9.864141800329278</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>13.09014541378793</v>
+        <v>13.16001905407679</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>12.70090525244132</v>
+        <v>12.77012792473553</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>13.55975687461019</v>
+        <v>13.629178941891</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>13.45978844304523</v>
+        <v>13.52937387879776</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>8.738765423406385</v>
+        <v>8.808128564449952</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>9.917323283760126</v>
+        <v>9.986514853585433</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>10.36770358812598</v>
+        <v>10.43757110813502</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>11.28480269522748</v>
+        <v>11.35480343946509</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>6.614813996862544</v>
+        <v>6.684534569646871</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>7.531411035840428</v>
+        <v>7.601265383547705</v>
       </c>
     </row>
     <row r="14">
@@ -1281,76 +1281,76 @@
         <v>97</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-9.266610254065746</v>
+        <v>-9.785971398503371</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-14.71823722683637</v>
+        <v>-14.68504735156834</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-18.20032554048903</v>
+        <v>-18.16548077117246</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-17.89487053617835</v>
+        <v>-17.8591579231592</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-19.28547947340788</v>
+        <v>-19.22052507700547</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-16.03472318780576</v>
+        <v>-15.96989427972415</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-10.66257991402195</v>
+        <v>-10.5967516628642</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.768261858509653</v>
+        <v>-3.702001867165627</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.6515863982895027</v>
+        <v>-0.5853020540744964</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.422202860091126</v>
+        <v>-1.354979707086912</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.227583376097577</v>
+        <v>-4.160648373344294</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-6.559551631677017</v>
+        <v>-6.492258429680234</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.62780732439375</v>
+        <v>-5.559154730659905</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.795041344249405</v>
+        <v>-3.726072469200155</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-5.480432565521511</v>
+        <v>-5.410655884210342</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-4.88874606871223</v>
+        <v>-4.819605545108303</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-5.023648557668437</v>
+        <v>-4.954301748209048</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-5.129988028166984</v>
+        <v>-5.060467181582503</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.828081440099091</v>
+        <v>-1.758752783419148</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-8.847947913653854</v>
+        <v>-8.778800774811501</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-7.333530732948368</v>
+        <v>-7.263694923750151</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-9.472380576688522</v>
+        <v>-9.402404037606637</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-6.109129068456859</v>
+        <v>-6.039416706215718</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-6.187074214746488</v>
+        <v>-6.117219867039211</v>
       </c>
     </row>
     <row r="15">
@@ -1363,896 +1363,896 @@
         <v>115</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.484163081869042</v>
+        <v>-1.918416706241899</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.680165151570527</v>
+        <v>-3.116094691103989</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.522486181930795</v>
+        <v>-1.487499138127404</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.686977192112835</v>
+        <v>-5.651178902165398</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.048988092996936</v>
+        <v>-5.983963397546574</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.140066375830813</v>
+        <v>-4.075179092340477</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-9.232680848422241</v>
+        <v>-9.166890847675774</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-9.514328300171243</v>
+        <v>-9.448160463465733</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7.747229669906837</v>
+        <v>-7.681039402514976</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-7.655284357849254</v>
+        <v>-7.588143256311959</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-8.249647735797346</v>
+        <v>-8.182775531524705</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.932997037429757</v>
+        <v>-5.865732533420797</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.188809015006612</v>
+        <v>-6.120189847873377</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-7.277232285809241</v>
+        <v>-7.208309207543849</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-4.469711776600398</v>
+        <v>-4.39995478071323</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-5.611789939999056</v>
+        <v>-5.542674247049632</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-5.747030361849532</v>
+        <v>-5.677705505118148</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.383378210914344</v>
+        <v>-2.313864337470037</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-3.035852732362031</v>
+        <v>-2.966539914015449</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-4.586329567948823</v>
+        <v>-4.517184908517279</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-5.998733423068401</v>
+        <v>-5.928904287790928</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-8.683587448629545</v>
+        <v>-8.613616314805725</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-6.673523532710284</v>
+        <v>-6.603814374049151</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-5.882278159166034</v>
+        <v>-5.812423811458757</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.007611</t>
+          <t>X ≈ -0.007612</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.135600962151344</v>
+        <v>2.472798909307805</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.091141269554853</v>
+        <v>1.41934059482692</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.80290068624641</v>
+        <v>2.138924565911147</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6661350693240919</v>
+        <v>0.3916531711662898</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.876974861507925</v>
+        <v>3.657487879438293</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9386036631652956</v>
+        <v>-1.194660318150099</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.566911562435436</v>
+        <v>-4.842906152094152</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.561868660205363</v>
+        <v>-5.842808504427524</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.662787364780584</v>
+        <v>-2.923090073491991</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.433927312369534</v>
+        <v>-3.693416980632698</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4170636680004378</v>
+        <v>0.1831521140987817</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.440330026455896</v>
+        <v>-3.699963761521822</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.412174350008655</v>
+        <v>-2.654999652333331</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.2334988467139638</v>
+        <v>0.01165145646462662</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.573506917815543</v>
+        <v>-2.810254133065875</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-4.132434136632412</v>
+        <v>-4.385536619680153</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-5.702033834443888</v>
+        <v>-5.965457966479271</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.220761973656302</v>
+        <v>-2.458114741976821</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.5692651745151522</v>
+        <v>-0.7965239696138795</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.3360349442277268</v>
+        <v>0.1137026458299459</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.642968067428036</v>
+        <v>-1.875148482385178</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.000641699751213</v>
+        <v>-1.2275861973826</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.7263324040238146</v>
+        <v>-0.9536586286611097</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.8025158820312157</v>
+        <v>-1.029815115806578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.005333</t>
+          <t>X ≈ -0.005334</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.335416875874905</v>
+        <v>-2.736199159159028</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.33545970174842</v>
+        <v>2.30778373685051</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.70938251379161</v>
+        <v>2.664906456700599</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.400344603497089</v>
+        <v>1.355464552353524</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.965171967580673</v>
+        <v>-1.628496805199887</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.029932844260031</v>
+        <v>3.337644174187282</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.346997627518576</v>
+        <v>-1.016552121565468</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.227602442876886</v>
+        <v>-1.893052184894138</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.9846560068243662</v>
+        <v>-0.657222905332965</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.6550669626911869</v>
+        <v>0.9690547201429496</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.736051508271281</v>
+        <v>3.03900709706982</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.666747200780783</v>
+        <v>3.962913203083829</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>4.961924739051177</v>
+        <v>5.245011027453977</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.347404625904169</v>
+        <v>5.627253780706482</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3.486422667401264</v>
+        <v>3.774433267419212</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>8.913481000061189</v>
+        <v>9.171867862529936</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>8.180183336113728</v>
+        <v>8.442486621589566</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>4.451017745620334</v>
+        <v>4.735409721867825</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.064371289012108</v>
+        <v>4.352294109272528</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>4.858329766264049</v>
+        <v>5.142534849364623</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>8.555642481412413</v>
+        <v>8.815103295104471</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>8.483373292074099</v>
+        <v>8.743051715761247</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>6.338475094113868</v>
+        <v>6.612558135119428</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>8.689526847421583</v>
+        <v>8.949231505461093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.003054</t>
+          <t>X ≈ -0.003056</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>158</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.718497643268371</v>
+        <v>-2.691214655216832</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-10.23313497238082</v>
+        <v>-9.931054744705797</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-12.2932831091394</v>
+        <v>-11.99462703327023</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-13.00701123541639</v>
+        <v>-12.70645079282168</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-8.978505093858175</v>
+        <v>-9.274309182427338</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-10.68447145366509</v>
+        <v>-10.61993413136516</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-12.71071570986294</v>
+        <v>-12.64525357204873</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-15.50745197363313</v>
+        <v>-15.44162910970143</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-15.47596608988487</v>
+        <v>-15.41010517639474</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-9.964496829173541</v>
+        <v>-9.897598902088745</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-10.32661284898784</v>
+        <v>-10.2599589299174</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-8.719375027891331</v>
+        <v>-8.652314316479398</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-8.583129144034295</v>
+        <v>-8.514694341253268</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-7.546978485200292</v>
+        <v>-7.478207397812653</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-6.94462234981507</v>
+        <v>-6.875016251664874</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-9.508488659857768</v>
+        <v>-9.439514865817571</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-7.121549813743073</v>
+        <v>-7.0523372055628</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.704856004192038</v>
+        <v>-4.635436679821687</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.596151955590777</v>
+        <v>-2.526907383135267</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-3.041820274624222</v>
+        <v>-2.972728151084247</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-2.952960759194163</v>
+        <v>-2.883169018593691</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.765301527939677</v>
+        <v>-1.695350440459343</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.2258540825720203</v>
+        <v>-0.1561548757984639</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-4.099119105781334</v>
+        <v>-4.029264758074056</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0007757</t>
+          <t>X ≈ -0.0007779</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>146</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4391623973196701</v>
+        <v>0.4717649147340737</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.311420408143697</v>
+        <v>-5.290063676975926</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.707112090697173</v>
+        <v>-4.680141764592605</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.738877834050626</v>
+        <v>-4.708589896304282</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-9.172622304404577</v>
+        <v>-9.112777118625033</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-10.35362502460487</v>
+        <v>-10.28924600621075</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-10.44329205097187</v>
+        <v>-10.3779595811076</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-10.04547505094315</v>
+        <v>-9.979736390394628</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-10.01281046577071</v>
+        <v>-9.947026174716832</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-12.83172088080774</v>
+        <v>-12.76498666831756</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-13.24745818205851</v>
+        <v>-13.1809566801187</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-12.1692601824896</v>
+        <v>-12.10234238670522</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-13.97571065363775</v>
+        <v>-13.90742790814694</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-14.20306260792161</v>
+        <v>-14.13443951836052</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-10.77341681849826</v>
+        <v>-10.7039195653726</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-8.821682981815279</v>
+        <v>-8.75277518503264</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-8.276363817307647</v>
+        <v>-8.207217949118132</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-7.703000805657467</v>
+        <v>-7.633645352819585</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.341507948157648</v>
+        <v>-1.272293579630912</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.8958952650121716</v>
+        <v>0.9649730427049619</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>3.090271344362762</v>
+        <v>3.160058043800348</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>4.384509530307163</v>
+        <v>4.45445808735078</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>3.977015183547756</v>
+        <v>4.046711621176726</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>5.273171513258184</v>
+        <v>5.343025860965305</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.001503</t>
+          <t>X ≈ 0.0015</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>225</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.069058541650385</v>
+        <v>2.105131095637944</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.74044568451189</v>
+        <v>1.774883835402171</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9977947655321415</v>
+        <v>0.7831359133058626</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.049444872092849</v>
+        <v>1.834525884974994</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.574238938528481</v>
+        <v>2.383887367269232</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.636491367194417</v>
+        <v>3.448615209179934</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5.077104888107861</v>
+        <v>5.142499079314305</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4.802773481948925</v>
+        <v>4.868558701594317</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.756286899026293</v>
+        <v>1.822062903249659</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3382657987118662</v>
+        <v>-0.2715400895673312</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.157041192073329</v>
+        <v>-3.090585336740439</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.87819835574134</v>
+        <v>-3.811344428900185</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-4.115183907621223</v>
+        <v>-4.046948214869936</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.454336329256378</v>
+        <v>-3.385746089090532</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.458835617477462</v>
+        <v>-1.389372946513241</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>2.228907414876403</v>
+        <v>2.297809196342243</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>5.19600701864421</v>
+        <v>5.265169100574226</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>6.864683057352678</v>
+        <v>6.934062956643871</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>5.310076576465967</v>
+        <v>5.379276528718968</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>4.613062473489357</v>
+        <v>4.682117955398077</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>3.186451002835845</v>
+        <v>3.256209758630192</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>3.55641463906359</v>
+        <v>3.626343510152942</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>3.83356118700204</v>
+        <v>3.903248465660013</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>3.315789473684106</v>
+        <v>3.385643821391483</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.003782</t>
+          <t>X ≈ 0.003778</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>266</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8513656906668388</v>
+        <v>-0.8219821376202248</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.290451257574446</v>
+        <v>-2.26623238177207</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.460449227199746</v>
+        <v>-4.439852525673842</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-5.328326604049586</v>
+        <v>-5.521678587286502</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-6.057315839474455</v>
+        <v>-6.223483782711583</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.397175294342276</v>
+        <v>-4.55317179988112</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.418772361406077</v>
+        <v>-4.574518462617014</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.209564290134963</v>
+        <v>-3.144268916909631</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.68352556910687</v>
+        <v>-1.618124957578978</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.200088095512371</v>
+        <v>-3.133719694508514</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.302735091887932</v>
+        <v>-3.236578501191168</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.95525796825013</v>
+        <v>-3.888686937668275</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.448594878249423</v>
+        <v>-5.38064745374129</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-6.047396936421357</v>
+        <v>-5.97908428139764</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-7.456141551071084</v>
+        <v>-7.386966759635634</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-9.865141065750862</v>
+        <v>-9.796548238106951</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-10.38028256356681</v>
+        <v>-10.31141553754219</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-10.49386505214891</v>
+        <v>-10.42474506721555</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-12.15905296908576</v>
+        <v>-12.09007433059828</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-12.72918419314678</v>
+        <v>-12.66030705538102</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-12.9029145416804</v>
+        <v>-12.83328782043428</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-12.98677747638406</v>
+        <v>-12.91693709891707</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-15.34947658455119</v>
+        <v>-15.2798377740488</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-14.30659983291562</v>
+        <v>-14.23674548520839</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.00606</t>
+          <t>X ≈ 0.006057</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.0682036333016</v>
+        <v>-2.858901545125434</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.276646324076602</v>
+        <v>-2.063647874245149</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.327640385777556</v>
+        <v>-3.115599204946868</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.04021812392697655</v>
+        <v>0.2793405831403888</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.39005843843033</v>
+        <v>1.444555787924998</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.07764221945053151</v>
+        <v>-0.2424712461083445</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.172237013764779</v>
+        <v>0.8585671227835405</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.2197806184399056</v>
+        <v>-0.5381038666918201</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.5571998080217142</v>
+        <v>-0.6536046112464149</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.069111054176986</v>
+        <v>-2.167485021667986</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.06155211597564403</v>
+        <v>-0.0300159508345601</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.1575503663990503</v>
+        <v>0.06771992507658808</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1612431092248059</v>
+        <v>0.07692757458953992</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.8068308102391981</v>
+        <v>-0.8937031796127499</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.149104968207837</v>
+        <v>1.072937295588297</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.6162255623858854</v>
+        <v>0.535182386228044</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.388408367571614</v>
+        <v>-1.476359410172499</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.369437674046218</v>
+        <v>-3.464313240019088</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-5.029729549664296</v>
+        <v>-5.131920115523435</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-4.097432747117459</v>
+        <v>-4.196980470018374</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-3.516987477376766</v>
+        <v>-3.611635364739065</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-4.347496990888175</v>
+        <v>-4.444863149274532</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-5.578947751732571</v>
+        <v>-5.682283929704774</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-5.284043441938223</v>
+        <v>-5.385844648210146</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.008339</t>
+          <t>X ≈ 0.008335</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.893799316293908</v>
+        <v>-3.085543123013565</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.467600049815118</v>
+        <v>-4.664185027129896</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.46467065143429</v>
+        <v>-3.667608034694553</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.587309129351951</v>
+        <v>-4.78899882621041</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.141482980219706</v>
+        <v>-4.318036548909909</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.343892540327104</v>
+        <v>-5.347946683783192</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.009395736235497</v>
+        <v>-3.26421156126105</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.679382052398743</v>
+        <v>-5.182917290505692</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.034277396774812</v>
+        <v>-6.772646998308879</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-6.141932040962203</v>
+        <v>-6.899889294735814</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.882847938145275</v>
+        <v>-6.377241277226986</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.70350564123715</v>
+        <v>-3.955040169164128</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.766428684695221</v>
+        <v>-2.777916589910475</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.5243424224593198</v>
+        <v>-0.2886044418394675</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.007845165536018</v>
+        <v>-1.767630483928912</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-3.483412234505103</v>
+        <v>-3.235029725650925</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-3.208316436167635</v>
+        <v>-2.961122675144345</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-3.733003700614368</v>
+        <v>-3.483611369331719</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-3.521389367587624</v>
+        <v>-3.271888019060597</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-5.406552312261596</v>
+        <v>-5.148390051395054</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-3.885280108566157</v>
+        <v>-3.634648249330034</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-6.037709508175126</v>
+        <v>-5.778074072840589</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-4.526084515520324</v>
+        <v>-4.271521700843273</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-5.438475164397758</v>
+        <v>-5.180012744265085</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.01062</t>
+          <t>X ≈ 0.01061</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.862444348986557</v>
+        <v>-0.6292398772089882</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.988500783880788</v>
+        <v>6.872965110301465</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>7.583360667523799</v>
+        <v>7.479060807498783</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.690130055461601</v>
+        <v>7.594251246337471</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>8.134783136769556</v>
+        <v>8.070028558718931</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.86912617538254</v>
+        <v>5.786375264432614</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.554401535121748</v>
+        <v>7.493334397602318</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.448190965272914</v>
+        <v>6.375927378999272</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.44096023616779</v>
+        <v>4.351197583548554</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.247090292933798</v>
+        <v>3.149014394464622</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.371249369062717</v>
+        <v>3.020052923054315</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.57657504965907</v>
+        <v>3.9849015964746</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.298830455016862</v>
+        <v>2.431090627124981</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.513634425801236</v>
+        <v>1.386011460735105</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.8851702747236985</v>
+        <v>-0.2591320693784169</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3.112801124183505</v>
+        <v>2.256731052371357</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.336143588732725</v>
+        <v>0.7229245313278057</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.4024470151069437</v>
+        <v>0.04701796162808591</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.2081555586401507</v>
+        <v>-0.3086486039353815</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.3894712631955173</v>
+        <v>0.2906070677186818</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.085090874662967</v>
+        <v>0.9921662224685903</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.421194300353001</v>
+        <v>1.330217174098472</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.27971847110539</v>
+        <v>1.186823192690504</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.200528984979684</v>
+        <v>1.107866043613683</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.0129</t>
+          <t>X ≈ 0.01289</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>175</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.822942220896863</v>
+        <v>2.280812477797397</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.487741626095833</v>
+        <v>2.512266944790404</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.742951315198091</v>
+        <v>2.768843640948212</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.594211653590293</v>
+        <v>2.626218937688023</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.5337307534967479</v>
+        <v>0.5761620759213741</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.981059812531356</v>
+        <v>3.041167086077067</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.338275903491251</v>
+        <v>3.40823781421588</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.05959585718891</v>
+        <v>3.121830267783409</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.361201127769057</v>
+        <v>5.436438612748802</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.022186664630581</v>
+        <v>4.084997518850422</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.036519426580213</v>
+        <v>2.090034048801357</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.192447111990248</v>
+        <v>1.245872990178455</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.6328214439128246</v>
+        <v>0.6807460869857636</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4114771729568574</v>
+        <v>0.4604868207071746</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.942615020836463</v>
+        <v>-1.908644425421009</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.9961085748998215</v>
+        <v>-1.303602571294803</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.9254450289715663</v>
+        <v>0.263632918260015</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.945629270250308</v>
+        <v>1.298631236635899</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.595979673968493</v>
+        <v>0.9441933013777302</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.484586563992579</v>
+        <v>3.193864097031721</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.511043810720359</v>
+        <v>3.579671740305187</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.574699417543577</v>
+        <v>4.64389025102161</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>5.42220838827992</v>
+        <v>5.491518970114512</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.776106934001639</v>
+        <v>4.845961281708973</v>
       </c>
     </row>
     <row r="26">
@@ -2265,76 +2265,76 @@
         <v>132</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.969071498905478</v>
+        <v>5.008069552596481</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>6.880414831267842</v>
+        <v>7.690188015761443</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>9.939029223057545</v>
+        <v>10.77305405817533</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.229626153766795</v>
+        <v>7.043762002321188</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>8.119167898676324</v>
+        <v>8.209732459290123</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.30695335425505</v>
+        <v>6.137649162423664</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.7893865570125485</v>
+        <v>1.595417239294974</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.2299663146700723</v>
+        <v>0.5571311155772278</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1899580101795308</v>
+        <v>0.5997327476988019</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.2056559486651608</v>
+        <v>0.5740755732481162</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.311452764126443</v>
+        <v>3.113314174511558</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.771782363977493</v>
+        <v>5.854246158095577</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.404674737508067</v>
+        <v>5.478899817928713</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.930901075032459</v>
+        <v>6.012880594515934</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.278754758389859</v>
+        <v>5.349722271004516</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.619003278077706</v>
+        <v>3.687845835500873</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.990497167077407</v>
+        <v>2.043252167352271</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.605190537610099</v>
+        <v>1.186695161117846</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.074132312305579</v>
+        <v>0.6464124388014056</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.2493713796539083</v>
+        <v>-0.6746321568845346</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.7062713917875314</v>
+        <v>0.2912693059068161</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>1.378434795443063</v>
+        <v>1.44697636571825</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.8939280330363033</v>
+        <v>0.9628808351658193</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.7044125465177657</v>
+        <v>-0.6345581988105309</v>
       </c>
     </row>
     <row r="27">
@@ -2347,404 +2347,404 @@
         <v>85</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>9.618012430620283</v>
+        <v>9.704815695302095</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.461309027494487</v>
+        <v>3.497231356086026</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.651434637611985</v>
+        <v>-3.847004134897027</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-5.697657941771674</v>
+        <v>-6.917672030965527</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.92535399811738</v>
+        <v>-3.776550440513013</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.0678739237859034</v>
+        <v>-0.03630898893426604</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.173170046806476</v>
+        <v>-3.165971549450319</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.01282354792862606</v>
+        <v>0.03272906879628579</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.05979509234255431</v>
+        <v>0.08376165102115607</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.077482433401961</v>
+        <v>5.135926514299797</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.038505887420627</v>
+        <v>3.08568118092186</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.616382775875834</v>
+        <v>1.663870090324323</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.4618864207360573</v>
+        <v>1.664678909997235</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.57568734036392</v>
+        <v>3.806086610331462</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>4.221908695336261</v>
+        <v>5.457930187825518</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.514543890643807</v>
+        <v>3.747102934849103</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>3.531662623651805</v>
+        <v>4.765792885331194</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>4.602441291974728</v>
+        <v>5.85651357036582</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>5.555578119254015</v>
+        <v>4.876843562434338</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4.163897040297648</v>
+        <v>2.710748195931842</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.1146004170968666</v>
+        <v>-1.356437036584857</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.144244837736828</v>
+        <v>-2.599208185919032</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.2932873696626643</v>
+        <v>-0.4100367581606648</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.381148950808395</v>
+        <v>1.451003298515609</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.01973</t>
+          <t>X ≈ 0.01972</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.796173540444833</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.8192682288614108</v>
+        <v>-0.3170873264159226</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.307156344066705</v>
+        <v>4.342454600162831</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.821805869997519</v>
+        <v>4.849012775842077</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.141864602345365</v>
+        <v>6.952246693538676</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.396834895128862</v>
+        <v>2.261164099148282</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.852411602198771</v>
+        <v>2.708727610379846</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.506051276903392</v>
+        <v>7.308564946114515</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.799038885709237</v>
+        <v>8.569564323151241</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>10.23522335033638</v>
+        <v>9.016160842236701</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9.285745519259649</v>
+        <v>8.070708289276673</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.554371678468712</v>
+        <v>6.572446690706755</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.34825755740921</v>
+        <v>9.107821209216418</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>8.903063648182815</v>
+        <v>7.66723013764792</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>9.45415228454204</v>
+        <v>8.228599035189312</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>10.08605826161811</v>
+        <v>8.822985957132232</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>11.17580166566133</v>
+        <v>9.908581015276852</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>8.609326830386266</v>
+        <v>7.364715921211697</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>10.04928709151022</v>
+        <v>10.01963169238</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>12.71163952910595</v>
+        <v>12.64550189259185</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>12.96799184799874</v>
+        <v>12.10295572462578</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>13.70327825613786</v>
+        <v>12.02710976321665</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>14.00707670255229</v>
+        <v>12.30158447569883</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>15.20467836257313</v>
+        <v>13.44526441759752</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.02201</t>
+          <t>X ≈ 0.022</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.777550168811892</v>
+        <v>-0.6996706428437278</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.953955934245855</v>
+        <v>2.887121186257374</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.521790699404747</v>
+        <v>3.409886450951937</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2356656544819984</v>
+        <v>0.7361481177836993</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.6319021350331724</v>
+        <v>0.4003576452364257</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.457433867192563</v>
+        <v>-1.373460482391678</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.240622231089006</v>
+        <v>-2.145409166282029</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.560201086260676</v>
+        <v>3.458732330141359</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.683882116748947</v>
+        <v>7.421788139507044</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.845739201601219</v>
+        <v>4.688088149745063</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.135581816480233</v>
+        <v>4.962147791906986</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.88229349261124</v>
+        <v>4.683398388458933</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.755015271526723</v>
+        <v>5.521020635328419</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-7.650903044850168</v>
+        <v>-6.464764123471163</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1.825903064840446</v>
+        <v>2.681014147575723</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-3.637770384721485</v>
+        <v>-2.606951871657756</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-3.787347426634085</v>
+        <v>-2.740869008635229</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-5.910188303816696</v>
+        <v>-4.806494026181895</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-5.709548488648551</v>
+        <v>-4.590602645257569</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-11.62252711958109</v>
+        <v>-10.28610977646602</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-10.14270895157056</v>
+        <v>-8.867871630706446</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-8.180162082440901</v>
+        <v>-6.982933278390163</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-6.617040461124681</v>
+        <v>-6.70845856590806</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-10.81572980069227</v>
+        <v>-10.70585944658232</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.02429</t>
+          <t>X ≈ 0.02428</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.985865666001033</v>
+        <v>4.051460578875719</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.665054871603679</v>
+        <v>3.716683780525905</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.078977908199889</v>
+        <v>8.047895500725687</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>13.22599045581268</v>
+        <v>13.10417225051371</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>10.85684219632184</v>
+        <v>10.84530485488952</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>16.94790683087572</v>
+        <v>16.80150181021766</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>18.12146029230009</v>
+        <v>17.95263004940424</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.992586031756034</v>
+        <v>9.982110912343472</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.187660956219908</v>
+        <v>4.25436732502741</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.245901965762265</v>
+        <v>9.250682418221743</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.183681882830321</v>
+        <v>-3.936796401154851</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-10.30921692686391</v>
+        <v>-9.984776573833614</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-9.516017992366834</v>
+        <v>-9.184861717612755</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-7.798137570046322</v>
+        <v>-7.482863670982475</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-12.3858197966582</v>
+        <v>-11.98716081471688</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-9.794063632693558</v>
+        <v>-9.469696969696912</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-9.949704407213112</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-6.118754475610331</v>
+        <v>-5.862300964341728</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-2.002609765598102</v>
+        <v>-1.800255737263555</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.084455577102617</v>
+        <v>2.232743918858326</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.4267115057443647</v>
+        <v>-0.2328791721847452</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-6.370654782316365</v>
+        <v>-6.077955902824556</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-8.078211009930293</v>
+        <v>-7.726558113419422</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.9717922256621918</v>
+        <v>-2.033159597411981</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.02657</t>
+          <t>X ≈ 0.02656</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>55</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.689514957885564</v>
+        <v>2.722789250204393</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.354339443241294</v>
+        <v>2.388012451854635</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-4.539906475390382</v>
+        <v>-4.504552051721895</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.435517970401698</v>
+        <v>-3.399324252982794</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.800787755425709</v>
+        <v>-3.735114725530032</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.61362314241898</v>
+        <v>-3.548148539432709</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.568307456291187</v>
+        <v>-2.50191540514124</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.7895015345539491</v>
+        <v>0.8562367864693812</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9871642186052725</v>
+        <v>-0.9204578497977707</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-5.397363265738385</v>
+        <v>-5.329737162197944</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-3.30482218044115</v>
+        <v>-3.237495701854122</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.765734265734267</v>
+        <v>-1.698063287120334</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.7461381521422084</v>
+        <v>0.8151382823871671</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.929764113437585</v>
+        <v>-4.860486048604862</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-5.588695352474886</v>
+        <v>-5.518629346185421</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-4.993635302853548</v>
+        <v>-4.924242424242472</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-3.309547178820608</v>
+        <v>-3.239977743038082</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-5.232712413097751</v>
+        <v>-5.163000265041127</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-1.380225613802274</v>
+        <v>-1.31074524775314</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-1.193181818181863</v>
+        <v>-1.123899437785134</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-1.736382227179796</v>
+        <v>-1.666445605751143</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-1.812337282822384</v>
+        <v>-1.742291567160223</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>5.735165156386962</v>
+        <v>5.804910418049047</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>5.659223817118551</v>
+        <v>5.729078164825829</v>
       </c>
     </row>
     <row r="32">
@@ -2757,76 +2757,76 @@
         <v>41</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.862463960102858</v>
+        <v>4.895738252421687</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.527288445458531</v>
+        <v>4.560961454071872</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.08758798137243</v>
+        <v>3.122942405040916</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.812819058423145</v>
+        <v>4.849012775842048</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4304995070887472</v>
+        <v>-0.3648264771930698</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-5.121383674569728</v>
+        <v>-5.055909071583457</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.300872144595793</v>
+        <v>6.36726419574574</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.461341889321062</v>
+        <v>8.528077141236494</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.502857954343739</v>
+        <v>8.569564323151241</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.72902254357431</v>
+        <v>7.79664864711475</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.564357420445738</v>
+        <v>5.631683899032765</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.285263516970836</v>
+        <v>5.352934495584769</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.7172764820041451</v>
+        <v>-0.6482763517591863</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.939415487449338</v>
+        <v>4.008693552282061</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>3.280484248412037</v>
+        <v>3.350550254701503</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-5.880553262942186</v>
+        <v>-5.81116038433111</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-6.014646957091109</v>
+        <v>-5.945077521308583</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-8.558654763430297</v>
+        <v>-8.488942615373674</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-8.342531600498511</v>
+        <v>-8.273051234449376</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-5.716463414634141</v>
+        <v>-5.647181034237413</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-3.820639433388159</v>
+        <v>-3.750702811959506</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-6.335618879274705</v>
+        <v>-6.265573163612544</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-8.499868103036512</v>
+        <v>-8.430122841374427</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-6.136785052061043</v>
+        <v>-6.066930704353766</v>
       </c>
     </row>
     <row r="33">
@@ -2839,158 +2839,158 @@
         <v>25</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.325878594249204</v>
+        <v>6.359152886568033</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>13.99070307960491</v>
+        <v>14.02437608821825</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.55100261551874</v>
+        <v>12.58635703918723</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>11.83720930232558</v>
+        <v>11.87340301974449</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>15.47193951730154</v>
+        <v>15.53761254719721</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>15.65910413030838</v>
+        <v>15.72457873329465</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.886237998254295</v>
+        <v>6.952630049404242</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.60768335273573</v>
+        <v>14.67441860465117</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>14.64919941775837</v>
+        <v>14.71590578656587</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>25.87536400698894</v>
+        <v>25.94299011052938</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>26.14972327410422</v>
+        <v>26.21704975269125</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.87062937062937</v>
+        <v>13.93830034924331</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>20.74613815214223</v>
+        <v>20.81513828238719</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>24.52478134110788</v>
+        <v>24.5940594059406</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>27.86585010207057</v>
+        <v>27.93591610836004</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>24.46091015169196</v>
+        <v>24.53030303030303</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>16.32681645754303</v>
+        <v>16.39638589332556</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>8.221833041447752</v>
+        <v>8.291545189504376</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>16.43795620437957</v>
+        <v>16.5074365704287</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>12.625</v>
+        <v>12.69428238039673</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>16.08179959100205</v>
+        <v>16.1517362124307</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>16.00584453535944</v>
+        <v>16.0758902510216</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>12.28061970184162</v>
+        <v>12.35036496350371</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>8.204678362573098</v>
+        <v>8.274532710280376</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.0334</t>
+          <t>X ≈ 0.03339</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>32</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>11.9508785942492</v>
+        <v>11.98415288656803</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>14.74070307960483</v>
+        <v>14.77437608821818</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>22.67600261551877</v>
+        <v>22.71135703918726</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>15.71220930232561</v>
+        <v>15.74840301974452</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>18.47193951730154</v>
+        <v>18.53761254719721</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>9.284104130308322</v>
+        <v>9.349578733294592</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.386237998254295</v>
+        <v>5.452630049404242</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.142316647264266</v>
+        <v>-1.075581395348834</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.149199417758346</v>
+        <v>5.215905786565848</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.375364006988939</v>
+        <v>4.442990110529379</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>23.39972327410428</v>
+        <v>23.4670497526913</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>23.12062937062937</v>
+        <v>23.18830034924331</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>28.24613815214223</v>
+        <v>28.31513828238719</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>21.77478134110785</v>
+        <v>21.84405940594057</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>24.2408501020706</v>
+        <v>24.31091610836007</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>21.71091015169198</v>
+        <v>21.78030303030306</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>27.82681645754303</v>
+        <v>27.89638589332556</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>24.59683304144775</v>
+        <v>24.66654518950438</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>24.8129562043796</v>
+        <v>24.88243657042873</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>21.875</v>
+        <v>21.94428238039673</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>18.20679959100205</v>
+        <v>18.2767362124307</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>21.25584453535944</v>
+        <v>21.3258902510216</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>24.65561970184157</v>
+        <v>24.72536496350365</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>21.4546783625731</v>
+        <v>21.52453271028038</v>
       </c>
     </row>
   </sheetData>
@@ -3180,165 +3180,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.03154</t>
+          <t>X &gt; -0.03153</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3303</v>
+        <v>3307</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1864485254140504</v>
+        <v>-0.1873936599785111</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1145600782898626</v>
+        <v>-0.1156058883513253</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3045930523513007</v>
+        <v>-0.3054698838896996</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.4601123949359334</v>
+        <v>-0.460832026844038</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3269767981710672</v>
+        <v>-0.3288937666933478</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3938919552080975</v>
+        <v>-0.3957220185851114</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.4571354957216087</v>
+        <v>-0.4589222971661471</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.5077128509400737</v>
+        <v>-0.509451392339507</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.4791911789866603</v>
+        <v>-0.4809635692438832</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.5424834455283971</v>
+        <v>-0.544212539274902</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.4317001275845058</v>
+        <v>-0.4335526569472492</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.5426436308789278</v>
+        <v>-0.5443751554267777</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.533282487568087</v>
+        <v>-0.5350726880769443</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.5256261445546713</v>
+        <v>-0.5274359211622084</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.4119276757072043</v>
+        <v>-0.4139029507473211</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.4028772237233298</v>
+        <v>-0.4048402577814301</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.3680475907953351</v>
+        <v>-0.3700594898971374</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.4853292432304031</v>
+        <v>-0.4872051877971657</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.4628902285103891</v>
+        <v>-0.4647856517935196</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.6208421530087733</v>
+        <v>-0.6225403317748217</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.5715579407583888</v>
+        <v>-0.5733393162702072</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.7505851166829203</v>
+        <v>-0.7521544754818805</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.6697434942843401</v>
+        <v>-0.6714004536668483</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.6975317494462772</v>
+        <v>-0.6991594578478413</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02926</t>
+          <t>X &gt; -0.02925</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3277</v>
+        <v>3281</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1892729209023187</v>
+        <v>-0.1904839173060608</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.144489402965597</v>
+        <v>-0.1457722617666448</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.355001023050086</v>
+        <v>-0.3561020765002354</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.5061331301888288</v>
+        <v>-0.5070877406311567</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.399419705999442</v>
+        <v>-0.4017813921967317</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.4683617270513167</v>
+        <v>-0.4706319366053719</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.526026725485842</v>
+        <v>-0.5282674642403933</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.5140901061163774</v>
+        <v>-0.5163608918608134</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.4249196587908415</v>
+        <v>-0.4272980969292703</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.4825819061073915</v>
+        <v>-0.4849309820351095</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.3730730784793153</v>
+        <v>-0.3755428399012928</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.4522651261781689</v>
+        <v>-0.4546544032620119</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4643241349623892</v>
+        <v>-0.4667572218655422</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.5156810866377839</v>
+        <v>-0.5180645685352445</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.4262984067547464</v>
+        <v>-0.4288255329773492</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.4523318574404698</v>
+        <v>-0.4547988243640404</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.3857292184618402</v>
+        <v>-0.3882856395211576</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.472653708476102</v>
+        <v>-0.4751113362029571</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.4212759711231797</v>
+        <v>-0.4237868014520103</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.5819491008838753</v>
+        <v>-0.5842564323886634</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.5279565065589296</v>
+        <v>-0.5303587936594383</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.7077876695810943</v>
+        <v>-0.709976334418549</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.6589776135946721</v>
+        <v>-0.6612133424073861</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.686380532758001</v>
+        <v>-0.6885882894148381</v>
       </c>
     </row>
     <row r="8">
@@ -3348,79 +3348,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3239</v>
+        <v>3243</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2406450109010052</v>
+        <v>-0.2421943271490505</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.007456993992185801</v>
+        <v>-0.009314570281020451</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2649483047266585</v>
+        <v>-0.2665841372833597</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.4094921398345903</v>
+        <v>-0.4109978383615456</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3279377079900598</v>
+        <v>-0.331179604856743</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.4305489246502319</v>
+        <v>-0.4336549373585754</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.5105678985516064</v>
+        <v>-0.513627619307421</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.5259572002596542</v>
+        <v>-0.5290180323540525</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.4055024875889046</v>
+        <v>-0.4087105424703452</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.3625702075822232</v>
+        <v>-0.365883085663441</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1011992351208235</v>
+        <v>-0.1048175691760207</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.2087308262331291</v>
+        <v>-0.2122372851652941</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2077080017039208</v>
+        <v>-0.211290728061492</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2569976678179486</v>
+        <v>-0.2605363518214716</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.1587804398013475</v>
+        <v>-0.1624848756498025</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.1920002271192587</v>
+        <v>-0.1956274526252955</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.1537750396843265</v>
+        <v>-0.1574602605205939</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.2404165733442341</v>
+        <v>-0.2440042103109548</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.1908970631913292</v>
+        <v>-0.1945338729210562</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.3247378970089443</v>
+        <v>-0.328199910949138</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.23282101356304</v>
+        <v>-0.2364338430221693</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.5063430610614219</v>
+        <v>-0.5096259277149144</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.4601210388991817</v>
+        <v>-0.463445147470452</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.517766836562437</v>
+        <v>-0.5210269566946479</v>
       </c>
     </row>
     <row r="9">
@@ -3430,79 +3430,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3197</v>
+        <v>3201</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1648046355644652</v>
+        <v>-0.1669017040026901</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01737396295492744</v>
+        <v>-0.01968224252953377</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2283634503606962</v>
+        <v>-0.2305268838419465</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4276337191229729</v>
+        <v>-0.4296084673713167</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3402495374248318</v>
+        <v>-0.344375030442535</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.5088585446527958</v>
+        <v>-0.5127620557703381</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.7043033832018324</v>
+        <v>-0.7080287448779146</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.685189351901677</v>
+        <v>-0.6889634282987842</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.5326187640598121</v>
+        <v>-0.5365817756231905</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5101856660101305</v>
+        <v>-0.5142416157536687</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2801832679517986</v>
+        <v>-0.2845059411481543</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3232004829075521</v>
+        <v>-0.3274948577283752</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.338649877782963</v>
+        <v>-0.3430186291943755</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2921815525622193</v>
+        <v>-0.2966288531687127</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.2152478392893826</v>
+        <v>-0.2198471315153441</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.2567185534562455</v>
+        <v>-0.2612208088992176</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.153832730971331</v>
+        <v>-0.1584769495672091</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.2090130403505555</v>
+        <v>-0.2135998058183546</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.06797758700081857</v>
+        <v>-0.07272562545401939</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2372305529522052</v>
+        <v>-0.2417550611009318</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1369504089979543</v>
+        <v>-0.1416470584806646</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.4130363649219007</v>
+        <v>-0.4173972919069016</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.432325889152807</v>
+        <v>-0.4366431564213968</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.5522812870984666</v>
+        <v>-0.5564576052460168</v>
       </c>
     </row>
     <row r="10">
@@ -3512,79 +3512,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2754492590546178</v>
+        <v>-0.2780431980546325</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1509793998385121</v>
+        <v>-0.1537666786800713</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3398547081130232</v>
+        <v>-0.3425529134194036</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.529879305269354</v>
+        <v>-0.5324124037700528</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.402704357342337</v>
+        <v>-0.408008698455653</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.6727514745048566</v>
+        <v>-0.6776983065536015</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8578228189772474</v>
+        <v>-0.8626182897289425</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.7383242518270094</v>
+        <v>-0.7433029143361765</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.615459853240047</v>
+        <v>-0.6205931054885738</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.5786626258582359</v>
+        <v>-0.5839256589449704</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.4129154826353343</v>
+        <v>-0.4183636144293885</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.4517056547513363</v>
+        <v>-0.4571369131141125</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4471338250078816</v>
+        <v>-0.4526905607189917</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3641075477810105</v>
+        <v>-0.3697960157461466</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.210364569253656</v>
+        <v>-0.2163198573868712</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.1998268241657399</v>
+        <v>-0.2057375788340252</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.002698249726059032</v>
+        <v>-0.003487162847086722</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.01204283165754561</v>
+        <v>0.005830903790098318</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.1835841853016689</v>
+        <v>0.1771729946903662</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.0397582697201031</v>
+        <v>0.03354540453903354</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.1836131449314067</v>
+        <v>0.1771572483379131</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1278282845005307</v>
+        <v>-0.1338999587686089</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1523634245513108</v>
+        <v>-0.1583790746521601</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.3048757775542938</v>
+        <v>-0.3107090199995213</v>
       </c>
     </row>
     <row r="11">
@@ -3594,79 +3594,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3082</v>
+        <v>3086</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1797574766042587</v>
+        <v>-0.1831436718108677</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1433175389518269</v>
+        <v>-0.1467950829529485</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2765835913778147</v>
+        <v>-0.2800736013019929</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5535063649858287</v>
+        <v>-0.5567322024061951</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2881378770873724</v>
+        <v>-0.2949156331570535</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4054119987239417</v>
+        <v>-0.4120192048497344</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.7084699720587153</v>
+        <v>-0.7147885777307934</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.6137498299627779</v>
+        <v>-0.6202300091463826</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4247431072658543</v>
+        <v>-0.4314660289775105</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.5018969749232056</v>
+        <v>-0.5086227926964284</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3704705869619573</v>
+        <v>-0.3773355328846932</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3724216959511111</v>
+        <v>-0.3793239244816817</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3143209490540144</v>
+        <v>-0.3214455083780692</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2255420741573246</v>
+        <v>-0.2328139790723185</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1535610917178474</v>
+        <v>-0.1610144247578944</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1539765796996306</v>
+        <v>-0.1613582495935404</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.1520026019263199</v>
+        <v>0.1442035460898623</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.09877604662909789</v>
+        <v>0.0910277250800533</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.204720052776068</v>
+        <v>0.1968574698140131</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.08708684381075926</v>
+        <v>0.07939564900514284</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.2438741452970206</v>
+        <v>0.2359058466165251</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.03955105478323873</v>
+        <v>-0.04716674379705665</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.004816561538262931</v>
+        <v>-0.01244682787957174</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.1911684901199564</v>
+        <v>-0.1985716319101627</v>
       </c>
     </row>
     <row r="12">
@@ -3676,79 +3676,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3020</v>
+        <v>3024</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1414234103515142</v>
+        <v>-0.1456058925589758</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1631430742412761</v>
+        <v>-0.1673507666734366</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3026639415348527</v>
+        <v>-0.3069106127011167</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6693696450428419</v>
+        <v>-0.6732461261162186</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3911733487728384</v>
+        <v>-0.3992918234896123</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4488616366436204</v>
+        <v>-0.4568808327803637</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.7423428380973647</v>
+        <v>-0.7500993159361116</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.6400109819151183</v>
+        <v>-0.6479498164014572</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.5797956399022581</v>
+        <v>-0.5878125418316316</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.7086834551073053</v>
+        <v>-0.7166543924330995</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.5472763961891616</v>
+        <v>-0.5554230823432675</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.5436186504788054</v>
+        <v>-0.551818227831788</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.4613841177356974</v>
+        <v>-0.4698699548451017</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.399311068133045</v>
+        <v>-0.4079181814028416</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.2794123607884558</v>
+        <v>-0.2882843532291517</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.3581123053754141</v>
+        <v>-0.3667945950267821</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.1753308830582228</v>
+        <v>-0.1842805533916945</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.2276051607994347</v>
+        <v>-0.2365076157761479</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1901429691741541</v>
+        <v>-0.1990672262038515</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.2810846560846514</v>
+        <v>-0.2898655720471339</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.07698307522355208</v>
+        <v>-0.08612305416989585</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.2654989457788872</v>
+        <v>-0.2744071713181242</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.2026639790587978</v>
+        <v>-0.2116185075707335</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.3582355447116683</v>
+        <v>-0.3670016812540169</v>
       </c>
     </row>
     <row r="13">
@@ -3758,79 +3758,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2953</v>
+        <v>2957</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1458955992991804</v>
+        <v>-0.1509142275259236</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.3622380968657097</v>
+        <v>-0.3670304240342119</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.5061594557657187</v>
+        <v>-0.5110237532909423</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.8314755278123229</v>
+        <v>-0.8360360128386546</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5724750183646847</v>
+        <v>-0.5820111087167632</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.7030634900215276</v>
+        <v>-0.7123960566213725</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.019485907469608</v>
+        <v>-1.028540091819693</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.9086521137513017</v>
+        <v>-0.9179123741581137</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.8481051644518729</v>
+        <v>-0.857445492034401</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9625193769005165</v>
+        <v>-0.9718533765120156</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.7700339747156804</v>
+        <v>-0.7795832439416941</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.7937888418495405</v>
+        <v>-0.8033635106421784</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.7518375563597957</v>
+        <v>-0.7616811246208925</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.649703977825645</v>
+        <v>-0.6597323028561632</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.5460337601846632</v>
+        <v>-0.5563293400553349</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.5725244987639684</v>
+        <v>-0.5826817926311989</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.4502105694839926</v>
+        <v>-0.4605641741508251</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.5013842616952005</v>
+        <v>-0.5116947699961258</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.4004481228685748</v>
+        <v>-0.410861876566571</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.4977595536016182</v>
+        <v>-0.5080141410487329</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2091341031792879</v>
+        <v>-0.2198854091909226</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.3664058876524123</v>
+        <v>-0.3769654434697856</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.3422645229384003</v>
+        <v>-0.3528128593496263</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.3642346072880613</v>
+        <v>-0.3747740195133318</v>
       </c>
     </row>
     <row r="14">
@@ -3840,79 +3840,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2852</v>
+        <v>2856</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.03022642033615597</v>
+        <v>0.02361971532801732</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2166733991703538</v>
+        <v>-0.2230179354093025</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4542184078018323</v>
+        <v>-0.4605668398534419</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8703115890393249</v>
+        <v>-0.8762492751094726</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5545320953769703</v>
+        <v>-0.5667352788897375</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.731139772130696</v>
+        <v>-0.7430621852857797</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.031503375046505</v>
+        <v>-1.043193131939297</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.046431012675697</v>
+        <v>-1.058171924596742</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.9852616914149834</v>
+        <v>-0.9970862022881875</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.146268930903588</v>
+        <v>-1.15805518563787</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.166158052248257</v>
+        <v>-1.177861366165445</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.181046607024264</v>
+        <v>-1.192801463866878</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.16793799176277</v>
+        <v>-1.17997856449108</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.019593222134617</v>
+        <v>-1.031900119530434</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.0289419286879</v>
+        <v>-1.041396282564918</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.042586351804552</v>
+        <v>-1.054892500423229</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.9463559803723172</v>
+        <v>-0.9588359019940356</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.9958016681393715</v>
+        <v>-1.008245166889751</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.7241018985255749</v>
+        <v>-0.7368835973448071</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.8665966386554587</v>
+        <v>-0.8791441930298447</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.5836995333412176</v>
+        <v>-0.5967772538162421</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.7790188143252195</v>
+        <v>-0.7918494270749719</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.5886407257784825</v>
+        <v>-0.6016826388764613</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.643848986655513</v>
+        <v>-0.6568398387392307</v>
       </c>
     </row>
     <row r="15">
@@ -3922,899 +3922,899 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2755</v>
+        <v>2759</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3575560600519481</v>
+        <v>0.3685020415482541</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2939079769761364</v>
+        <v>0.285433261896749</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1705991573054817</v>
+        <v>0.1618966075325474</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2708988057825295</v>
+        <v>-0.2791698481936251</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1049604257370049</v>
+        <v>0.08908842912666159</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1923203197457681</v>
+        <v>-0.2077223109978092</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6924055803892912</v>
+        <v>-0.707312313708151</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9505988558532295</v>
+        <v>-0.965221034988474</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.9970099685232157</v>
+        <v>-1.01156357176145</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.136553652816048</v>
+        <v>-1.151131779120817</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.058369211444855</v>
+        <v>-1.072993537351984</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.9916763756662519</v>
+        <v>-1.006484926830311</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.010911739397905</v>
+        <v>-1.026016952269849</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.9218732701037027</v>
+        <v>-0.9371793083967077</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.8722106794055549</v>
+        <v>-0.8877833136052828</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.9071680242038056</v>
+        <v>-0.9225339772864203</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.8027997625873056</v>
+        <v>-0.818364648973791</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.8502422935757892</v>
+        <v>-0.8657784994648878</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.6852322014175414</v>
+        <v>-0.7009570619880847</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.5855835447625921</v>
+        <v>-0.601410706827302</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.346046674407674</v>
+        <v>-0.3623839903209287</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.4729367486449121</v>
+        <v>-0.4891224255448634</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.3942714447477016</v>
+        <v>-0.4105046017137468</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.4486791691873364</v>
+        <v>-0.4648656224488761</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.00875</t>
+          <t>X &gt; -0.008751</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2640</v>
+        <v>2644</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.437782462067446</v>
+        <v>0.4679708978250616</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4234604049241923</v>
+        <v>0.4333817167360436</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2443509807949482</v>
+        <v>0.233636588905803</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.03497114880223506</v>
+        <v>-0.04551589917442556</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.373030152878826</v>
+        <v>0.3532340267315774</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.02035410896933598</v>
+        <v>-0.03950841922231518</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.320386013789367</v>
+        <v>-0.3393654410128946</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.577557611119687</v>
+        <v>-0.5962580870781622</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.7029663072887047</v>
+        <v>-0.7214766880486465</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.8525937925589133</v>
+        <v>-0.8711558638874735</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.7451127605734413</v>
+        <v>-0.7637556669549141</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.7764294529000395</v>
+        <v>-0.7951333856964595</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.785359395952824</v>
+        <v>-0.8044474049951091</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6450299796468357</v>
+        <v>-0.6644183634640655</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.7155013513080561</v>
+        <v>-0.7350224517605781</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.7022318422657534</v>
+        <v>-0.7215823392293927</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.5874260811800482</v>
+        <v>-0.6070090519781033</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.7834579638432473</v>
+        <v>-0.8027944331371302</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.5828377464710996</v>
+        <v>-0.6024162042032373</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.4113086232980336</v>
+        <v>-0.4310952631078067</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.09981221376526861</v>
+        <v>-0.1202698321480682</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1152758280016499</v>
+        <v>-0.135749960618611</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1207434181887237</v>
+        <v>-0.1411284202392622</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.2119883040935662</v>
+        <v>-0.2322751565880026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.006472</t>
+          <t>X &gt; -0.006473</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2501</v>
+        <v>2506</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2878437289560196</v>
+        <v>0.3575693552932862</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3307744232434047</v>
+        <v>0.3790870937605746</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1021524965655303</v>
+        <v>0.1287165007865951</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.07393706816231571</v>
+        <v>-0.0695898543647786</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1782887236507378</v>
+        <v>0.1712759135338402</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.03068015253936096</v>
+        <v>0.0241032974784261</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.08437359825086332</v>
+        <v>-0.09136519435318746</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3005407235455522</v>
+        <v>-0.3073419028825413</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5940438254848743</v>
+        <v>-0.6002386005820881</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.709129034760565</v>
+        <v>-0.7157400482007858</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.8097039335329583</v>
+        <v>-0.8158998304766172</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.6283758024705079</v>
+        <v>-0.635170659493788</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6949446504055388</v>
+        <v>-0.7025414951257289</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.6938566517236637</v>
+        <v>-0.7016480662374605</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.6122375473318229</v>
+        <v>-0.6207439314013854</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.5115888518951266</v>
+        <v>-0.5198163014392065</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.3031675934936544</v>
+        <v>-0.311930859559439</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.7035758137576735</v>
+        <v>-0.711639523871419</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.5835920797385441</v>
+        <v>-0.5917271093801375</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.4528443113772411</v>
+        <v>-0.4610961056590455</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.01404705436537057</v>
+        <v>-0.02363246034730082</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.06606916819629305</v>
+        <v>-0.07562490049355119</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.08708613349016758</v>
+        <v>-0.09638413900931653</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.1791680988423323</v>
+        <v>-0.18835635596065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004193</t>
+          <t>X &gt; -0.004195</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2336</v>
+        <v>2340</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.5437675302390232</v>
+        <v>0.5770418225578524</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1891763620476254</v>
+        <v>0.242265024208038</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.08200544557587364</v>
+        <v>-0.05120124822268934</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1780708334978485</v>
+        <v>-0.1706834575764091</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3296889865159685</v>
+        <v>0.2989520978542686</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1811677473467341</v>
+        <v>-0.2109598587325507</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.004810033953404513</v>
+        <v>-0.02573227558514901</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.1644254908016833</v>
+        <v>-0.1948513444150493</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.5664534958954022</v>
+        <v>-0.596196124262157</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.8054870568408461</v>
+        <v>-0.8352596770661975</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.060153269105605</v>
+        <v>-1.089367586875206</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.9317556378885143</v>
+        <v>-0.9613595147022735</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.094509483136854</v>
+        <v>-1.124461887753178</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.120572452583509</v>
+        <v>-1.150621445123235</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.9017405162663152</v>
+        <v>-0.9325385531980643</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.177315104280737</v>
+        <v>-1.207346032729333</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.9023768843263653</v>
+        <v>-0.9329707321537697</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.067663115682905</v>
+        <v>-1.098054128483696</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.9118942868634861</v>
+        <v>-0.9424568197631942</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.8279914529914478</v>
+        <v>-0.8586186434940615</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.6193547484592656</v>
+        <v>-0.6506538857340445</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.6699467392342271</v>
+        <v>-0.7012233271167503</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.5409464085563798</v>
+        <v>-0.5723176507637504</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.8055956100296413</v>
+        <v>-0.8365784008307315</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001915</t>
+          <t>X &gt; -0.001917</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2178</v>
+        <v>2182</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7804240487946572</v>
+        <v>0.8136983411134864</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.9452485341503305</v>
+        <v>0.9789215427636719</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8038448165191951</v>
+        <v>0.8136297664599539</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7525869183401426</v>
+        <v>0.7370393833808464</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.004939062135399</v>
+        <v>0.9921580017426734</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.5807799044431192</v>
+        <v>0.5427605514764124</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.9272402761586278</v>
+        <v>0.8880552426739072</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9486131613045501</v>
+        <v>0.9091774763527098</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.5151364902617814</v>
+        <v>0.476488399219491</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1410593506752988</v>
+        <v>-0.1790499623303674</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3879307651472104</v>
+        <v>-0.425319267809833</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3668135517450537</v>
+        <v>-0.4044526133820341</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5512579191231808</v>
+        <v>-0.589330481862703</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.6543777082522695</v>
+        <v>-0.6924369444243652</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.4633680049253144</v>
+        <v>-0.5022399847481296</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.5729416323885559</v>
+        <v>-0.6112494811124947</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.4512155790702437</v>
+        <v>-0.4898635356374399</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.8038079841932699</v>
+        <v>-0.8419100207332804</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.7897121419328528</v>
+        <v>-0.8277257523879413</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.6673923006416089</v>
+        <v>-0.7055346369866129</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.4500665254582898</v>
+        <v>-0.4889960530155264</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.5904857398699193</v>
+        <v>-0.6292379541066069</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.5638043458867443</v>
+        <v>-0.6024522605000158</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.5666714996858531</v>
+        <v>-0.6053939624968905</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.0003636</t>
+          <t>X &gt; 0.0003613</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2032</v>
+        <v>2036</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8049438328081138</v>
+        <v>0.8382181251269429</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.394792660909651</v>
+        <v>1.428465669522993</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.199809239970762</v>
+        <v>1.207583913578652</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.147150822793414</v>
+        <v>1.127541286540982</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.736200853235225</v>
+        <v>1.716775156739573</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.366421203479049</v>
+        <v>1.31951544215535</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.744217500450482</v>
+        <v>1.695932533573753</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.738542727735734</v>
+        <v>1.690013146561498</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.271573623913717</v>
+        <v>1.223950642733584</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.7707696765881593</v>
+        <v>0.7234779154074218</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.5360313425639305</v>
+        <v>0.4893777175522089</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4811968853064741</v>
+        <v>0.4343940992433062</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.4132942950692993</v>
+        <v>0.3657000801400017</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.3191006359168824</v>
+        <v>0.2714787607793099</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.2774130614042392</v>
+        <v>0.2293146413673739</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.01973368110371609</v>
+        <v>-0.02742691098855232</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.1110244026141416</v>
+        <v>0.06354203625262755</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.308098263753422</v>
+        <v>-0.3548798839530178</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.7500653960131629</v>
+        <v>-0.7958461341278849</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.7797151277013725</v>
+        <v>-0.8253254627405227</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.7044411952387435</v>
+        <v>-0.7506669263628325</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.947941108691694</v>
+        <v>-0.9937859020696607</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.8900640168008351</v>
+        <v>-0.9358402402273214</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.986266519316672</v>
+        <v>-1.031950590309016</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.002642</t>
+          <t>X &gt; 0.002639</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1807</v>
+        <v>1811</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.6475416139428631</v>
+        <v>0.6808159062616923</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.351753407832447</v>
+        <v>1.385426416445789</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.224963228210207</v>
+        <v>1.260317651878694</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.034800982675883</v>
+        <v>1.039704989109914</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.631851894081379</v>
+        <v>1.633892634724567</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.083761664554892</v>
+        <v>1.054994488218007</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.329220454394644</v>
+        <v>1.267728517675572</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.356997669795518</v>
+        <v>1.295108259823571</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.211219176265502</v>
+        <v>1.149640726324911</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.9088620849680709</v>
+        <v>0.847099699570478</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9958771202581218</v>
+        <v>0.9341550158491998</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.02401034918902</v>
+        <v>0.9618878423864743</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.9771612544524615</v>
+        <v>0.9139308180622692</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.7889530527204229</v>
+        <v>0.7258551225798087</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.4936034060353336</v>
+        <v>0.430421602865529</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.2553432918342153</v>
+        <v>-0.3163159911373228</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.5221361334161756</v>
+        <v>-0.5827120164654147</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.201222667322241</v>
+        <v>-1.26046361621934</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.50464865213258</v>
+        <v>-1.5630480110691</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.451200993926008</v>
+        <v>-1.509574368914571</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.188918641042157</v>
+        <v>-1.248484294735789</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.50880444197611</v>
+        <v>-1.567794249805765</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.47822985568056</v>
+        <v>-1.537052255039391</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.521940342462869</v>
+        <v>-1.580795837483294</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.004921</t>
+          <t>X &gt; 0.004918</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9062757755432429</v>
+        <v>0.9395500678620721</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.980453239758624</v>
+        <v>2.014126248371966</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.206351750688505</v>
+        <v>2.241706174356992</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.133173427886121</v>
+        <v>2.169367145305024</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.959119004481025</v>
+        <v>2.986683655461142</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.029854611385936</v>
+        <v>2.02054285885513</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.321411297355702</v>
+        <v>2.273578159590024</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.145255607070993</v>
+        <v>2.059428213876025</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.710896075856056</v>
+        <v>1.626162196822278</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.618129280300835</v>
+        <v>1.532470546706413</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.737882862263859</v>
+        <v>1.65222305179271</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.88350767069376</v>
+        <v>1.797002982512417</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.086344337709242</v>
+        <v>1.997657562592849</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.969010870443789</v>
+        <v>1.88023303938111</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.865850102070574</v>
+        <v>1.776327948771872</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.403453728192929</v>
+        <v>1.315879334230914</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.179529635837604</v>
+        <v>1.092262181985348</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.4028285165608736</v>
+        <v>0.3173350025282318</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.3344633195154003</v>
+        <v>0.2493720542996698</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.4955501618122966</v>
+        <v>0.4102281518621922</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.8330949277896167</v>
+        <v>0.7460514579087345</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.4724679961501081</v>
+        <v>0.3861682083583773</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.9161579638389696</v>
+        <v>0.8290195560004108</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.6848860199384461</v>
+        <v>0.5981573057496377</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.007199</t>
+          <t>X &gt; 0.007196</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.735461283584591</v>
+        <v>1.725948253363399</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.868601070331309</v>
+        <v>2.858352922195046</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.360894423864956</v>
+        <v>3.350835803665994</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.569821357967001</v>
+        <v>2.560661707003177</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.286468110810034</v>
+        <v>3.305952315536985</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.437139706487756</v>
+        <v>2.489057497773359</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.561160598873492</v>
+        <v>2.566529663303854</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.638667086275625</v>
+        <v>2.59719852743109</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.184083138688599</v>
+        <v>2.098145168805246</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.387388832435029</v>
+        <v>2.298476972971422</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.087611472862037</v>
+        <v>2.000499095305386</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.243589743589745</v>
+        <v>2.15501861549717</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.48797329988718</v>
+        <v>2.39530869292166</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.548127644609821</v>
+        <v>2.454524522219671</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.01538281235095</v>
+        <v>1.921951794938785</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.567691133765216</v>
+        <v>1.47750799924713</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.71527199576456</v>
+        <v>1.624047120986781</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.189826796326756</v>
+        <v>1.100254365243103</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.45358120437956</v>
+        <v>1.363467698833368</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.453772478498827</v>
+        <v>1.364064311860901</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.740641531534131</v>
+        <v>1.648228807910044</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.478045005210646</v>
+        <v>1.386342669118328</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.271215313126838</v>
+        <v>2.177062855775318</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.930168558651538</v>
+        <v>1.837032710280376</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.009478</t>
+          <t>X &gt; 0.009474</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.814428212569823</v>
+        <v>2.847702504888652</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.578489339146863</v>
+        <v>4.612162347760204</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.951765974297373</v>
+        <v>4.98712039796586</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.237972661104216</v>
+        <v>4.27416637852312</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.017741044019097</v>
+        <v>5.083414073914774</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4.250707183743437</v>
+        <v>4.316181786729707</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.859520441002381</v>
+        <v>3.925912492152328</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.344324574109777</v>
+        <v>4.411059826025209</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.099581097147677</v>
+        <v>4.166287465955179</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.375364006988939</v>
+        <v>4.442990110529379</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.945329768851167</v>
+        <v>3.953690974065346</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.629711588602603</v>
+        <v>3.579521723289112</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.712645329175722</v>
+        <v>3.601397824371922</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.264244942640438</v>
+        <v>3.094059405940598</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.953098424218226</v>
+        <v>2.782143424501399</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.744979249580631</v>
+        <v>2.57619213164147</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.862839512298073</v>
+        <v>2.693036611028909</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.337217656832365</v>
+        <v>2.168939825519701</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.613124635563402</v>
+        <v>2.444157567552388</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.052745664739888</v>
+        <v>2.882382188458152</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.051905666219014</v>
+        <v>2.879882225879307</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.229782759297663</v>
+        <v>3.056659481790824</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.855498928894704</v>
+        <v>3.680490083811641</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.647618401257809</v>
+        <v>3.472991284461493</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.01176</t>
+          <t>X &gt; 0.01175</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.931863631655688</v>
+        <v>3.893399461910498</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.846064675614855</v>
+        <v>3.932221667296673</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.152000121753147</v>
+        <v>4.237664635700305</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.188830249956503</v>
+        <v>3.275644613766907</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.070443257949918</v>
+        <v>4.185184153672928</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.758854753749716</v>
+        <v>3.874018334788985</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.736612063092203</v>
+        <v>2.85300364840797</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.704940210591097</v>
+        <v>3.820122216108203</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.995832834217218</v>
+        <v>4.110675400513564</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.718256775068745</v>
+        <v>4.832155739421033</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.119798087071857</v>
+        <v>4.234484372865651</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.341951066389967</v>
+        <v>3.457602964436333</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.838407478825523</v>
+        <v>3.9533699137695</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.492362388489425</v>
+        <v>3.607758036077584</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.581560825262592</v>
+        <v>3.696812745969005</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.633194795886709</v>
+        <v>2.672270651722712</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.326816457543032</v>
+        <v>3.285551522217212</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.925212265477796</v>
+        <v>2.80711181466004</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.470537658013654</v>
+        <v>3.272069198075023</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.862139272271015</v>
+        <v>3.661863427778279</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.649638786981946</v>
+        <v>3.44761636224343</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.779429441019808</v>
+        <v>3.575890251021598</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.638302321488929</v>
+        <v>4.4304650886601</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.391311401665156</v>
+        <v>4.184307146370607</v>
       </c>
     </row>
     <row r="26">
@@ -4824,79 +4824,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.245878594249206</v>
+        <v>4.346373333852384</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.230703079604879</v>
+        <v>4.331085353393931</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.55100261551874</v>
+        <v>4.650254802765502</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.357209302325579</v>
+        <v>3.458067556485702</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.071939517301537</v>
+        <v>5.19895440023236</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.979104130308315</v>
+        <v>4.107965314764236</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.566237998254294</v>
+        <v>2.697038995091141</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.887683352735735</v>
+        <v>4.016271639794937</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.609199417758369</v>
+        <v>3.738270003818272</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.915364006988938</v>
+        <v>5.042031644075706</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.709723274104277</v>
+        <v>4.836858059400569</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.950629370629372</v>
+        <v>4.078875429115513</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.74613815214223</v>
+        <v>4.872646269607635</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.364781341107872</v>
+        <v>4.491822984215354</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.145850102070575</v>
+        <v>5.271379367145975</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.660910151691958</v>
+        <v>3.789088972795042</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.006816457543039</v>
+        <v>4.134405062654629</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.202602272216978</v>
+        <v>3.230842314105011</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.001359093625155</v>
+        <v>3.925966921866397</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.969051446945336</v>
+        <v>3.793323913943055</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.688884937217829</v>
+        <v>3.41052215492271</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.554231632133629</v>
+        <v>3.2758902510216</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>4.416322448206678</v>
+        <v>4.132416245554928</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>4.28234826548573</v>
+        <v>3.998449243185675</v>
       </c>
     </row>
     <row r="27">
@@ -4906,79 +4906,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.049455830021564</v>
+        <v>4.168483515371278</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.511028282856905</v>
+        <v>3.428027203836876</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.087587981372394</v>
+        <v>3.00420693776735</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.577046700699569</v>
+        <v>2.494092674916892</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.244297240878765</v>
+        <v>4.389539524884846</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.618453723804258</v>
+        <v>3.56230692802076</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.048839624270563</v>
+        <v>2.9931980007227</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.006057336475578</v>
+        <v>4.946223878484837</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.641069336457548</v>
+        <v>4.582031547214953</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.30625831593202</v>
+        <v>6.243192950285973</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.361105387925413</v>
+        <v>5.300214052894148</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.455995224287911</v>
+        <v>3.6015863533001</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.567276363524343</v>
+        <v>4.709661608959195</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.939415487449338</v>
+        <v>4.082903219328017</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>5.10975254109497</v>
+        <v>5.250317731078091</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>3.672292265513093</v>
+        <v>3.81630708709816</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.554458733965802</v>
+        <v>4.696588733082152</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.636467187789215</v>
+        <v>3.780389002891795</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.796408342872446</v>
+        <v>4.807639410185296</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.114795918367349</v>
+        <v>4.994485220153322</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>4.498977505112471</v>
+        <v>4.249099295595009</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>4.145188797654519</v>
+        <v>3.767573821001314</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>5.37302216590728</v>
+        <v>4.984511304967072</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>5.6367771280052</v>
+        <v>5.243982812113366</v>
       </c>
     </row>
     <row r="28">
@@ -4988,407 +4988,407 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.869088470792413</v>
+        <v>3.009399191986752</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.521567277135738</v>
+        <v>3.413538649794575</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.304089035271829</v>
+        <v>4.438573787955697</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.331036462819412</v>
+        <v>4.464536024670601</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.187988900017594</v>
+        <v>6.099188901877014</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.399844871049062</v>
+        <v>4.315711738220706</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.367719479735776</v>
+        <v>4.282679310487985</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.064473476192518</v>
+        <v>5.974911215488596</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.61216238072133</v>
+        <v>5.52378755996488</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.566722031680293</v>
+        <v>6.475009814962874</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.853426977807985</v>
+        <v>5.76384778224795</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.845938012604684</v>
+        <v>4.007265866484687</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.437496176833584</v>
+        <v>5.347157986820683</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.228485044811585</v>
+        <v>4.140857435497246</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>5.297948867502676</v>
+        <v>5.206852068951171</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>3.917700275148739</v>
+        <v>3.830795641140462</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.771260901987475</v>
+        <v>4.68210017903985</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.431709584657625</v>
+        <v>3.345732381622604</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.635487068577099</v>
+        <v>4.793150856142994</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5.316358024691354</v>
+        <v>5.47260750354944</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>5.428334244467401</v>
+        <v>5.42267217302183</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>5.26639044106664</v>
+        <v>5.100520792893512</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>6.449773930697283</v>
+        <v>6.113911761533217</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>6.538842951101778</v>
+        <v>6.038079508309941</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.02087</t>
+          <t>X &gt; 0.02086</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.530212959574278</v>
+        <v>4.692486219901369</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.195037444929952</v>
+        <v>4.357709421551554</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.303324596942893</v>
+        <v>4.462900249063772</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.208726330189357</v>
+        <v>4.367230180238316</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.701041684484196</v>
+        <v>5.88329155954289</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.649816204611732</v>
+        <v>4.835689844405707</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.496145118997326</v>
+        <v>4.681025111132634</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.455980566358029</v>
+        <v>5.637381567614128</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.56870406172122</v>
+        <v>4.752942823602908</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.652453790270677</v>
+        <v>5.831878999418265</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.998020487726571</v>
+        <v>5.180012715654264</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.170938968152591</v>
+        <v>3.358053435663052</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.213630412204147</v>
+        <v>4.395385195967442</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.063481031510349</v>
+        <v>3.248380393594921</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4.262134931791941</v>
+        <v>4.442088947866218</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.380414795654808</v>
+        <v>2.567340067340069</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.175113671165327</v>
+        <v>3.35934885628852</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>2.141337685410605</v>
+        <v>2.328582226541414</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.286253418001863</v>
+        <v>3.470399533391664</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>3.473297213622295</v>
+        <v>3.657245343359691</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>3.549291851063963</v>
+        <v>3.731983126010952</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>3.163739272201539</v>
+        <v>3.347495189293205</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>4.566333987555858</v>
+        <v>4.547895827701183</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>4.379133191233528</v>
+        <v>4.163421599169261</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.02315</t>
+          <t>X &gt; 0.02314</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.666537934908547</v>
+        <v>5.699812227227376</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.59876168766349</v>
+        <v>4.632434696276832</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.624262688778813</v>
+        <v>4.6596171124473</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.009370474486758</v>
+        <v>5.045564191905662</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.841902887264901</v>
+        <v>6.907575917160578</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.930166401370592</v>
+        <v>5.995641004356862</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.889901001917295</v>
+        <v>5.956293053067242</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.977646722699099</v>
+        <v>6.044381974614531</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.187660956219908</v>
+        <v>4.25436732502741</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.977928109553041</v>
+        <v>6.045554213093482</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.153386277767275</v>
+        <v>5.220712756354303</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.042790542790549</v>
+        <v>3.110461521404481</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.116101522105595</v>
+        <v>4.185101652350554</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.993645809972342</v>
+        <v>5.062923874805065</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>4.701014937235406</v>
+        <v>4.771080943524872</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>3.464573155354955</v>
+        <v>3.533966033966031</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.429380560107134</v>
+        <v>4.49894999588966</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.591796411411117</v>
+        <v>3.661508559467741</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.906820673244034</v>
+        <v>4.976301039293169</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>6.192765567765562</v>
+        <v>6.262047948162291</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>6.015865525067973</v>
+        <v>6.085802146496626</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>5.207309736824634</v>
+        <v>5.277355452486795</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>6.580986002207858</v>
+        <v>6.650731263869943</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>7.116443068455446</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.02543</t>
+          <t>X &gt; 0.02542</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>221</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.054385381579522</v>
+        <v>6.087659673898351</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.814232491369587</v>
+        <v>4.847905499982929</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.827020715066254</v>
+        <v>3.862375138734741</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.113227401873097</v>
+        <v>3.149421119292001</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.915378431328683</v>
+        <v>5.981051461224361</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.387610917638639</v>
+        <v>3.45308552062491</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.067233473367416</v>
+        <v>3.133625524517363</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.051122266762881</v>
+        <v>5.117857518678314</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.187660956219908</v>
+        <v>4.25436732502741</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.223780296581694</v>
+        <v>5.291406400122135</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.308094314828253</v>
+        <v>7.37542079341528</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.124023035787744</v>
+        <v>6.191694014401676</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.261975256214619</v>
+        <v>7.330975386459578</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.945595820745886</v>
+        <v>8.014873885578609</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>8.644130645056997</v>
+        <v>8.714196651346462</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>6.524258567981541</v>
+        <v>6.593651446592617</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>7.747630937181043</v>
+        <v>7.817200372963569</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>5.832692769954534</v>
+        <v>5.902404918011158</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>6.501304620669153</v>
+        <v>6.570784986718287</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>7.140837104072389</v>
+        <v>7.210119484469118</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>7.502614070640057</v>
+        <v>7.57255069206871</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>7.879147702780251</v>
+        <v>7.949193418442412</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>9.963877620393596</v>
+        <v>10.03362288205568</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>8.982958905559521</v>
+        <v>9.052813253266798</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.02771</t>
+          <t>X &gt; 0.0277</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>166</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.169252088225107</v>
+        <v>7.202526380543937</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.629257296472346</v>
+        <v>5.662930305085688</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.599195386603085</v>
+        <v>6.634549810271572</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.2829924348557</v>
+        <v>5.319186152274604</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.134590119711163</v>
+        <v>9.20026314960684</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>5.707296901392667</v>
+        <v>5.772771504378937</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.93443076933864</v>
+        <v>5.000822820488587</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.463105039482713</v>
+        <v>6.529840291398145</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.90221146595114</v>
+        <v>5.968917834758642</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.742833886507007</v>
+        <v>8.810459990047448</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.82442206928499</v>
+        <v>10.89174854787202</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.738099250147442</v>
+        <v>8.805770228761375</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>9.420836947322947</v>
+        <v>9.489837077567906</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>12.21152832905968</v>
+        <v>12.28080639389241</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>13.35982600568503</v>
+        <v>13.42989201197449</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>10.34042822398111</v>
+        <v>10.40982110259219</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>11.41115380694062</v>
+        <v>11.48072324272314</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>9.49894147518269</v>
+        <v>9.568653623239314</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>9.112654999560284</v>
+        <v>9.182135365609419</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>9.902108433734938</v>
+        <v>9.971390814131667</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>10.56372730184543</v>
+        <v>10.63366392327408</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>11.09018188475702</v>
+        <v>11.16022760041918</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>11.36495705123915</v>
+        <v>11.43470231290124</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>10.08419643486226</v>
+        <v>10.15405078256953</v>
       </c>
     </row>
     <row r="33">
@@ -5401,76 +5401,76 @@
         <v>125</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.925878594249205</v>
+        <v>7.959152886568035</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.990703079604877</v>
+        <v>6.024376088218219</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.751002615518743</v>
+        <v>7.78635703918723</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.437209302325584</v>
+        <v>5.473403019744488</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>12.27193951730153</v>
+        <v>12.33761254719721</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.25910413030833</v>
+        <v>9.324578733294601</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.486237998254296</v>
+        <v>4.552630049404243</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.807683352735737</v>
+        <v>5.874418604651169</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.049199417758366</v>
+        <v>5.115905786565868</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.075364006988941</v>
+        <v>9.142990110529382</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.54972327410427</v>
+        <v>12.61704975269129</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9.870629370629374</v>
+        <v>9.938300349243306</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.74613815214223</v>
+        <v>12.81513828238719</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>14.92478134110788</v>
+        <v>14.9940594059406</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>16.66585010207057</v>
+        <v>16.73591610836004</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>15.66091015169196</v>
+        <v>15.73030303030303</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>17.12681645754303</v>
+        <v>17.19638589332556</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>15.42183304144775</v>
+        <v>15.49154518950438</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>14.83795620437957</v>
+        <v>14.90743657042871</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>15.02500000000001</v>
+        <v>15.09428238039673</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>15.28179959100205</v>
+        <v>15.3517362124307</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>16.80584453535943</v>
+        <v>16.87589025102159</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>17.88061970184157</v>
+        <v>17.95036496350366</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>15.4046783625731</v>
+        <v>15.47453271028038</v>
       </c>
     </row>
     <row r="34">
@@ -5483,158 +5483,158 @@
         <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>8.325878594249204</v>
+        <v>8.359152886568033</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.99070307960487</v>
+        <v>4.024376088218212</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.55100261551874</v>
+        <v>6.586357039187227</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.837209302325583</v>
+        <v>3.873403019744487</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.47193951730154</v>
+        <v>11.53761254719721</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.659104130308322</v>
+        <v>7.724578733294592</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.886237998254295</v>
+        <v>3.952630049404242</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.607683352735734</v>
+        <v>3.674418604651166</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.649199417758368</v>
+        <v>2.71590578656587</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.875364006988939</v>
+        <v>4.942990110529379</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.149723274104275</v>
+        <v>9.217049752691302</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.870629370629374</v>
+        <v>8.938300349243306</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.74613815214223</v>
+        <v>10.81513828238719</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.52478134110788</v>
+        <v>12.5940594059406</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>13.86585010207057</v>
+        <v>13.93591610836004</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>13.46091015169196</v>
+        <v>13.53030303030303</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>17.32681645754303</v>
+        <v>17.39638589332556</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>17.22183304144775</v>
+        <v>17.29154518950438</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>14.43795620437957</v>
+        <v>14.5074365704287</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>15.625</v>
+        <v>15.69428238039673</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>15.08179959100205</v>
+        <v>15.1517362124307</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>17.00584453535944</v>
+        <v>17.0758902510216</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>19.28061970184157</v>
+        <v>19.35036496350365</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>17.2046783625731</v>
+        <v>17.27453271028038</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.03454</t>
+          <t>X &gt; 0.03453</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>68</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>6.619996241308023</v>
+        <v>6.653270533626852</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-1.068120449806884</v>
+        <v>-1.034447441193542</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.037232678598912</v>
+        <v>-1.001878254930425</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-1.751025991792069</v>
+        <v>-1.714832274373165</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.17782187024271</v>
+        <v>8.243494900138387</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>6.89439824795538</v>
+        <v>6.95987285094165</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>3.180355645313114</v>
+        <v>3.246747696463061</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>5.842977470382792</v>
+        <v>5.909712722298224</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.472728829523078</v>
+        <v>1.53943519833058</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.110658124635997</v>
+        <v>5.178284228176437</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2.443840921163094</v>
+        <v>2.511167399750121</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2.164747017688192</v>
+        <v>2.232417996302125</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>2.510844034495172</v>
+        <v>2.57984416474013</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>8.171840164637295</v>
+        <v>8.241118229470018</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>8.983497160894096</v>
+        <v>9.053563167183562</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>9.578557210515477</v>
+        <v>9.647950089126553</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>12.3856399869548</v>
+        <v>12.45520942273733</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>13.75124480615364</v>
+        <v>13.82095695421026</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>9.555603263203089</v>
+        <v>9.625083629252224</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>12.68382352941177</v>
+        <v>12.7531059098085</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>13.61121135570793</v>
+        <v>13.68114797713658</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>15.00584453535944</v>
+        <v>15.0758902510216</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>16.75120793713568</v>
+        <v>16.82095319879777</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>15.2046783625731</v>
+        <v>15.27453271028038</v>
       </c>
     </row>
   </sheetData>
@@ -5824,165 +5824,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.03154</t>
+          <t>X &lt; -0.03153</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>68</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.732944935162557</v>
+        <v>-0.6996706428437278</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-5.479885155689239</v>
+        <v>-5.446212147075897</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.903943791989327</v>
+        <v>1.939298215657814</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.543091655266757</v>
+        <v>8.579285372685661</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8248806937721227</v>
+        <v>0.8905537236678001</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.012045306778909</v>
+        <v>1.077519909765179</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.180355645313114</v>
+        <v>3.246747696463061</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.842977470382792</v>
+        <v>5.909712722298224</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.355081770699542</v>
+        <v>7.421788139507044</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.522422830518359</v>
+        <v>9.5900489340588</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.385017391751333</v>
+        <v>5.45234387033836</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.45886466474703</v>
+        <v>12.52653564336096</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>15.74613815214223</v>
+        <v>15.81513828238719</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.52478134110788</v>
+        <v>15.5940594059406</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>11.92467363148234</v>
+        <v>11.99473963777181</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>11.04914544580961</v>
+        <v>11.11853832442068</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>7.973875281072452</v>
+        <v>8.043444716854978</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>12.28065657085952</v>
+        <v>12.35036871891614</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>15.43795620437957</v>
+        <v>15.5074365704287</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>20.03676470588235</v>
+        <v>20.10604708627908</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>20.96415253217852</v>
+        <v>21.03408915360718</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>26.77055041771238</v>
+        <v>26.84059613337454</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>27.04532558419451</v>
+        <v>27.11507084585659</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>26.96938424492604</v>
+        <v>27.03923859263332</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02926</t>
+          <t>X &lt; -0.02925</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>94</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.4826320440486711</v>
+        <v>-0.4493577517298419</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.945467133161081</v>
+        <v>-2.91179412454774</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.061640913391081</v>
+        <v>3.096995337059568</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.666996536368138</v>
+        <v>7.703190253787042</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.046407602407918</v>
+        <v>3.112080632303595</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.233572215414704</v>
+        <v>3.299046818400974</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.58836565782876</v>
+        <v>4.654757708978707</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.309811012310199</v>
+        <v>4.376546264225631</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.287497290098798</v>
+        <v>3.3542036589063</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.641321453797445</v>
+        <v>4.708947557337886</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.724191359210657</v>
+        <v>1.791517837797684</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.700416604671929</v>
+        <v>5.768087583285862</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.831244535120952</v>
+        <v>8.900244665365911</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>10.73754729855468</v>
+        <v>10.8068253633874</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>9.014786272283352</v>
+        <v>9.084852278572818</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>9.609846321904733</v>
+        <v>9.679239200515809</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>6.284263266053671</v>
+        <v>6.353832701836197</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>8.306939424426474</v>
+        <v>8.376651572483098</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>9.586892374592345</v>
+        <v>9.65637274064148</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>12.9654255319149</v>
+        <v>13.03470791231163</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>13.48605491015098</v>
+        <v>13.55599153157963</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>17.66541900344453</v>
+        <v>17.73546471910669</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>19.00402395716072</v>
+        <v>19.0737692188228</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>18.92808261789225</v>
+        <v>18.99793696559953</v>
       </c>
     </row>
     <row r="8">
@@ -5995,76 +5995,76 @@
         <v>132</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.8713331397037436</v>
+        <v>0.9046074320225728</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.524448435546638</v>
+        <v>-5.490775426933297</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1459670814509622</v>
+        <v>-0.1106126577824753</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.928118393234676</v>
+        <v>2.96431211065358</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2901213354833558</v>
+        <v>0.3557943653790332</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.2348617060659</v>
+        <v>1.30033630905217</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.734722846739146</v>
+        <v>2.801114897889093</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.213743958796343</v>
+        <v>3.280479210711775</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.740108508667461</v>
+        <v>1.806814877474963</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2086973403222743</v>
+        <v>0.2763234438627151</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-5.577549453168452</v>
+        <v>-5.510222974581424</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.068764568764571</v>
+        <v>-2.001093590150639</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.1629527569486768</v>
+        <v>-0.09395262670371807</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.130841947168484</v>
+        <v>1.200120012001207</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.2856650494445745</v>
+        <v>-0.2155990431551089</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.3093950001768064</v>
+        <v>0.3787878787878824</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-1.339850209123632</v>
+        <v>-1.270280773341106</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.07031788993260335</v>
+        <v>0.1400300379892272</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.044016810440176</v>
+        <v>1.113497176489311</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>2.746212121212125</v>
+        <v>2.815494501608853</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2.20301171221417</v>
+        <v>2.272948333642823</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>7.430086959601859</v>
+        <v>7.50013267526402</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>8.462437883659739</v>
+        <v>8.532183145321824</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>9.144072301967036</v>
+        <v>9.213926649674313</v>
       </c>
     </row>
     <row r="9">
@@ -6077,76 +6077,76 @@
         <v>174</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.8005581873599894</v>
+        <v>-0.7672838950411602</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.851296235055969</v>
+        <v>-0.8159418113874821</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.457898957497989</v>
+        <v>2.494092674916892</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3684912414394717</v>
+        <v>0.434164271335149</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.279793785480727</v>
+        <v>2.345268388466998</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.52991615917383</v>
+        <v>5.596308210323777</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.251361513655269</v>
+        <v>5.318096765570701</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.568739647643426</v>
+        <v>3.635446016450928</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.794904236873997</v>
+        <v>2.862530340414438</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.953725001757789</v>
+        <v>-0.8863985231707616</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4913190258017792</v>
+        <v>0.5589900044157119</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.240391025705442</v>
+        <v>2.309391155950401</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.444321570992933</v>
+        <v>1.513599635825656</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.7853903319556323</v>
+        <v>0.8554563382450979</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.380450381577013</v>
+        <v>1.449843260188089</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.052493887284562</v>
+        <v>-0.9829244515020363</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.5827646597016738</v>
+        <v>-0.5130525116450499</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-1.516066784126181</v>
+        <v>-1.446586418077047</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.3951149425287426</v>
+        <v>0.4643973229254712</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1480854664692117</v>
+        <v>-0.07814884504055897</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>3.798947983635301</v>
+        <v>3.868993699297462</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>5.797861081151915</v>
+        <v>5.867606342814</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>7.446057672917924</v>
+        <v>7.515912020625201</v>
       </c>
     </row>
     <row r="10">
@@ -6159,76 +6159,76 @@
         <v>231</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.8713331397037436</v>
+        <v>0.9046074320225728</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.195444106542311</v>
+        <v>-1.16177109792897</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.8280588925750223</v>
+        <v>0.8634133162435091</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.144568609684889</v>
+        <v>3.180762327103793</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.047697093059114</v>
+        <v>1.113370122954791</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.832264303468499</v>
+        <v>3.897738906454769</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6.089701201717503</v>
+        <v>6.15609325286745</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.512445257497639</v>
+        <v>4.579180509413071</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.688160456719402</v>
+        <v>3.754866825526904</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.914325045949973</v>
+        <v>2.981951149490413</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.024182148563156</v>
+        <v>1.091508627150183</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.043789543789551</v>
+        <v>2.111460522403483</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.083800489804567</v>
+        <v>3.152800620049526</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.996642812969341</v>
+        <v>2.065920877802064</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.4719107081311833</v>
+        <v>0.5419767144206489</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.2011698919516931</v>
+        <v>0.2705627705627691</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-2.963226832500254</v>
+        <v>-2.893657396717728</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.501110681495966</v>
+        <v>-3.431398533439342</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-4.583688817265454</v>
+        <v>-4.514208451216319</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-3.530844155844157</v>
+        <v>-3.461561775447429</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-4.506944997742544</v>
+        <v>-4.437008376313891</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.119696590181682</v>
+        <v>-1.049650874519521</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.453779875001743</v>
+        <v>0.5235251366638281</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>2.109440267335003</v>
+        <v>2.179294615042281</v>
       </c>
     </row>
     <row r="11">
@@ -6241,76 +6241,76 @@
         <v>289</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3869241739168885</v>
+        <v>-0.3536498815980593</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.068120449806884</v>
+        <v>-1.034447441193542</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.08567558517329843</v>
+        <v>-0.05032116150481158</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.660738714090293</v>
+        <v>2.696932431509197</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4726971608991519</v>
+        <v>-0.4070241310034746</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.06048821335330246</v>
+        <v>0.1259628163395732</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.0938504550017</v>
+        <v>3.160242506151647</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.123254286991788</v>
+        <v>2.18998953890722</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7806873070317266</v>
+        <v>0.8473936758392284</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.390934941244993</v>
+        <v>1.458561044785434</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.281211163377634</v>
+        <v>0.3485376419646613</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.6941587823940836</v>
+        <v>0.7618297610080162</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.953750608889635</v>
+        <v>1.022750739134594</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.04035227536392938</v>
+        <v>0.1096303401966523</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.2725582024277031</v>
+        <v>-0.2024921961382375</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.3695396752976663</v>
+        <v>-0.3001467966865903</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-3.963840981903338</v>
+        <v>-3.894271546120812</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.722803636752936</v>
+        <v>-3.653091488696312</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.852701235066803</v>
+        <v>-3.783220869017669</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-3.319636678200688</v>
+        <v>-3.250354297803959</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-4.208857848444325</v>
+        <v>-4.138921227015672</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.862667575367205</v>
+        <v>-1.792621859705044</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.241871647639407</v>
+        <v>-1.172126385977322</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.4122908193205035</v>
+        <v>0.482145167027781</v>
       </c>
     </row>
     <row r="12">
@@ -6323,76 +6323,76 @@
         <v>351</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.682668414297801</v>
+        <v>-0.6493941219789718</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.7329436440418533</v>
+        <v>-0.6992706354285119</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1065581710742975</v>
+        <v>0.1419125947427844</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.096468561584835</v>
+        <v>3.132662279003739</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4519964973585147</v>
+        <v>0.517669527254192</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3542608254650119</v>
+        <v>0.4197354284512826</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.715297827314124</v>
+        <v>2.781689878464071</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.866942611994986</v>
+        <v>1.933677863910418</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.90845867701762</v>
+        <v>1.975165045825122</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.844024975649909</v>
+        <v>2.911651079190349</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.693882818263823</v>
+        <v>1.761209296850851</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.984589484589492</v>
+        <v>2.052260463203424</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.999699405703481</v>
+        <v>2.06869953594844</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.493442309768845</v>
+        <v>1.562720374601568</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.8345110707315442</v>
+        <v>0.9045770770210098</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.429571120352925</v>
+        <v>1.498963998964001</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.4139242831977157</v>
+        <v>-0.3443548474151896</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.2340074143926998</v>
+        <v>-0.1642952663360759</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.2670160334393969</v>
+        <v>0.3364963994885315</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.4540598290598297</v>
+        <v>0.5233422094565583</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.6589411497387019</v>
+        <v>-0.5890045283100491</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.4047049342198363</v>
+        <v>0.4747506498819973</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.6794801007019657</v>
+        <v>0.7492253623640508</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.743139901034638</v>
+        <v>1.812994248741916</v>
       </c>
     </row>
     <row r="13">
@@ -6405,76 +6405,76 @@
         <v>418</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5640735588608408</v>
+        <v>-0.5307992665420116</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.7753920748201892</v>
+        <v>0.8090650834335307</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.48880165858094</v>
+        <v>1.524156082249426</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.645821742516972</v>
+        <v>3.682015459935876</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.605910809167561</v>
+        <v>1.671583839063238</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.032309871935119</v>
+        <v>2.09778447492139</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.130257137010275</v>
+        <v>4.196649188160222</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.373233591970177</v>
+        <v>3.439968843885609</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.414749656992811</v>
+        <v>3.481456025800313</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.076320944787987</v>
+        <v>4.143947048328428</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.915273513338718</v>
+        <v>2.982599991925746</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.353882959146127</v>
+        <v>3.421553937760059</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.664798439223567</v>
+        <v>3.733798569468526</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.964972728667682</v>
+        <v>3.034250793500405</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2.545275939391153</v>
+        <v>2.615341945680619</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>2.661867089491004</v>
+        <v>2.73125996810208</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>1.570835596299013</v>
+        <v>1.640405032081539</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.705086629964505</v>
+        <v>1.774798778021129</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.681975343135548</v>
+        <v>1.751455709184683</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.869019138755981</v>
+        <v>1.938301519152709</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.3688809307149654</v>
+        <v>0.4388175521436182</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.010629224354652</v>
+        <v>1.080674940016813</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>1.524638840597547</v>
+        <v>1.594384102259632</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.448697501329079</v>
+        <v>1.518551849036356</v>
       </c>
     </row>
     <row r="14">
@@ -6487,76 +6487,76 @@
         <v>519</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.458321791107252</v>
+        <v>-1.425047498788423</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.252071486869113</v>
+        <v>-0.2183984782557715</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8130450047287638</v>
+        <v>0.8483994283972507</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.98942510194022</v>
+        <v>3.025618819359124</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.082729498033714</v>
+        <v>1.148402527929392</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.655250565761108</v>
+        <v>1.720725168747379</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.194523162030791</v>
+        <v>3.260915213180738</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.301324971232845</v>
+        <v>3.368060223148277</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.342841036255479</v>
+        <v>3.40954740506298</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.110431444368515</v>
+        <v>4.178057547908956</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.384790711483852</v>
+        <v>4.452117190070879</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.683731490089869</v>
+        <v>4.751402468703802</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.100666090485198</v>
+        <v>5.169666220730157</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.301274597369918</v>
+        <v>4.370552662202641</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4.605734495134165</v>
+        <v>4.67580050142363</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>4.622759862674606</v>
+        <v>4.692152741285682</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.910631486444771</v>
+        <v>3.980200922227297</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>3.998326297709795</v>
+        <v>4.068038445766419</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3.058380096479766</v>
+        <v>3.127860462528901</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>3.438102119460495</v>
+        <v>3.507384499857224</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.316867028381623</v>
+        <v>2.386803649810275</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>3.011624882180243</v>
+        <v>3.081670597842404</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.515687139221143</v>
+        <v>2.585432400883228</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.632424027312986</v>
+        <v>2.702278375020263</v>
       </c>
     </row>
     <row r="15">
@@ -6569,896 +6569,896 @@
         <v>616</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.700095431724826</v>
+        <v>-2.749437064809605</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.548257959356157</v>
+        <v>-2.514584950742815</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.202244137728016</v>
+        <v>-2.166889714059529</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.3186348535185743</v>
+        <v>-0.2824411360996706</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.144943599581588</v>
+        <v>-2.07927056968591</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.14609067488648</v>
+        <v>-1.080616071900209</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.003121115137418</v>
+        <v>1.069513166287365</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.185605430657809</v>
+        <v>2.252340682573241</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.714134482693431</v>
+        <v>2.780840851500933</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3.239000370625305</v>
+        <v>3.306626474165746</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.026346650727646</v>
+        <v>3.093673129314674</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.909590409590407</v>
+        <v>2.97726138820434</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3.408475814479893</v>
+        <v>3.477475944724851</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3.024781341107875</v>
+        <v>3.094059405940598</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>3.015200751421219</v>
+        <v>3.085266757710684</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>3.123247814029618</v>
+        <v>3.192640692640694</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.502141132867706</v>
+        <v>2.571710568650232</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.559495379110089</v>
+        <v>2.629207527166713</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.288605555028923</v>
+        <v>2.358085921078057</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.501623376623371</v>
+        <v>1.5709057570201</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.7960853052877539</v>
+        <v>0.8660219267164067</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.04480557432047</v>
+        <v>1.114851289982631</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.157243078464937</v>
+        <v>1.226988340127022</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.243639401534132</v>
+        <v>1.31349374924141</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.00875</t>
+          <t>X &lt; -0.008751</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>731</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.511330708076372</v>
+        <v>-2.617654753268248</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.572908411503192</v>
+        <v>-2.609503693202548</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.097424197066758</v>
+        <v>-2.062069773398271</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.169630642954857</v>
+        <v>-1.133436925535953</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.766090578457693</v>
+        <v>-2.700417548562015</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.621333626189625</v>
+        <v>-1.555859023203354</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.6158139853298366</v>
+        <v>-0.5494219341798896</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.3368215196303979</v>
+        <v>0.4035567715458299</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.062332112696808</v>
+        <v>1.12903848150431</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.519686852406181</v>
+        <v>1.587312955946622</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.246850497086491</v>
+        <v>1.314176975673519</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.514952216046616</v>
+        <v>1.582623194660549</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.895248959255767</v>
+        <v>1.964249089500726</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.400294337003906</v>
+        <v>1.469572401836629</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1.835754342836644</v>
+        <v>1.90582034912611</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.746819864414256</v>
+        <v>1.816212743025332</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.202329453439063</v>
+        <v>1.271898889221589</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.781340565387559</v>
+        <v>1.851052713444183</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.450268105884355</v>
+        <v>1.519748471933489</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.5429206566347489</v>
+        <v>0.6122030370314775</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2738775635807116</v>
+        <v>-0.2039409421520588</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.4866315248320845</v>
+        <v>-0.4165858091699235</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.07505745274119136</v>
+        <v>-0.005312191079106299</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.122599019207847</v>
+        <v>0.1924533669151245</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.006472</t>
+          <t>X &lt; -0.006473</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.605155888509415</v>
+        <v>-1.805984728110865</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.82538887441811</v>
+        <v>-1.96643906677604</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.311066349998505</v>
+        <v>-1.390654455065643</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.87543437583534</v>
+        <v>-0.8906936430863581</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.700474275801916</v>
+        <v>-1.686783310110037</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.51330966279513</v>
+        <v>-1.499817124012658</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.251693036228467</v>
+        <v>-1.236092620331085</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6107074518619697</v>
+        <v>-0.5937056761313357</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.4652913717813547</v>
+        <v>0.4834546933552843</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7259387196326159</v>
+        <v>0.7462122048907176</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.115240515483578</v>
+        <v>1.135346645671738</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7212040832730509</v>
+        <v>0.7415224436046444</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.205908267084752</v>
+        <v>1.229407557415954</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.214436513521669</v>
+        <v>1.238478278207566</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.130217918162529</v>
+        <v>1.155708973722525</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.8057377378988519</v>
+        <v>0.8294975067126984</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.09693140007177448</v>
+        <v>0.1202063766397075</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.14137327133281</v>
+        <v>1.166113659009554</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.127611376793361</v>
+        <v>1.15185544269567</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.5100574712643677</v>
+        <v>0.5331776623299831</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4929130526761085</v>
+        <v>-0.4696677001124527</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.5688681083187177</v>
+        <v>-0.5455136615215537</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.1791504131009631</v>
+        <v>-0.1559641504204023</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.0252066948981593</v>
+        <v>-0.001646806405474877</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004193</t>
+          <t>X &lt; -0.004195</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1035</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.88668179222423</v>
+        <v>-1.956535275125901</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.159055374501406</v>
+        <v>-1.278128728737464</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.6663886888290875</v>
+        <v>-0.736690212500335</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5106167846309404</v>
+        <v>-0.5281413817999123</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.745451787046292</v>
+        <v>-1.679778757150615</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7853403141361213</v>
+        <v>-0.7198657111498505</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.268351373726382</v>
+        <v>-1.201959322576435</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.8705775168294849</v>
+        <v>-0.8038422649140529</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2337404805603001</v>
+        <v>0.3004468493678019</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.715943717133861</v>
+        <v>0.7835698206743018</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.376776414200897</v>
+        <v>1.444102892787924</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.194300868213915</v>
+        <v>1.261971846827848</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.808940084509381</v>
+        <v>1.877940214754339</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.877438345938785</v>
+        <v>1.946716410771508</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.508362179365264</v>
+        <v>1.57842818565473</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>2.103422228986645</v>
+        <v>2.172815107597721</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.389618389910183</v>
+        <v>1.459187825692709</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.671108403766596</v>
+        <v>1.740820551823219</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.597376494234638</v>
+        <v>1.666856860283772</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.204710144927532</v>
+        <v>1.27399252532426</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.9513648083933575</v>
+        <v>1.02130142982201</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.8754097527507483</v>
+        <v>0.9454554684129093</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.8603298467690976</v>
+        <v>0.9300751084311827</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.364098652428169</v>
+        <v>1.433953000135446</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001915</t>
+          <t>X &lt; -0.001917</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1193</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.999079529703891</v>
+        <v>-2.054870485719107</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.374762134141982</v>
+        <v>-2.430093418882862</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.221838960340442</v>
+        <v>-2.236385435729161</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.181231602955215</v>
+        <v>-2.151701582765973</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.714145981441135</v>
+        <v>-2.693543231697262</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.107869884779689</v>
+        <v>-2.042395281793418</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.796913720102786</v>
+        <v>-2.730521668952839</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.824001475428553</v>
+        <v>-2.75726622351312</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.86044014636569</v>
+        <v>-1.793733777558188</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.7063627323237114</v>
+        <v>-0.6387366287832705</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.1805365750155943</v>
+        <v>-0.1132100964285669</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1243412915667648</v>
+        <v>-0.05667031295283209</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.4276134245646972</v>
+        <v>0.496613554809656</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6253680971849889</v>
+        <v>0.6946461620177118</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.3855483418023411</v>
+        <v>0.4556143480918067</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.5614969077690688</v>
+        <v>0.6308897863801448</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.2597586201582871</v>
+        <v>0.3293280559408132</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.8253535779104482</v>
+        <v>0.895065725967072</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.041476740842263</v>
+        <v>1.110957106891398</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.6417644593461844</v>
+        <v>0.7110468397429131</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.4338532372719541</v>
+        <v>0.5037898587006069</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.5255427750912034</v>
+        <v>0.5955884907533644</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.7164956448424036</v>
+        <v>0.7862409065044886</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.6405543055739358</v>
+        <v>0.7104086532812133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.0003636</t>
+          <t>X &lt; 0.0003613</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1339</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.733822898288103</v>
+        <v>-1.780728065812923</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.702351438692361</v>
+        <v>-2.747031208877843</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.499034725780739</v>
+        <v>-2.507532677653302</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.466002049429456</v>
+        <v>-2.435321812470278</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.428732626089051</v>
+        <v>-3.402685960265472</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.017520216218941</v>
+        <v>-2.95204561323267</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.641021150364075</v>
+        <v>-3.574629099214128</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.620845400064866</v>
+        <v>-3.554110148149434</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.757820746543345</v>
+        <v>-2.691114377735843</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.0380041782239</v>
+        <v>-1.97037807468346</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.614279713199686</v>
+        <v>-1.546953234612658</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.445278022947932</v>
+        <v>-1.377607044333999</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.150799861300634</v>
+        <v>-1.081799731055675</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.9987436775627714</v>
+        <v>-0.9294656127300485</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.8361663281012</v>
+        <v>-0.7661003218117344</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.4651540753431433</v>
+        <v>-0.3957611967320673</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.6739303684465128</v>
+        <v>-0.6043609326639867</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.1067703939518054</v>
+        <v>-0.03705824589518159</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.7814961595700041</v>
+        <v>0.8509765256191386</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.6698095593726663</v>
+        <v>0.7390919397693949</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.7240699420102672</v>
+        <v>0.79400656343892</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.9468452821854285</v>
+        <v>1.01689099784759</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.072255250758666</v>
+        <v>1.142000512420751</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.14567910939909</v>
+        <v>1.215533457106368</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.002642</t>
+          <t>X &lt; 0.002639</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1564</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.183699949812102</v>
+        <v>-1.220464947826869</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.060415131257741</v>
+        <v>-2.095445454165457</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.996311962486374</v>
+        <v>-2.033540919996447</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.814964610717901</v>
+        <v>-1.819002851346774</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.563866109296931</v>
+        <v>-2.567112867873035</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.057008401660987</v>
+        <v>-2.026219988750135</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.382304201234199</v>
+        <v>-2.315912150084252</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.405104371049433</v>
+        <v>-2.338369119134001</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.107833830323479</v>
+        <v>-2.041127461515977</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.794712719353775</v>
+        <v>-1.727086615813334</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.840046546867597</v>
+        <v>-1.77272006828057</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.79944735571334</v>
+        <v>-1.731776377099408</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.581227576758025</v>
+        <v>-1.512227446513066</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.355014055311564</v>
+        <v>-1.285735990478841</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.9269887726097323</v>
+        <v>-0.8569227663202668</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.07617424728503153</v>
+        <v>-0.006781368673955512</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.1733637721210357</v>
+        <v>0.2429332079035618</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.8995824020615615</v>
+        <v>0.9692945501181853</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.435398659622535</v>
+        <v>1.50487902567167</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.238810741687978</v>
+        <v>1.308093122084706</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.079242046245014</v>
+        <v>1.149178667673667</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.322980085231563</v>
+        <v>1.393025800893724</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.469878013862022</v>
+        <v>1.539623275524107</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.457875293519393</v>
+        <v>1.527729641226671</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.004921</t>
+          <t>X &lt; 0.004918</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1830</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.137296528500386</v>
+        <v>-1.163982660519615</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.098816571050143</v>
+        <v>-2.123772059929934</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.363251890215835</v>
+        <v>-2.389119800049833</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.337654085652552</v>
+        <v>-2.364328714170455</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.085437531878789</v>
+        <v>-3.107231969987737</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.406469640183488</v>
+        <v>-2.399875415177021</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.687532493548986</v>
+        <v>-2.65086530832378</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.528928669122195</v>
+        <v>-2.462193417206763</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.050254134154201</v>
+        <v>-1.9835477653467</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.004417413776089</v>
+        <v>-1.936791310235648</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.057926999119765</v>
+        <v>-1.990600520532738</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.118441667621994</v>
+        <v>-2.050770689008061</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.150036711245754</v>
+        <v>-2.081036581000795</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.043524669821082</v>
+        <v>-1.974246604988359</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.882783777710841</v>
+        <v>-1.812717771421376</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.50630296306214</v>
+        <v>-1.436910084451064</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.367172613495221</v>
+        <v>-1.297603177712695</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.7617735159292991</v>
+        <v>-0.6920613678726752</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.5456503529974839</v>
+        <v>-0.4761699869483493</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.7957650273224033</v>
+        <v>-0.7264826469256747</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.9564517751181683</v>
+        <v>-0.8865151536895155</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.7591827870449279</v>
+        <v>-0.6891370713827669</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.9762108992513348</v>
+        <v>-0.9064656375892497</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.8335730035471158</v>
+        <v>-0.7637186558398383</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.007199</t>
+          <t>X &lt; 0.007196</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.388407120036504</v>
+        <v>-1.382169034497117</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.127448421109747</v>
+        <v>-2.120248079241343</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.493801960267717</v>
+        <v>-2.486465426305401</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.037850306639605</v>
+        <v>-2.031358885017418</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.520426894912198</v>
+        <v>-2.531944384675114</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.094712663584808</v>
+        <v>-2.128614784341259</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.19963986434113</v>
+        <v>-2.207121977300574</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.239644891539072</v>
+        <v>-2.220619563287762</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.864159360867589</v>
+        <v>-1.81870041868472</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.017765764003428</v>
+        <v>-1.971091035055345</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.791116420552214</v>
+        <v>-1.744764089790799</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.831660705706511</v>
+        <v>-1.784850008751917</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.858823679918842</v>
+        <v>-1.81016004696842</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.8893407962967</v>
+        <v>-1.840308135825509</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.498653714723325</v>
+        <v>-1.44833210166383</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.237563130750793</v>
+        <v>-1.188074058002464</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.371656824899716</v>
+        <v>-1.321991194979937</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.094960851682018</v>
+        <v>-1.044970323622117</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.117387307070814</v>
+        <v>-1.067742427184662</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.216603053435115</v>
+        <v>-1.167292798600883</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.282704225791854</v>
+        <v>-1.232511997593171</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.215529510442089</v>
+        <v>-1.165159868310148</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.560983351593549</v>
+        <v>-1.511210215493961</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.398375072541405</v>
+        <v>-1.348378984230372</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.009478</t>
+          <t>X &lt; 0.009474</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2337</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.54283410822309</v>
+        <v>-1.555740730453245</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.367505875619003</v>
+        <v>-2.379199901564668</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.590635609737234</v>
+        <v>-2.602740064731002</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.300221342147317</v>
+        <v>-2.313218198832416</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.685191140256109</v>
+        <v>-2.711321809154022</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.432309795364468</v>
+        <v>-2.458790136641447</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.284702172685869</v>
+        <v>-2.31187507004968</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.497062265049649</v>
+        <v>-2.524044903671495</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.303751822618025</v>
+        <v>-2.331062616508426</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.454974033233569</v>
+        <v>-2.482469094938367</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.223404667701459</v>
+        <v>-2.22739469175314</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.031809653760867</v>
+        <v>-2.012105807233823</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.958183627917677</v>
+        <v>-1.913689775782188</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.751641423119764</v>
+        <v>-1.682363358287041</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.554774630492538</v>
+        <v>-1.484708624203073</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.473193399869878</v>
+        <v>-1.403800521258802</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.564497192435567</v>
+        <v>-1.494927756653041</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.369951297448267</v>
+        <v>-1.300239149391643</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.367777642432586</v>
+        <v>-1.298297276383451</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.65142276422764</v>
+        <v>-1.582140383830911</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.552774649477207</v>
+        <v>-1.482838028048555</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.714309508286263</v>
+        <v>-1.644263792624102</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.867433357636401</v>
+        <v>-1.797688095974316</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.815004992155188</v>
+        <v>-1.745150644447911</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.01176</t>
+          <t>X &lt; 0.01175</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.475047331676727</v>
+        <v>-1.463583144260483</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.481315446060897</v>
+        <v>-1.508391837764812</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.626603562087439</v>
+        <v>-1.653519551634211</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.353984208682526</v>
+        <v>-1.38122660988514</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.659436062296606</v>
+        <v>-1.695888031729844</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.644336148006332</v>
+        <v>-1.680826672110818</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.351967724870221</v>
+        <v>-1.388814523790046</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.647635796200433</v>
+        <v>-1.68415944789907</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.661946093077546</v>
+        <v>-1.698473803693119</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.910930998818259</v>
+        <v>-1.947187770367762</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.692259684842284</v>
+        <v>-1.728791639958594</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.407169931966521</v>
+        <v>-1.444052591933165</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.463164173439168</v>
+        <v>-1.49999915470147</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.351915052843268</v>
+        <v>-1.388899540612464</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.328874490636949</v>
+        <v>-1.365904891252505</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.044132517043501</v>
+        <v>-1.058844256518675</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.294595489702893</v>
+        <v>-1.286436906209147</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.205630108280722</v>
+        <v>-1.174707719727586</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.261035261873346</v>
+        <v>-1.207736110983795</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.461889061287827</v>
+        <v>-1.408938418982395</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.306873799222934</v>
+        <v>-1.252997974608498</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.421618614369038</v>
+        <v>-1.367648747814265</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.57353080242531</v>
+        <v>-1.520026965095497</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.533102863183302</v>
+        <v>-1.479444782928788</v>
       </c>
     </row>
     <row r="26">
@@ -7468,79 +7468,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.200304143201137</v>
+        <v>-1.223819696404547</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.22750501288067</v>
+        <v>-1.2509757703166</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.347081952605578</v>
+        <v>-1.370321661173783</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.101330104760457</v>
+        <v>-1.124791274224457</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.519018891378394</v>
+        <v>-1.549092655114926</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.348131759706149</v>
+        <v>-1.378420905303173</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.051510825488009</v>
+        <v>-1.082077108947161</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.345973417720458</v>
+        <v>-1.37621430674124</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.211720538779126</v>
+        <v>-1.242126051350198</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.530433094460335</v>
+        <v>-1.560448181182522</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.453031347135308</v>
+        <v>-1.483167481197178</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.240320593112465</v>
+        <v>-1.270681903563641</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.328580745209962</v>
+        <v>-1.358774761091077</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.238643912883418</v>
+        <v>-1.268934432406631</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.368269680143577</v>
+        <v>-1.39838410918891</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.042357822164249</v>
+        <v>-1.072888844923668</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.155203157422463</v>
+        <v>-1.185617009432065</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.005918502322679</v>
+        <v>-1.015169874016493</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.080387420756644</v>
+        <v>-1.068453044676595</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.147611696331275</v>
+        <v>-1.114653326105262</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.000655912085499</v>
+        <v>-0.9456475084995404</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.040286957557377</v>
+        <v>-0.9851562606063098</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.128751892782482</v>
+        <v>-1.074053641147508</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.132045211709496</v>
+        <v>-1.077211475766134</v>
       </c>
     </row>
     <row r="27">
@@ -7550,79 +7550,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9174019019603037</v>
+        <v>-0.9386095919173414</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.8552121220497213</v>
+        <v>-0.8420150963547783</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.8283077293088468</v>
+        <v>-0.8149519515120502</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7643774517275403</v>
+        <v>-0.7509939478640604</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.076024595879971</v>
+        <v>-1.102166839221262</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.042311126854258</v>
+        <v>-1.034041956360582</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.9673531619666988</v>
+        <v>-0.9590636380741984</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.295598167126094</v>
+        <v>-1.286934052353658</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.165589801315576</v>
+        <v>-1.157066253475556</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.470643597573805</v>
+        <v>-1.461706022067311</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.280428869740817</v>
+        <v>-1.271723995149799</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.917333272054826</v>
+        <v>-0.9435241151658147</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.018567730210705</v>
+        <v>-1.044522968909043</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9082404657457133</v>
+        <v>-0.9342946742807001</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.062127737264611</v>
+        <v>-1.087951065628197</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.8276246595307626</v>
+        <v>-0.8537800146796712</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.010674879948304</v>
+        <v>-1.036635913528031</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.8873524004933273</v>
+        <v>-0.9134409600801092</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.9831876431074278</v>
+        <v>-0.988926436152525</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.108102253032925</v>
+        <v>-1.093659407545054</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.9233997157570499</v>
+        <v>-0.8881251393890608</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.9300306812783461</v>
+        <v>-0.8741790971060084</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.036538010463467</v>
+        <v>-0.9811190864270074</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.112479349731935</v>
+        <v>-1.056951339650283</v>
       </c>
     </row>
     <row r="28">
@@ -7632,407 +7632,407 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6128969159548774</v>
+        <v>-0.6328257230576426</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7295111104888363</v>
+        <v>-0.7158445737677326</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.8791949070791887</v>
+        <v>-0.8985927935886977</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.9049206373931042</v>
+        <v>-0.9241881478701046</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.184676898108854</v>
+        <v>-1.174569514382441</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.012477639128676</v>
+        <v>-1.002572254318395</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.029283289040372</v>
+        <v>-1.019238671292342</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.255495721710943</v>
+        <v>-1.245179385298577</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.128056536619354</v>
+        <v>-1.117874374292036</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.278998409118444</v>
+        <v>-1.268541904220875</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.153398578866522</v>
+        <v>-1.143111213103467</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8426009853142133</v>
+        <v>-0.8661276950371359</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.9737140480593141</v>
+        <v>-0.9633852075456986</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8058638201824522</v>
+        <v>-0.7956686907361359</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.9072591416269091</v>
+        <v>-0.8968575652464068</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.729405920937495</v>
+        <v>-0.7192770839059079</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.8773544136308615</v>
+        <v>-0.8670549668894907</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.7270229477850805</v>
+        <v>-0.7168581718401583</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.7939522439543296</v>
+        <v>-0.817378493458321</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.9574915824915848</v>
+        <v>-0.9807933007334384</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.8946313854289301</v>
+        <v>-0.8980619033162753</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.9369164074015117</v>
+        <v>-0.9204072918932411</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.9988415776197144</v>
+        <v>-0.9627663496276639</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.04111288321814</v>
+        <v>-0.9851506848021501</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.02087</t>
+          <t>X &lt; 0.02086</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6946358961448027</v>
+        <v>-0.7130657211092668</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6868213503625569</v>
+        <v>-0.7052041265556142</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7406233212684867</v>
+        <v>-0.7586950441461084</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7520996937630784</v>
+        <v>-0.7700355995977475</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.9362769809051841</v>
+        <v>-0.9575014593174416</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.8940596009376023</v>
+        <v>-0.9153691324597233</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.8984275808647908</v>
+        <v>-0.9195994160455641</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.9954498065331947</v>
+        <v>-1.016484558048532</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.8375782511936336</v>
+        <v>-0.8587843634667465</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.9724478806661878</v>
+        <v>-0.9933883560285324</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.8754319039421148</v>
+        <v>-0.8965272708073897</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.645710498651674</v>
+        <v>-0.6669885831758862</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6726261499172637</v>
+        <v>-0.6936794837787161</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5478151271720435</v>
+        <v>-0.5689592154249681</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.6313693941675709</v>
+        <v>-0.6523191857576052</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.4422312095645893</v>
+        <v>-0.4634857895727436</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.5569805964667864</v>
+        <v>-0.5781072394409534</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.4788873252844041</v>
+        <v>-0.5000805874010865</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.5053782207760165</v>
+        <v>-0.5265948431838652</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.5938728702490153</v>
+        <v>-0.6150465885067078</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.5278365938553762</v>
+        <v>-0.5489841543014577</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.5515325138208951</v>
+        <v>-0.5726521662728672</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.604626199797778</v>
+        <v>-0.6063847088423557</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.6149937685744433</v>
+        <v>-0.5973125863436763</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.02315</t>
+          <t>X &lt; 0.02314</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3099</v>
+        <v>3102</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.7103277498712757</v>
+        <v>-0.7128471134319696</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6439123050105096</v>
+        <v>-0.6465586108854993</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6878559930096344</v>
+        <v>-0.6906202262626664</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.742649581574355</v>
+        <v>-0.7454310609729973</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9297287534716432</v>
+        <v>-0.9353127972436681</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.9172758440177446</v>
+        <v>-0.9228571641413055</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.9339867208468249</v>
+        <v>-0.9396431150715543</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.937596030693939</v>
+        <v>-0.9432850515387017</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.7173280477090316</v>
+        <v>-0.7232985766038453</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.8945588721884405</v>
+        <v>-0.9003988496760087</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.7946675969982664</v>
+        <v>-0.8006067481112709</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5731005329076027</v>
+        <v>-0.5793618215980558</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5854797314216142</v>
+        <v>-0.5918646087146442</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6592598429333094</v>
+        <v>-0.6655806968871687</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.5911824051711321</v>
+        <v>-0.5976743770144424</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.4920840530730146</v>
+        <v>-0.4986358764493772</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.6071609981735548</v>
+        <v>-0.6135851584595855</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.5642494327790502</v>
+        <v>-0.5707456727864866</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.5868584910764483</v>
+        <v>-0.5933036934914782</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.767649903288202</v>
+        <v>-0.7738438269438959</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.6792452332481886</v>
+        <v>-0.6856228857979687</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.6715748194792681</v>
+        <v>-0.6779757283598471</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.7003418986747292</v>
+        <v>-0.7066766091679568</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.776283237943197</v>
+        <v>-0.7635072639298102</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.02543</t>
+          <t>X &lt; 0.02542</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3150</v>
+        <v>3154</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.6328355563968699</v>
+        <v>-0.6348666286979423</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.5729791398150468</v>
+        <v>-0.5751201334442513</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5451815535131104</v>
+        <v>-0.5475012285293062</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5161030005135387</v>
+        <v>-0.5185314478043495</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.7375903028309949</v>
+        <v>-0.7422487827744249</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6275120313078446</v>
+        <v>-0.6322939022665679</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.6249713481303019</v>
+        <v>-0.6298360496181488</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.7593412840299081</v>
+        <v>-0.7640671997652362</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.6367405506460528</v>
+        <v>-0.6416202468831642</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.7289343495218148</v>
+        <v>-0.7337775662383024</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.847431325958965</v>
+        <v>-0.8521008630333569</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.728991122729262</v>
+        <v>-0.7338411542311079</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.7280788677881773</v>
+        <v>-0.7330449719572059</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.7726870133225034</v>
+        <v>-0.7776220099886118</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.7799238770367367</v>
+        <v>-0.7849185422880822</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.6410531161991173</v>
+        <v>-0.6461675579322588</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.756490479422439</v>
+        <v>-0.7614755429287925</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.6526916733811419</v>
+        <v>-0.6578218991032116</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.6080025911830305</v>
+        <v>-0.6131712168457497</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.7193246670894027</v>
+        <v>-0.7243369989572983</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.6730370724930381</v>
+        <v>-0.6781655930808625</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.7619219621024982</v>
+        <v>-0.7669487857337884</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.8174444047912459</v>
+        <v>-0.8223767163695612</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.7794486215538896</v>
+        <v>-0.7844400227570389</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.02771</t>
+          <t>X &lt; 0.0277</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3205</v>
+        <v>3209</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.5762279732848725</v>
+        <v>-0.5777283015507706</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.5230868181329598</v>
+        <v>-0.524679931589894</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.613287527072707</v>
+        <v>-0.6148813509056552</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5658914728682092</v>
+        <v>-0.5676003868829582</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7898470831947435</v>
+        <v>-0.793242471390144</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.6784695588011971</v>
+        <v>-0.6819908359647755</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.6581443729437169</v>
+        <v>-0.6617530876075364</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.7328941076802877</v>
+        <v>-0.7364341085271278</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.6427260480801422</v>
+        <v>-0.6463770918460341</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.8086993667296127</v>
+        <v>-0.8122069108792545</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.8894314804016261</v>
+        <v>-0.8928198934911933</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.7467159821838152</v>
+        <v>-0.7503056737309208</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.702866822982152</v>
+        <v>-0.7066008480476</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.8438034178345859</v>
+        <v>-0.8473820355008428</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.862214614793146</v>
+        <v>-0.8658241029513363</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.7155604365433348</v>
+        <v>-0.7193084089260608</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.8002072037272043</v>
+        <v>-0.8038628628933466</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.7311411099069645</v>
+        <v>-0.7348933797024699</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.6212338267730786</v>
+        <v>-0.6251085446926439</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.727446244936111</v>
+        <v>-0.7311766921211742</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.6912677406687777</v>
+        <v>-0.6950881960375455</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.7799365684759252</v>
+        <v>-0.783655061965014</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.7050322008409111</v>
+        <v>-0.7088250676489949</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.6689565828247197</v>
+        <v>-0.6728029082923896</v>
       </c>
     </row>
     <row r="33">
@@ -8042,79 +8042,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3246</v>
+        <v>3250</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.5080155629854204</v>
+        <v>-0.5091636426100905</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4597253169679547</v>
+        <v>-0.4609539851314111</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.5668425023263737</v>
+        <v>-0.5680299984159589</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.4983693872028923</v>
+        <v>-0.4996856652708104</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.7853346021471594</v>
+        <v>-0.7878692515179893</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.7342782226328595</v>
+        <v>-0.7368655751509365</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.5707034666552957</v>
+        <v>-0.5735407494938229</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.6173319752838893</v>
+        <v>-0.620131303493352</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.5277401713247372</v>
+        <v>-0.5306485779058008</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.7013231095754762</v>
+        <v>-0.7040687130000336</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.8082392910997811</v>
+        <v>-0.8108386935238343</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.6708070934590253</v>
+        <v>-0.6735941939817067</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.7030482156809228</v>
+        <v>-0.7058675440464199</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.783572467245925</v>
+        <v>-0.7863086922189169</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.8100331544578481</v>
+        <v>-0.812779810633522</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.7806387112459703</v>
+        <v>-0.7833863496846973</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.8659287007723719</v>
+        <v>-0.8685818684183744</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.8298274751574155</v>
+        <v>-0.8325334345742448</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.7186110057096329</v>
+        <v>-0.7214420778047881</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.7903846153846175</v>
+        <v>-0.7931177425289064</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.7307581190625854</v>
+        <v>-0.733600399927127</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.8500667946898304</v>
+        <v>-0.8527690355712636</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.8034579082600644</v>
+        <v>-0.8062022465855492</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.7380203435267134</v>
+        <v>-0.7408519051042433</v>
       </c>
     </row>
     <row r="34">
@@ -8124,161 +8124,161 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3271</v>
+        <v>3275</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.4561493353197079</v>
+        <v>-0.4570993875374825</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3500196656122441</v>
+        <v>-0.351116784089939</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.4672233869113853</v>
+        <v>-0.4682546112982067</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.4046624691724361</v>
+        <v>-0.4058079059004314</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.6617990845221797</v>
+        <v>-0.6639660806109191</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.6096705732489909</v>
+        <v>-0.6118925694688429</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.5140053107481322</v>
+        <v>-0.5163857464645289</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.5015347792995541</v>
+        <v>-0.503946633878158</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4122734976402924</v>
+        <v>-0.4147933015800263</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4990652167553549</v>
+        <v>-0.5015218992000143</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.6030172861880487</v>
+        <v>-0.6053346755325464</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.5600742541041086</v>
+        <v>-0.5624602227067967</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5396631885037166</v>
+        <v>-0.5421349981971062</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.5907322218302582</v>
+        <v>-0.5931552059315521</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.5914669711001537</v>
+        <v>-0.593925548156399</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.5881901837761703</v>
+        <v>-0.590622952030202</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.7348064832745465</v>
+        <v>-0.7370693169120983</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.7607730006639386</v>
+        <v>-0.7630113481365868</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.5876848212614547</v>
+        <v>-0.5901244051810579</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.6879770992366332</v>
+        <v>-0.6902860855989985</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.6023787840743182</v>
+        <v>-0.6048226649335504</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.7213170900606656</v>
+        <v>-0.723621497528903</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.7034878776205389</v>
+        <v>-0.705801092662405</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.6696719890013441</v>
+        <v>-0.6720321752158114</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.03454</t>
+          <t>X &lt; 0.03453</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3303</v>
+        <v>3307</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.3367792530147753</v>
+        <v>-0.3375438101286576</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2047856421996315</v>
+        <v>-0.2057230406493105</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2444245806304792</v>
+        <v>-0.2453737300435463</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2494593705603592</v>
+        <v>-0.2504322673009014</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4774885380867815</v>
+        <v>-0.4792244942940727</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.5143376041090164</v>
+        <v>-0.5160227704648079</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4571354957216087</v>
+        <v>-0.4589222971661471</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.5077128509400737</v>
+        <v>-0.509451392339507</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3586366280523663</v>
+        <v>-0.3605541773113075</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.4520402739878477</v>
+        <v>-0.4538783025991933</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3713864967039342</v>
+        <v>-0.3733116930918285</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3314822432469526</v>
+        <v>-0.3334682557581985</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2617073517805295</v>
+        <v>-0.2638249484747774</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3747055287985575</v>
+        <v>-0.3766973019279618</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.3515412022772537</v>
+        <v>-0.3535893198667424</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3726748679395797</v>
+        <v>-0.3746743452625765</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.4586820318829581</v>
+        <v>-0.4605845351596614</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.5155498536867285</v>
+        <v>-0.5173893109483885</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.3419712442298675</v>
+        <v>-0.3440127049336184</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.469647716964019</v>
+        <v>-0.4715285528560571</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4203177713694046</v>
+        <v>-0.4222819144575212</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.5085276280293627</v>
+        <v>-0.5103895918312276</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4578790875046792</v>
+        <v>-0.4597922311759106</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.4553276925283285</v>
+        <v>-0.4572483601762301</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/ma/ma_cross_10_50.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/ma/ma_cross_10_50.xlsx
@@ -618,739 +618,739 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.03039</t>
+          <t>X ≈ -0.03037</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.2025730435486466</v>
+        <v>-5.357767007263462</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.691158387635518</v>
+        <v>-1.923384073952676</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.083923345154474</v>
+        <v>0.5092713224168079</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.376283239906499</v>
+        <v>-0.08037356526035211</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.868963897790977</v>
+        <v>3.329435706670296</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.057333405432914</v>
+        <v>7.169776553829287</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.29190436324135</v>
+        <v>6.380754027716506</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.3624742972535344</v>
+        <v>-1.292861786884131</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.253133364021856</v>
+        <v>-4.852589791948766</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.025089050958442</v>
+        <v>-5.646869182794973</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.753945338786544</v>
+        <v>-9.066141428259115</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-11.86644391898818</v>
+        <v>-9.344651688851329</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-9.155959020369352</v>
+        <v>-6.767316217977417</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.710028535356322</v>
+        <v>0.3683362732749131</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1.469212137588286</v>
+        <v>3.382174912856463</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.899546548278209</v>
+        <v>7.637878547865057</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>1.929940391503301</v>
+        <v>3.840544697663972</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-2.013356229358131</v>
+        <v>0.01187430807346601</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-5.638525189119427</v>
+        <v>-3.472074687106527</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-5.453673942773818</v>
+        <v>-3.258975593880741</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-5.997150650344466</v>
+        <v>-3.826803725885974</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-6.074711430435038</v>
+        <v>-3.903177203800034</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-1.956935532216548</v>
+        <v>0.04184508477872839</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-2.033159597411938</v>
+        <v>-0.1202710393771866</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02812</t>
+          <t>X ≈ -0.0281</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.222591322715388</v>
+        <v>7.515303728697255</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-11.79135893250025</v>
+        <v>-9.28100403024844</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-7.995751468087263</v>
+        <v>-5.01087100634625</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.707602294850957</v>
+        <v>-5.602141937734899</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-6.427086559132668</v>
+        <v>-3.114937740547404</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.626326898640613</v>
+        <v>-2.960362795487114</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.777662651546315</v>
+        <v>-0.9889501964676768</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.5638261244434233</v>
+        <v>1.471494384559122</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.013599126146936</v>
+        <v>-3.930474420985163</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-10.64472908554292</v>
+        <v>-13.02222473668931</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-23.47980739153338</v>
+        <v>-23.82156841982992</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-21.14304161346315</v>
+        <v>-24.10461432379762</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-22.26880562730092</v>
+        <v>-25.22327966463853</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-22.49606474755571</v>
+        <v>-25.47851954211785</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-23.15889794648356</v>
+        <v>-26.16624829115389</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-22.57302931248959</v>
+        <v>-25.61440249632336</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-20.08740943159547</v>
+        <v>-22.95406460082683</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-20.1982800011444</v>
+        <v>-23.09385047856038</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-19.98871436002793</v>
+        <v>-22.88671135726319</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-22.43665903839881</v>
+        <v>-25.45395643201192</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-25.6145328704139</v>
+        <v>-28.80380747057058</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-17.80830183283672</v>
+        <v>-20.55960601290013</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-17.53916745241995</v>
+        <v>-20.32229434966251</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-14.98862518445647</v>
+        <v>-17.71286363197125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.02584</t>
+          <t>X ≈ -0.02583</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>42</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.980567819803859</v>
+        <v>-5.88252480821734</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.7808501646591353</v>
+        <v>0.9680869860931196</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.014661953139999</v>
+        <v>-2.644540177773408</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.007397958311898</v>
+        <v>1.497509695396467</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.6745003308604751</v>
+        <v>1.225027401415701</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.595437587309235</v>
+        <v>6.116365833374182</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>14.30251530810022</v>
+        <v>14.80097456385923</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>11.66110607286231</v>
+        <v>12.13272026701344</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.336904155678369</v>
+        <v>9.894568918643053</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.94115631478438</v>
+        <v>11.47598102566235</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>13.59000335184275</v>
+        <v>14.12306480760306</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.572036280891808</v>
+        <v>9.107324550102561</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.828257165423373</v>
+        <v>10.37168979573328</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.49022785800063</v>
+        <v>3.006496696049673</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>4.20933848210209</v>
+        <v>4.701767204061731</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>4.803523343394787</v>
+        <v>5.262929719371812</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.07997403103988887</v>
+        <v>0.4091333186985509</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-2.561254181282422</v>
+        <v>-2.100122707949403</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-9.478062447730416</v>
+        <v>-9.018466290871736</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-6.916532395808808</v>
+        <v>-6.429174045111218</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-7.460540922006565</v>
+        <v>-6.998048047352832</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.538765528225518</v>
+        <v>-7.075599124843301</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-2.50613975099477</v>
+        <v>-2.073832677387657</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>2.179294615041741</v>
+        <v>2.525231606125168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.02356</t>
+          <t>X ≈ -0.02355</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.963429125809604</v>
+        <v>4.632243589790633</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7.376132972510646</v>
+        <v>8.837760846412387</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.948593063378212</v>
+        <v>4.628264690342782</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.240840235043265</v>
+        <v>1.073420122661879</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.165524131543648</v>
+        <v>0.8009098795493301</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.584774303221934</v>
+        <v>3.924408208539809</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.818805097431714</v>
+        <v>6.103077252559963</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.308288222606024</v>
+        <v>4.316626332242954</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.097306313793538</v>
+        <v>4.446223420825355</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.32938350342944</v>
+        <v>5.14130340661238</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.098801511416504</v>
+        <v>8.387826723024247</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.823287986706276</v>
+        <v>9.601833120182391</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.70625422542664</v>
+        <v>9.980963840047245</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.739117798470517</v>
+        <v>9.736855587866209</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.4144041466016049</v>
+        <v>6.083346596090898</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-3.321558972494849</v>
+        <v>3.66740630408686</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-8.707387290760607</v>
+        <v>-0.902817046586847</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-12.31693578843252</v>
+        <v>-4.015306834728371</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-13.8566074102603</v>
+        <v>-5.29251870074301</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-15.42674916587356</v>
+        <v>-6.570854932445556</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-17.72622145563182</v>
+        <v>-8.630944263473594</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-16.05451335132416</v>
+        <v>-7.217501312376086</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-15.78510408769255</v>
+        <v>-6.976307738405175</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-14.11143220199993</v>
+        <v>-5.648187015055875</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.02128</t>
+          <t>X ≈ -0.02127</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.327352473714384</v>
+        <v>-6.719632647989606</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5247036513332475</v>
+        <v>-3.76181391880769</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.66688320987393</v>
+        <v>-5.009128642384447</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.76156860642147</v>
+        <v>0.8100092886973513</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-6.425339724515176</v>
+        <v>-5.874733108913439</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-14.81365878686626</v>
+        <v>-12.13630209975596</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-8.728178483285355</v>
+        <v>-8.119744070298921</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.291630249089586</v>
+        <v>-6.82082833124803</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-10.68345790054283</v>
+        <v>-9.904998864847684</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.590557473478917</v>
+        <v>-4.27783127799367</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.601340504893635</v>
+        <v>-2.40121966566516</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.597324549660641</v>
+        <v>-4.284218676189766</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.435832483547856</v>
+        <v>-7.003943737933682</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-7.658185070494447</v>
+        <v>-7.253347348396346</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-3.158950290025004</v>
+        <v>-1.502413017588346</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.567023958767443</v>
+        <v>0.6656601399677626</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-7.861651434906335</v>
+        <v>-4.265345342425348</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-4.527227553119971</v>
+        <v>-1.179819769460209</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.8701768368878504</v>
+        <v>2.254656785811186</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-2.406003809640602</v>
+        <v>0.8585276592356408</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-2.948673342830652</v>
+        <v>0.2919233516598041</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-4.748705155358714</v>
+        <v>-1.395354474854436</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-7.92298103224195</v>
+        <v>-4.377148412623619</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-6.277191427650664</v>
+        <v>-2.92791739541147</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.019</t>
+          <t>X ≈ -0.01899</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.01401858241875</v>
+        <v>-2.0565515288</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.8557918133494553</v>
+        <v>0.6192771490286404</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.028879986939501</v>
+        <v>0.8341762533057562</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.126140463708843</v>
+        <v>4.627054313809971</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.795948875966104</v>
+        <v>4.356770004401945</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.776070518734642</v>
+        <v>1.589670261146715</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.007464201831681</v>
+        <v>0.7978748128658708</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.7317812350365358</v>
+        <v>0.4949038630115723</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.194209049585112</v>
+        <v>6.476998915493674</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>9.637950717040454</v>
+        <v>8.614051105230544</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>8.308741072965667</v>
+        <v>7.424222147230836</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>8.0339466131107</v>
+        <v>7.151270001175149</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>6.917837170917288</v>
+        <v>6.042718786879483</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>8.307752276532426</v>
+        <v>7.263307406049229</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6.046473699388521</v>
+        <v>5.119495608289007</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>9.858633824440645</v>
+        <v>8.614260940934301</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>16.16575059177099</v>
+        <v>14.38271305781993</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>16.06629983393726</v>
+        <v>17.18999885000252</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>19.50776522397567</v>
+        <v>20.3461209656035</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>18.08981391452254</v>
+        <v>19.09817778214719</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>15.94260578174798</v>
+        <v>17.06849204667402</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>11.03630185013413</v>
+        <v>14.05938622280262</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>9.701991226733995</v>
+        <v>11.36724512230713</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>8.016468194151336</v>
+        <v>11.20870499548069</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01673</t>
+          <t>X ≈ -0.01672</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.08867390590761914</v>
+        <v>0.7375783116518875</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.645376797741442</v>
+        <v>9.002144743305564</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.701485756315698</v>
+        <v>7.759585782261397</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.511376187887222</v>
+        <v>5.752435623245816</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.66490110810291</v>
+        <v>6.902230570750589</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>10.82011195673982</v>
+        <v>9.900041174176785</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11.53869731522418</v>
+        <v>10.5316014966894</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>11.26666635205231</v>
+        <v>10.23199281802572</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>11.31225661860958</v>
+        <v>10.36336996796644</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>10.54638136758723</v>
+        <v>9.574028329974723</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>9.337735094471064</v>
+        <v>8.426751207966191</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>10.54996388068055</v>
+        <v>9.577106466745207</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>12.40902003063251</v>
+        <v>11.31622750678877</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>10.70572894005186</v>
+        <v>9.649115356944186</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>11.54170111012954</v>
+        <v>10.39689106134288</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>9.161241872379875</v>
+        <v>8.110391079888913</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>12.00931148518615</v>
+        <v>10.86013674854343</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>11.90869260852982</v>
+        <v>10.73096295897508</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>9.148347417415842</v>
+        <v>8.096390332680485</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>9.337975003142901</v>
+        <v>8.313291207724944</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>5.817388644295256</v>
+        <v>4.895202998767459</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>4.251933287673602</v>
+        <v>3.393906431079778</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>6.019899376163437</v>
+        <v>5.06668555893706</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.02397475240619684</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01445</t>
+          <t>X ≈ -0.01444</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-5.086250274960221</v>
+        <v>-4.46807325269932</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.439304359803735</v>
+        <v>-2.806515451742634</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.937805384751513</v>
+        <v>-0.2343761912709184</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3010835618688645</v>
+        <v>1.084862298576404</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.013969227389836</v>
+        <v>-0.1414705552125355</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.154757046998121</v>
+        <v>0.9691752343720879</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.614192739526608</v>
+        <v>0.1773936499077209</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.048238873888586</v>
+        <v>3.699219757028835</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.091206671181638</v>
+        <v>3.8285297364963</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.293417582532015</v>
+        <v>4.951010088853948</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10.48261791517744</v>
+        <v>10.96784683479697</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>10.20886217658308</v>
+        <v>10.69639718028365</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>11.0666108384411</v>
+        <v>11.5052378578766</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>9.864141800329278</v>
+        <v>10.30418322021882</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>13.16001905407679</v>
+        <v>13.46225545971019</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>12.77012792473553</v>
+        <v>13.06770129556057</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>13.629178941891</v>
+        <v>13.92799722333749</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>13.52937387879776</v>
+        <v>13.80012139091463</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>8.808128564449952</v>
+        <v>9.219975782016661</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>9.986514853585433</v>
+        <v>10.39760369587161</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>10.43757110813502</v>
+        <v>9.834784213875253</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>11.35480343946509</v>
+        <v>10.72380175962522</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>6.684534569646871</v>
+        <v>7.126303918023687</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>7.601265383547705</v>
+        <v>8.889700470593489</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.01217</t>
+          <t>X ≈ -0.01216</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-9.785971398503371</v>
+        <v>-9.563050268275333</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-14.68504735156834</v>
+        <v>-13.82235987722098</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-18.16548077117246</v>
+        <v>-17.09115075271675</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-17.8591579231592</v>
+        <v>-16.68722691611118</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-19.22052507700547</v>
+        <v>-18.97802627988123</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-15.96989427972415</v>
+        <v>-15.81490276341868</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-10.5967516628642</v>
+        <v>-10.59214454013367</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.702001867165627</v>
+        <v>-3.869163213423967</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5853020540744964</v>
+        <v>-0.7273375500551538</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.354979707086912</v>
+        <v>-1.526929429152723</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.160648373344294</v>
+        <v>-4.270486509863161</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-6.492258429680234</v>
+        <v>-6.562349597585822</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.559154730659905</v>
+        <v>-5.673351257552682</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.726072469200155</v>
+        <v>-3.91250363593565</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-5.410655884210342</v>
+        <v>-5.60795417727018</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-4.819605545108303</v>
+        <v>-5.043889570793823</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-4.954301748209048</v>
+        <v>-5.150365285193992</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-5.060467181582503</v>
+        <v>-5.285359764660889</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.758752783419148</v>
+        <v>-2.047138640502439</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-8.778800774811501</v>
+        <v>-9.902207578098583</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-7.263694923750151</v>
+        <v>-7.453665405622544</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-9.402404037606637</v>
+        <v>-10.55952037941353</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-6.039416706215718</v>
+        <v>-6.278690571529246</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-6.117219867039211</v>
+        <v>-5.844176763283748</v>
       </c>
     </row>
     <row r="15">
@@ -1363,1634 +1363,1634 @@
         <v>115</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.918416706241899</v>
+        <v>-0.9575135227936613</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.116094691103989</v>
+        <v>-2.067189296355657</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.487499138127404</v>
+        <v>-0.7347808187300018</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.651178902165398</v>
+        <v>-3.919072612002033</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.983963397546574</v>
+        <v>-4.197824126726886</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.075179092340477</v>
+        <v>-3.177197036270677</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-9.166890847675774</v>
+        <v>-8.297794103845405</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-9.448160463465733</v>
+        <v>-8.605603094130089</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7.681039402514976</v>
+        <v>-6.749642897158353</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-7.588143256311959</v>
+        <v>-6.685182344174983</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-8.182775531524705</v>
+        <v>-7.28029896578682</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.865732533420797</v>
+        <v>-4.962425892505927</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.120189847873377</v>
+        <v>-5.217847961062134</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-7.208309207543849</v>
+        <v>-6.336743363835133</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-4.39995478071323</v>
+        <v>-3.556546771849689</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-5.542674247049632</v>
+        <v>-4.727592119127515</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-5.677705505118148</v>
+        <v>-4.833970130614063</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.313864337470037</v>
+        <v>-2.364182612661423</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.966539914015449</v>
+        <v>-3.018617318799166</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-4.517184908517279</v>
+        <v>-4.54245349670601</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-5.928904287790928</v>
+        <v>-5.987897576721871</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-8.613616314805725</v>
+        <v>-7.804373158379441</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-6.603814374049151</v>
+        <v>-6.173913043478251</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-5.812423811458757</v>
+        <v>-6.336052037767715</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.007612</t>
+          <t>X ≈ -0.007613</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.472798909307805</v>
+        <v>2.884123653653845</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.41934059482692</v>
+        <v>1.925207203145739</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.138924565911147</v>
+        <v>2.813915191436649</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3916531711662898</v>
+        <v>0.7931272265726506</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.657487879438293</v>
+        <v>4.091405810512157</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.194660318150099</v>
+        <v>-0.7557190344999611</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.842906152094152</v>
+        <v>-4.413787059228738</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.842808504427524</v>
+        <v>-5.436136574054679</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.923090073491991</v>
+        <v>-2.445852488063807</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.693416980632698</v>
+        <v>-3.244623769278853</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1831521140987817</v>
+        <v>0.6098050421054708</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.699963761521822</v>
+        <v>-3.251677672807446</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.654999652333331</v>
+        <v>-2.220510476362648</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.01165145646462662</v>
+        <v>0.3984235019239506</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.810254133065875</v>
+        <v>-2.439604043595175</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-4.385536619680153</v>
+        <v>-4.030126435278895</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-5.965457966479271</v>
+        <v>-6.291095154697643</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.458114741976821</v>
+        <v>-2.833263709846435</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.7965239696138795</v>
+        <v>-1.181966268514032</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.1137026458299459</v>
+        <v>-0.2487780067868641</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.875148482385178</v>
+        <v>-1.54244837051958</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.2275861973826</v>
+        <v>-1.187644494662166</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.9536586286611097</v>
+        <v>-0.9440100093837884</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.029815115806578</v>
+        <v>-1.106149003673252</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.005334</t>
+          <t>X ≈ -0.005337</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>166</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.736199159159028</v>
+        <v>-2.040373403604875</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.30778373685051</v>
+        <v>2.495515749669181</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.664906456700599</v>
+        <v>3.635466834229341</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.355464552353524</v>
+        <v>2.446441190972799</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.628496805199887</v>
+        <v>-1.419356448102178</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.337644174187282</v>
+        <v>4.724916157267074</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.016552121565468</v>
+        <v>-0.8613101064823212</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.893052184894138</v>
+        <v>-1.766103073385139</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.657222905332965</v>
+        <v>-0.4393159214467275</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.9690547201429496</v>
+        <v>1.162651805634376</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.03900709706982</v>
+        <v>3.236581176988437</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.962913203083829</v>
+        <v>4.160928493199371</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.245011027453977</v>
+        <v>4.846729045003976</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.627253780706482</v>
+        <v>5.200626741031918</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3.774433267419212</v>
+        <v>3.315515795420168</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>9.171867862529936</v>
+        <v>8.691457935621798</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>8.442486621589566</v>
+        <v>7.988435519073697</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>4.735409721867825</v>
+        <v>4.850773257394067</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.352294109272528</v>
+        <v>4.465819824632071</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>5.142534849364623</v>
+        <v>5.284898217185017</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>8.815103295104471</v>
+        <v>9.288835527509676</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>8.743051715761247</v>
+        <v>9.213673005554519</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>6.612558135119428</v>
+        <v>7.047668936616041</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>8.949231505461093</v>
+        <v>8.692758857989226</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.003056</t>
+          <t>X ≈ -0.00306</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.691214655216832</v>
+        <v>-2.886832097387348</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-9.931054744705797</v>
+        <v>-9.33357840302611</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-11.99462703327023</v>
+        <v>-11.82391667561257</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-12.70645079282168</v>
+        <v>-12.41824071907513</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-9.274309182427338</v>
+        <v>-8.348208016685007</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-10.61993413136516</v>
+        <v>-10.06293019770231</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-12.64525357204873</v>
+        <v>-11.47754765165672</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-15.44162910970143</v>
+        <v>-14.27411552272575</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-15.41010517639474</v>
+        <v>-14.77713714773305</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-9.897598902088745</v>
+        <v>-9.355848099144012</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-10.2599589299174</v>
+        <v>-9.712357713112198</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-8.652314316479398</v>
+        <v>-8.123339663985448</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-8.514694341253268</v>
+        <v>-7.992824778370966</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-7.478207397812653</v>
+        <v>-6.997230601548381</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-6.875016251664874</v>
+        <v>-6.433067307807818</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-9.439514865817571</v>
+        <v>-8.995412401730455</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-7.0523372055628</v>
+        <v>-6.606105757436374</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.635436679821687</v>
+        <v>-4.868590403112989</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.526907383135267</v>
+        <v>-2.78195487356065</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-2.972728151084247</v>
+        <v>-3.193418766290179</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-2.883169018593691</v>
+        <v>-3.135863267670771</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.695350440459343</v>
+        <v>-1.961025789626206</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.1561548757984639</v>
+        <v>-0.4673913043479629</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-4.029264758074056</v>
+        <v>-3.754530298637285</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0007779</t>
+          <t>X ≈ -0.0007841</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4717649147340737</v>
+        <v>1.251206656993986</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.290063676975926</v>
+        <v>-4.46540314395849</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.680141764592605</v>
+        <v>-4.352946989477779</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.708589896304282</v>
+        <v>-4.263176655795448</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-9.112777118625033</v>
+        <v>-7.966014312895872</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-10.28924600621075</v>
+        <v>-9.86919692735102</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-10.3779595811076</v>
+        <v>-9.985188885675186</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-9.979736390394628</v>
+        <v>-9.610063907586863</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-9.947026174716832</v>
+        <v>-9.486558335940451</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-12.76498666831756</v>
+        <v>-12.34797900479081</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-13.1809566801187</v>
+        <v>-12.76737891601894</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-12.10234238670522</v>
+        <v>-12.36417819047899</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-13.90742790814694</v>
+        <v>-14.1763702188144</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-14.13443951836052</v>
+        <v>-14.43226834677161</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-10.7039195653726</v>
+        <v>-10.99606651418169</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-8.75277518503264</v>
+        <v>-9.059108125517589</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-8.207217949118132</v>
+        <v>-8.479408404814635</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-7.633645352819585</v>
+        <v>-7.925851506260116</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.272293579630912</v>
+        <v>-1.50683031074248</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.9649730427049619</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>3.160058043800348</v>
+        <v>3.372757421984261</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>4.45445808735078</v>
+        <v>4.676905244856393</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>4.046711621176726</v>
+        <v>4.230884557721147</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>5.343025860965305</v>
+        <v>5.448055908259114</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0015</t>
+          <t>X ≈ 0.001492</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.105131095637944</v>
+        <v>2.159010061798519</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.774883835402171</v>
+        <v>2.371902079824771</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7831359133058626</v>
+        <v>2.48749561748744</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.834525884974994</v>
+        <v>3.262827002633529</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.383887367269232</v>
+        <v>3.44616534703809</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.448615209179934</v>
+        <v>5.425587250247055</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5.142499079314305</v>
+        <v>7.825990192245612</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4.868558701594317</v>
+        <v>7.52429795606885</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.822062903249659</v>
+        <v>4.003410796910444</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2715400895673312</v>
+        <v>1.838453046702163</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.090585336740439</v>
+        <v>-1.087279535421828</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.811344428900185</v>
+        <v>-1.822630367573716</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-4.046948214869936</v>
+        <v>-2.026043751055262</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.385746089090532</v>
+        <v>-1.36092695998255</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.389372946513241</v>
+        <v>0.7014729835591282</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>2.297809196342243</v>
+        <v>4.473131264876159</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>5.265169100574226</v>
+        <v>7.121660362007994</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>6.934062956643871</v>
+        <v>9.287171006928858</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>5.379276528718968</v>
+        <v>7.939471852871023</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>4.682117955398077</v>
+        <v>7.236627105269349</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>3.256209758630192</v>
+        <v>5.751751411228284</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>3.626343510152942</v>
+        <v>6.135304485603363</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>3.903248465660013</v>
+        <v>6.378938970881642</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>3.385643821391483</v>
+        <v>5.758084380261913</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.003778</t>
+          <t>X ≈ 0.003769</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8219821376202248</v>
+        <v>-1.014008640017941</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.26623238177207</v>
+        <v>-2.016690678662648</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.439852525673842</v>
+        <v>-3.643082902494342</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-5.521678587286502</v>
+        <v>-4.617665207386992</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-6.223483782711583</v>
+        <v>-4.888521018283448</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.55317179988112</v>
+        <v>-3.209458303512392</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.574518462617014</v>
+        <v>-3.233518911829137</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.144268916909631</v>
+        <v>-2.389356104670306</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.618124957578978</v>
+        <v>-0.3452656035119901</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.133719694508514</v>
+        <v>-1.523895399913044</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.236578501191168</v>
+        <v>-1.638603499745486</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.888686937668275</v>
+        <v>-1.915443764528199</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.38064745374129</v>
+        <v>-3.79891164784889</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.97908428139764</v>
+        <v>-4.050201650664555</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-7.386966759635634</v>
+        <v>-5.120248645502997</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-9.796548238106951</v>
+        <v>-8.034972256697905</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-10.31141553754219</v>
+        <v>-8.530062085588916</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-10.42474506721555</v>
+        <v>-8.668316859344493</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-12.09007433059828</v>
+        <v>-9.99825617660013</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-12.66030705538102</v>
+        <v>-10.55587050374183</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-12.83328782043428</v>
+        <v>-10.73721461902235</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-12.91693709891707</v>
+        <v>-10.81237714097764</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-15.2798377740488</v>
+        <v>-13.27144535840187</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-14.23674548520839</v>
+        <v>-12.27528319439018</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.006057</t>
+          <t>X ≈ 0.006045</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.858901545125434</v>
+        <v>-1.990386772726993</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.063647874245149</v>
+        <v>-2.230003191103748</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.115599204946868</v>
+        <v>-2.718493087928373</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.2793405831403888</v>
+        <v>0.4819448254980045</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.444555787924998</v>
+        <v>2.489176518115727</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2424712461083445</v>
+        <v>0.3607182551511841</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.8585671227835405</v>
+        <v>1.469410168578719</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.5381038666918201</v>
+        <v>-0.3580538849906745</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6536046112464149</v>
+        <v>-0.6139079570649741</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.167485021667986</v>
+        <v>-2.172869471049495</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.0300159508345601</v>
+        <v>0.003172080842219316</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.06771992507658808</v>
+        <v>0.4885929331470606</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.07692757458953992</v>
+        <v>0.5174747112448586</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.8937031796127499</v>
+        <v>-0.4966971576065973</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.072937295588297</v>
+        <v>1.495792827790446</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.535182386228044</v>
+        <v>1.294120410022018</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.476359410172499</v>
+        <v>-1.108152465166178</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.464313240019088</v>
+        <v>-2.925628358035169</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-5.131920115523435</v>
+        <v>-5.010016705602084</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-4.196980470018374</v>
+        <v>-3.646004973186734</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-3.611635364739065</v>
+        <v>-2.680882424759034</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-4.444863149274532</v>
+        <v>-3.522328471618543</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-5.682283929704774</v>
+        <v>-4.811261036148586</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-5.385844648210146</v>
+        <v>-4.590258267985945</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.008335</t>
+          <t>X ≈ 0.008321</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.085543123013565</v>
+        <v>-2.912014809118901</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.664185027129896</v>
+        <v>-4.534606211501995</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.667608034694553</v>
+        <v>-3.765495043112942</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.78899882621041</v>
+        <v>-4.365313838424584</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.318036548909909</v>
+        <v>-4.237365090667332</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.347946683783192</v>
+        <v>-5.305567460980818</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.26421156126105</v>
+        <v>-3.271201458408491</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.182917290505692</v>
+        <v>-5.200671247412437</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.772646998308879</v>
+        <v>-6.703220287238622</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-6.899889294735814</v>
+        <v>-7.10032337170729</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.377241277226986</v>
+        <v>-6.837502051696354</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.955040169164128</v>
+        <v>-4.683028588392212</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.777916589910475</v>
+        <v>-3.364184615609695</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.2886044418394675</v>
+        <v>-1.581678495266871</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.767630483928912</v>
+        <v>-3.083690193439317</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-3.235029725650925</v>
+        <v>-4.563805151681223</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.961122675144345</v>
+        <v>-4.012542517006857</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-3.483611369331719</v>
+        <v>-4.55358988747453</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-3.271888019060597</v>
+        <v>-4.339127660328757</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-5.148390051395054</v>
+        <v>-6.165357541800432</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-3.634648249330034</v>
+        <v>-4.691985716650507</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-5.778074072840589</v>
+        <v>-6.39980129983028</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-4.271521700843273</v>
+        <v>-4.931677018633536</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-5.180012744265085</v>
+        <v>-5.910142543535244</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.01061</t>
+          <t>X ≈ 0.0106</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.6292398772089882</v>
+        <v>-0.7332991757988978</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.872965110301465</v>
+        <v>7.513893923664384</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>7.479060807498783</v>
+        <v>8.114213912958959</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.594251246337471</v>
+        <v>7.763910046006146</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>8.070028558718931</v>
+        <v>8.711909162131036</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.786375264432614</v>
+        <v>6.437089090621427</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.493334397602318</v>
+        <v>8.082697566340897</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.375927378999272</v>
+        <v>6.968740882675256</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.351197583548554</v>
+        <v>5.063756202203095</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.149014394464622</v>
+        <v>3.857291360833862</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.020052923054315</v>
+        <v>3.723383814271784</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.9849015964746</v>
+        <v>4.672884807954127</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.431090627124981</v>
+        <v>2.732649792040469</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.386011460735105</v>
+        <v>2.074237995711549</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.2591320693784169</v>
+        <v>0.4168192640759187</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.256731052371357</v>
+        <v>2.874542980031016</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.7229245313278057</v>
+        <v>1.131318306010954</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.04701796162808591</v>
+        <v>0.1787620697018539</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.3086486039353815</v>
+        <v>-0.4264478342999354</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.2906070677186818</v>
+        <v>-0.2118613892409513</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.9921662224685903</v>
+        <v>0.4502023060995768</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.330217174098472</v>
+        <v>0.7848758497180555</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.186823192690504</v>
+        <v>1.028510334996433</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.107866043613683</v>
+        <v>0.8663713407069693</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.01289</t>
+          <t>X ≈ 0.01288</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.280812477797397</v>
+        <v>2.015508555683056</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.512266944790404</v>
+        <v>2.32431054215342</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.768843640948212</v>
+        <v>2.736364243542425</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.626218937688023</v>
+        <v>2.698296390228634</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.5761620759213741</v>
+        <v>-0.01759886987778714</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.041167086077067</v>
+        <v>2.353232294543773</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.40823781421588</v>
+        <v>2.668416184185794</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.121830267783409</v>
+        <v>2.366619322049424</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.436438612748802</v>
+        <v>4.725697743782987</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.084997518850422</v>
+        <v>3.370257223884977</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.090034048801357</v>
+        <v>1.402003889525425</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.245872990178455</v>
+        <v>0.5615262107968704</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.6807460869857636</v>
+        <v>-0.005984468217363315</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4604868207071746</v>
+        <v>0.09891148640088687</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.908644425421009</v>
+        <v>-2.26863615391111</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.303602571294803</v>
+        <v>-1.707332135091477</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.263632918260015</v>
+        <v>-0.1258192883894793</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.298631236635899</v>
+        <v>0.8648921120668334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.9441933013777302</v>
+        <v>0.51755658640365</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.193864097031721</v>
+        <v>2.979334042698582</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.579671740305187</v>
+        <v>2.973687294126833</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.64389025102161</v>
+        <v>4.022120277789533</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>5.491518970114512</v>
+        <v>4.827552515876867</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.845961281708973</v>
+        <v>4.665413521587432</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.01517</t>
+          <t>X ≈ 0.01515</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.008069552596481</v>
+        <v>4.235290055148802</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>7.690188015761443</v>
+        <v>6.961186269105767</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>10.77305405817533</v>
+        <v>10.1586117000347</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.043762002321188</v>
+        <v>6.596193664900305</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>8.209732459290123</v>
+        <v>7.800505204626887</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.137649162423664</v>
+        <v>6.175820339464785</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.595417239294974</v>
+        <v>1.662133242391214</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.5571311155772278</v>
+        <v>0.6104316617155874</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.5997327476988019</v>
+        <v>0.7318384006297478</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.5740755732481162</v>
+        <v>0.6707523756307694</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.113314174511558</v>
+        <v>3.18680821583348</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.854246158095577</v>
+        <v>5.916570858652037</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.478899817928713</v>
+        <v>6.020035638228514</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.012880594515934</v>
+        <v>6.523681276043582</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.349722271004516</v>
+        <v>5.841526894158427</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.687845835500873</v>
+        <v>4.147191815233775</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.043252167352271</v>
+        <v>2.539552005012524</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.186695161117846</v>
+        <v>1.654788200602852</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.6464124388014056</v>
+        <v>1.117370728500461</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.6746321568845346</v>
+        <v>-0.1718022249367976</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.2912693059068161</v>
+        <v>0.764512672178661</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>1.44697636571825</v>
+        <v>1.441229849471547</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.9628808351658193</v>
+        <v>0.9329846355018887</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.6345581988105309</v>
+        <v>-0.7329137572839031</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.01745</t>
+          <t>X ≈ 0.01742</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>9.704815695302095</v>
+        <v>9.8725757699087</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.497231356086026</v>
+        <v>0.3942506091826914</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.847004134897027</v>
+        <v>-6.744304237454195</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.917672030965527</v>
+        <v>-9.676269282885876</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.776550440513013</v>
+        <v>-6.617251293982996</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.03630898893426604</v>
+        <v>-2.902038338588454</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.165971549450319</v>
+        <v>-5.353856818058524</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.03272906879628579</v>
+        <v>-1.587774237626832</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.08376165102115607</v>
+        <v>-0.7318605777311049</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.135926514299797</v>
+        <v>4.941797210431076</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.08568118092186</v>
+        <v>3.64572225403267</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.663870090324323</v>
+        <v>2.938389899410708</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.664678909997235</v>
+        <v>2.986288479634361</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.806086610331462</v>
+        <v>5.063635813550029</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>5.457930187825518</v>
+        <v>6.707062827013935</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>3.747102934849103</v>
+        <v>4.942785450484699</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.765792885331194</v>
+        <v>6.001695736434108</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>5.85651357036582</v>
+        <v>5.86881163127245</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.876843562434338</v>
+        <v>4.920483160743863</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>2.710748195931842</v>
+        <v>2.809488210453935</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.356437036584857</v>
+        <v>-1.246328383949916</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-2.599208185919032</v>
+        <v>-2.484281603579618</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.4100367581606648</v>
+        <v>-1.077856420626951</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.451003298515609</v>
+        <v>-0.07720471724193345</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.01972</t>
+          <t>X ≈ 0.0197</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.3170873264159226</v>
+        <v>1.211466436185539</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.342454600162831</v>
+        <v>6.206772334293959</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.849012775842077</v>
+        <v>5.614370135485736</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.952246693538676</v>
+        <v>7.838811995386386</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.261164099148282</v>
+        <v>4.245745601384478</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.708727610379846</v>
+        <v>4.700663589151794</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>7.308564946114515</v>
+        <v>6.895743145743133</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>8.569564323151241</v>
+        <v>9.523672055427276</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.016160842236701</v>
+        <v>9.97762056020791</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>8.070708289276673</v>
+        <v>8.999855574812244</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.572446690706755</v>
+        <v>8.723273620340947</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.107821209216418</v>
+        <v>10.10838150289018</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>7.66723013764792</v>
+        <v>8.610147441457023</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>8.228599035189312</v>
+        <v>10.42799305957194</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>8.822985957132232</v>
+        <v>10.98929707839167</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>9.908581015276852</v>
+        <v>12.13541666666664</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>7.364715921211697</v>
+        <v>10.75253256150506</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>10.01963169238</v>
+        <v>13.46699478865081</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>12.64550189259185</v>
+        <v>16.18158123370985</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>12.10295572462578</v>
+        <v>15.61413673232909</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>12.02710976321665</v>
+        <v>15.53897421037373</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>12.30158447569883</v>
+        <v>15.78260869565218</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>13.44526441759752</v>
+        <v>16.87046970136272</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.022</t>
+          <t>X ≈ 0.02198</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6996706428437278</v>
+        <v>-0.7124380488653728</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.887121186257374</v>
+        <v>0.9284475682610562</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.409886450951937</v>
+        <v>1.560545919199555</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.7361481177836993</v>
+        <v>0.9681437203913887</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.4003576452364257</v>
+        <v>0.6925855802920537</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.373460482391678</v>
+        <v>-2.92406571937024</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.145409166282029</v>
+        <v>-3.719147731603016</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.458732330141359</v>
+        <v>5.409894089139364</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.421788139507044</v>
+        <v>5.537822998823472</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.688088149745063</v>
+        <v>2.854979050773949</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.962147791906986</v>
+        <v>3.127214065378283</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.683398388458933</v>
+        <v>0.9638396580767932</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.521020635328419</v>
+        <v>5.509324899116585</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-6.464764123471163</v>
+        <v>-6.059663879297595</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.681014147575723</v>
+        <v>0.805351550137992</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-2.606951871657756</v>
+        <v>-4.29372178953286</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-2.740869008635229</v>
+        <v>-4.397602201257811</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-4.806494026181895</v>
+        <v>-6.417278759249655</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-4.590602645257569</v>
+        <v>-6.202816532103824</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-10.28610977646602</v>
+        <v>-11.6486074455354</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-8.867871630706446</v>
+        <v>-10.32925949408601</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-6.982933278390163</v>
+        <v>-8.517629563211052</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-6.70845856590806</v>
+        <v>-8.273995077932724</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-10.70585944658232</v>
+        <v>-12.20971897788257</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.02428</t>
+          <t>X ≈ 0.02425</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.051460578875719</v>
+        <v>3.061146856795119</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.716683780525905</v>
+        <v>2.815240021091078</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.047895500725687</v>
+        <v>7.220923277690233</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>13.10417225051371</v>
+        <v>12.28889843737252</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>10.84530485488952</v>
+        <v>10.126547844443</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>16.80150181021766</v>
+        <v>15.94385880893164</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>17.95263004940424</v>
+        <v>17.03556924952912</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.982110912343472</v>
+        <v>9.183478994799742</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.25436732502741</v>
+        <v>5.537822998823472</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.250682418221743</v>
+        <v>10.40214886209475</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.936796401154851</v>
+        <v>-2.533163293112288</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-9.984776573833614</v>
+        <v>-8.470122606074149</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-9.184861717612755</v>
+        <v>-9.585014723524864</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-7.482863670982475</v>
+        <v>-7.946456332127838</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-11.98716081471688</v>
+        <v>-12.40219561967321</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-9.469696969696912</v>
+        <v>-9.954099148023367</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-10.05797955974843</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-5.862300964341728</v>
+        <v>-6.417278759249598</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-1.800255737263555</v>
+        <v>-2.429231626443446</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.232743918858326</v>
+        <v>1.558939724275909</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.2328791721847452</v>
+        <v>-0.8952972299350677</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-6.077955902824556</v>
+        <v>-6.630837110380973</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-7.726558113419422</v>
+        <v>-8.273995077932675</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-2.033159597411981</v>
+        <v>-2.775756713731624</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.02656</t>
+          <t>X ≈ 0.02653</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>55</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.722789250204393</v>
+        <v>2.821009635525762</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.388012451854635</v>
+        <v>2.575102799821948</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-4.504552051721895</v>
+        <v>-4.13413675661517</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.399324252982794</v>
+        <v>-2.908357137241552</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.735114725530032</v>
+        <v>-3.183915277340851</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.548148539432709</v>
+        <v>-3.026981671342824</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.50191540514124</v>
+        <v>-2.003881865393723</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.8562367864693812</v>
+        <v>1.327561327561355</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9204578497977707</v>
+        <v>-0.3626915809363922</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-5.329737162197944</v>
+        <v>-4.795106712519413</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-3.237495701854122</v>
+        <v>-2.704689879733181</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.698063287120334</v>
+        <v>-1.163090016022693</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.8151382823871671</v>
+        <v>1.358381502890154</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.860486048604862</v>
+        <v>-4.344398013088394</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-5.518629346185421</v>
+        <v>-5.02655239497345</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-4.924242424242472</v>
+        <v>-4.465248376153831</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-3.239977743038082</v>
+        <v>-2.750946969696976</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-5.163000265041127</v>
+        <v>-4.70201289304044</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-1.31074524775314</v>
+        <v>-0.8511870295310047</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-1.123899437785134</v>
+        <v>-0.6366005844720419</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-1.666445605751143</v>
+        <v>-1.204045085852755</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-1.742291567160223</v>
+        <v>-1.279207607808019</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>5.804910418049047</v>
+        <v>6.237154150197576</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>5.729078164825829</v>
+        <v>6.075015155908169</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.02884</t>
+          <t>X ≈ 0.02881</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>41</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.895738252421687</v>
+        <v>4.993958637743056</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.560961454071872</v>
+        <v>4.748051802039186</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.122942405040916</v>
+        <v>3.493357700147641</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.849012775842048</v>
+        <v>5.33997989158329</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3648264771930698</v>
+        <v>0.1863729709961106</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-5.055909071583457</v>
+        <v>-4.534742203493572</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.36726419574574</v>
+        <v>6.865297735493257</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.528077141236494</v>
+        <v>8.999401682328468</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.569564323151241</v>
+        <v>9.127330592012619</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.79664864711475</v>
+        <v>8.331279096793281</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.631683899032765</v>
+        <v>6.164489721153707</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.352934495584769</v>
+        <v>5.88790776668241</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.6482763517591863</v>
+        <v>-0.1050331312561994</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.008693552282061</v>
+        <v>4.524781587798529</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>3.350550254701503</v>
+        <v>3.842627205913473</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-5.81116038433111</v>
+        <v>-5.352166336242469</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-5.945077521308583</v>
+        <v>-5.456046747967477</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-8.488942615373674</v>
+        <v>-8.027955243372986</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-8.273051234449376</v>
+        <v>-7.813493016227241</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-5.647181034237413</v>
+        <v>-5.15988218092432</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-3.750702811959506</v>
+        <v>-3.288302292061118</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-6.265573163612544</v>
+        <v>-5.80248920426034</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-8.430122841374427</v>
+        <v>-7.997879109225899</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-6.066930704353766</v>
+        <v>-5.720993713271426</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.03112</t>
+          <t>X ≈ 0.03109</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>25</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.359152886568033</v>
+        <v>6.457373271889402</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>14.02437608821825</v>
+        <v>14.21146643618556</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.58635703918723</v>
+        <v>12.95677233429395</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>11.87340301974449</v>
+        <v>12.36437013548573</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>15.53761254719721</v>
+        <v>16.08881199538639</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>15.72457873329465</v>
+        <v>16.24574560138453</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.952630049404242</v>
+        <v>7.450663589151759</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.67441860465117</v>
+        <v>15.14574314574314</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>14.71590578656587</v>
+        <v>15.27367205542725</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>25.94299011052938</v>
+        <v>26.47762056020791</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>26.21704975269125</v>
+        <v>26.74985557481219</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.93830034924331</v>
+        <v>14.47327362034095</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>20.81513828238719</v>
+        <v>21.35838150289018</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>24.5940594059406</v>
+        <v>25.11014744145707</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>27.93591610836004</v>
+        <v>28.42799305957201</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>24.53030303030303</v>
+        <v>24.98929707839167</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>16.39638589332556</v>
+        <v>16.88541666666666</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>8.291545189504376</v>
+        <v>8.752532561505063</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>16.5074365704287</v>
+        <v>16.96699478865084</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>12.69428238039673</v>
+        <v>13.18158123370982</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>16.1517362124307</v>
+        <v>16.61413673232909</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>16.0758902510216</v>
+        <v>16.5389742103738</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>12.35036496350371</v>
+        <v>12.78260869565224</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>8.274532710280376</v>
+        <v>8.620469701362715</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.03339</t>
+          <t>X ≈ 0.03336</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>11.98415288656803</v>
+        <v>10.97350230414744</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>14.77437608821818</v>
+        <v>17.17920837166939</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>22.71135703918726</v>
+        <v>22.37612717300363</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>15.74840301974452</v>
+        <v>18.55791852258248</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>18.53761254719721</v>
+        <v>18.28236038248316</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>9.349578733294592</v>
+        <v>11.98768108525544</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.452630049404242</v>
+        <v>7.966792621409823</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.075581395348834</v>
+        <v>1.210259274775403</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.215905786565848</v>
+        <v>4.563994636072408</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.442990110529379</v>
+        <v>3.767943140853092</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>23.4670497526913</v>
+        <v>23.39501686513479</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>23.18830034924331</v>
+        <v>26.34424136227643</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>28.31513828238719</v>
+        <v>31.68096214805144</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>21.84405940594057</v>
+        <v>24.98111518339258</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>24.31091610836007</v>
+        <v>24.2989608015075</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>21.78030303030306</v>
+        <v>21.63445836871425</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>27.89638589332556</v>
+        <v>27.98219086021505</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>24.66654518950438</v>
+        <v>27.84930675505345</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>24.88243657042873</v>
+        <v>24.83796253058632</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>21.94428238039673</v>
+        <v>21.8267425240324</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>18.2767362124307</v>
+        <v>18.03349157103878</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>21.3258902510216</v>
+        <v>21.18413550069635</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>24.72536496350365</v>
+        <v>27.87938288920055</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>21.52453271028038</v>
+        <v>24.49143744329823</v>
       </c>
     </row>
   </sheetData>
@@ -3180,493 +3180,493 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.03153</t>
+          <t>X &gt; -0.03151</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3307</v>
+        <v>3331</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1873936599785111</v>
+        <v>-0.08406978118156161</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1156058883513253</v>
+        <v>0.07367937981810257</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3054698838896996</v>
+        <v>0.02837137964001357</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.460832026844038</v>
+        <v>-0.1298107060541156</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3288937666933478</v>
+        <v>0.08881199538640061</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3957220185851114</v>
+        <v>0.02358973396137287</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.4589222971661471</v>
+        <v>-0.008117772855413818</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.509451392339507</v>
+        <v>-0.08700259671279298</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.4809635692438832</v>
+        <v>-0.03176727511669242</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.544212539274902</v>
+        <v>-0.06348556834216623</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.4335526569472492</v>
+        <v>0.04650629251558769</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.5443751554267777</v>
+        <v>-0.003543609691959659</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.5350726880769443</v>
+        <v>-0.02402424217265775</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.5274359211622084</v>
+        <v>0.01466704636577987</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.4139029507473211</v>
+        <v>0.1585319817276982</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.4048402577814301</v>
+        <v>0.1686921068433023</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.3700594898971374</v>
+        <v>0.1424568104653403</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.4872051877971657</v>
+        <v>0.05729732027042189</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.4647856517935196</v>
+        <v>0.07970462078512952</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.6225403317748217</v>
+        <v>-0.04780407363649886</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.5733393162702072</v>
+        <v>0.03225310905373391</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.7521544754818805</v>
+        <v>-0.1150911961668513</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.6714004536668483</v>
+        <v>-0.03371783496006486</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.6991594578478413</v>
+        <v>-0.05800523109000011</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02925</t>
+          <t>X &gt; -0.02924</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3281</v>
+        <v>3304</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1904839173060608</v>
+        <v>-0.04097358714275856</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1457722617666448</v>
+        <v>0.08999920828415497</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3561020765002354</v>
+        <v>0.02444150722628535</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.5070877406311567</v>
+        <v>-0.1302147020593978</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.4017813921967317</v>
+        <v>0.06232990089346657</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.4706319366053719</v>
+        <v>-0.03480828181841389</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.5282674642403933</v>
+        <v>-0.06032707631045042</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.5163608918608134</v>
+        <v>-0.07714842052192239</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.4272980969292703</v>
+        <v>0.007628066273888123</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.4849309820351095</v>
+        <v>-0.01785864413204763</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.3755428399012928</v>
+        <v>0.1209740553669576</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.4546544032620119</v>
+        <v>0.07279111129390259</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4667572218655422</v>
+        <v>0.03108135206061746</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.5180645685352445</v>
+        <v>0.01177689227179712</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.4288255329773492</v>
+        <v>0.1321886526900258</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.4547988243640404</v>
+        <v>0.1076545663143733</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.3882856395211576</v>
+        <v>0.1122363586026367</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.4751113362029571</v>
+        <v>0.0576685131666963</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.4237868014520103</v>
+        <v>0.1087294516910262</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.5842564323886634</v>
+        <v>-0.0215626598814751</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.5303587936594383</v>
+        <v>0.06378898512618036</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.709976334418549</v>
+        <v>-0.08413528750883614</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.6612133424073861</v>
+        <v>-0.03433532855356702</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.6885882894148381</v>
+        <v>-0.05749640033220516</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.02698</t>
+          <t>X &gt; -0.02696</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3243</v>
+        <v>3268</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2421943271490505</v>
+        <v>-0.1242128721397719</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.009314570281020451</v>
+        <v>0.1932293541186638</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2665841372833597</v>
+        <v>0.07991006612733287</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.4109978383615456</v>
+        <v>-0.06993643385733606</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.331179604856743</v>
+        <v>0.09733040122758041</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.4336549373585754</v>
+        <v>-0.002580631117048426</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.513627619307421</v>
+        <v>-0.05009744585584741</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.5290180323540525</v>
+        <v>-0.09420813318499199</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.4087105424703452</v>
+        <v>0.05100985621920984</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.365883085663441</v>
+        <v>0.125396306703955</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1048175691760207</v>
+        <v>0.3847229932822245</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.2122372851652941</v>
+        <v>0.3391272788775268</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.211290728061492</v>
+        <v>0.3092811674220499</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2605363518214716</v>
+        <v>0.2925757514021541</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.1624848756498025</v>
+        <v>0.4218899164533028</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.1956274526252955</v>
+        <v>0.3910064801010762</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.1574602605205939</v>
+        <v>0.3663326972010097</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.2440042103109548</v>
+        <v>0.3127036060988289</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.1945338729210562</v>
+        <v>0.362045201116473</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.328199910949138</v>
+        <v>0.2585983486242398</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.2364338430221693</v>
+        <v>0.3817918836589556</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.5096259277149144</v>
+        <v>0.141420693554231</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.463445147470452</v>
+        <v>0.1891550401000188</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.5210269566946479</v>
+        <v>0.1369935691717714</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.0247</t>
+          <t>X &gt; -0.02469</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3201</v>
+        <v>3226</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1669017040026901</v>
+        <v>-0.04924414885544337</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01968224252953377</v>
+        <v>0.1831413130328201</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2305268838419465</v>
+        <v>0.1153802800900721</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4296084673713167</v>
+        <v>-0.09034335804476967</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.344375030442535</v>
+        <v>0.08264866718916863</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.5127620557703381</v>
+        <v>-0.08224453425054179</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.7080287448779146</v>
+        <v>-0.2434468024609444</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.6889634282987842</v>
+        <v>-0.2533931898521757</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.5365817756231905</v>
+        <v>-0.07714559344655925</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5142416157536687</v>
+        <v>-0.02237943979209689</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2845059411481543</v>
+        <v>0.2058605146084815</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3274948577283752</v>
+        <v>0.2249721997109262</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3430186291943755</v>
+        <v>0.178276467363446</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2966288531687127</v>
+        <v>0.2572426206906897</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.2198471315153441</v>
+        <v>0.3661692574081812</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.2612208088992176</v>
+        <v>0.3275778452438658</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1584769495672091</v>
+        <v>0.3657754665429422</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.2135998058183546</v>
+        <v>0.3441167199209048</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.07272562545401939</v>
+        <v>0.4841721331262292</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2417550611009318</v>
+        <v>0.3456679210163287</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1416470584806646</v>
+        <v>0.47787163477566</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.4173972919069016</v>
+        <v>0.235380653992145</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.4366431564213968</v>
+        <v>0.2186173724417628</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.5564576052460168</v>
+        <v>0.1059005755102618</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.02242</t>
+          <t>X &gt; -0.02241</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3144</v>
+        <v>3159</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2780431980546325</v>
+        <v>-0.1485349619258045</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1537666786800713</v>
+        <v>-0.0004166194573471671</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3425529134194036</v>
+        <v>0.01966541605496275</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5324124037700528</v>
+        <v>-0.1150259010037331</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.408008698455653</v>
+        <v>0.06741489028884473</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.6776983065536015</v>
+        <v>-0.1672226076177239</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8626182897289425</v>
+        <v>-0.3780517760875313</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.7433029143361765</v>
+        <v>-0.3503198463828454</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6205931054885738</v>
+        <v>-0.1730828280006023</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.5839256589449704</v>
+        <v>-0.1318972462843675</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.4183636144293885</v>
+        <v>0.03232720154616686</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.4571369131141125</v>
+        <v>0.02609607382565571</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4526905607189917</v>
+        <v>-0.02963111540636021</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3697960157461466</v>
+        <v>0.05618720163378299</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.2163198573868712</v>
+        <v>0.2449122514912005</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.2057375788340252</v>
+        <v>0.2567426104409307</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.003487162847086722</v>
+        <v>0.3926813539692517</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.005830903790098318</v>
+        <v>0.4365767953123267</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.1771729946903662</v>
+        <v>0.6066913752500795</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.03354540453903354</v>
+        <v>0.4923621379146965</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.1771572483379131</v>
+        <v>0.6710627285340252</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1338999587686089</v>
+        <v>0.3934506418828221</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1583790746521601</v>
+        <v>0.3712162905888832</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.3107090199995213</v>
+        <v>0.2279404199445523</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.02014</t>
+          <t>X &gt; -0.02013</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3086</v>
+        <v>3097</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1831436718108677</v>
+        <v>-0.01698570246957587</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1467950829529485</v>
+        <v>0.07488419828877113</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2800736013019929</v>
+        <v>0.1203387230046715</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5567322024061951</v>
+        <v>-0.1335445260477925</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2949156331570535</v>
+        <v>0.1863729709961532</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4120192048497344</v>
+        <v>0.07239086623198432</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.7147885777307934</v>
+        <v>-0.2230679458514544</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.6202300091463826</v>
+        <v>-0.2207843197242596</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4314660289775105</v>
+        <v>0.02174403486169041</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.5086227926964284</v>
+        <v>-0.0488982440351009</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3773355328846932</v>
+        <v>0.08104528542317269</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3793239244816817</v>
+        <v>0.1123858750852449</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3214455083780692</v>
+        <v>0.1099902544989249</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2328139790723185</v>
+        <v>0.2025195045404331</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1610144247578944</v>
+        <v>0.2798926088315099</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1613582495935404</v>
+        <v>0.2485563376509248</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.1442035460898623</v>
+        <v>0.4859321305841888</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.0910277250800533</v>
+        <v>0.4689360420078046</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1968574698140131</v>
+        <v>0.5737001400370403</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.07939564900514284</v>
+        <v>0.4850317335485812</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.2359058466165251</v>
+        <v>0.6786528613613427</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.04716674379705665</v>
+        <v>0.4292613997897377</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.01244682787957174</v>
+        <v>0.4662755775114462</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.1985716319101627</v>
+        <v>0.2911187165386977</v>
       </c>
     </row>
     <row r="12">
@@ -3676,243 +3676,243 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3024</v>
+        <v>3029</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1456058925589758</v>
+        <v>0.02880184331797153</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1673507666734366</v>
+        <v>0.06266276525796854</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3069106127011167</v>
+        <v>0.1043133179005125</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6732461261162186</v>
+        <v>-0.2404183197454941</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3992918234896123</v>
+        <v>0.09274900326040836</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4568808327803637</v>
+        <v>0.03832846977962134</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.7500993159361116</v>
+        <v>-0.2459877568758202</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.6479498164014572</v>
+        <v>-0.2368512713340394</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.5878125418316316</v>
+        <v>-0.1231741995004754</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.7166543924330995</v>
+        <v>-0.2433784539228796</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.5554230823432675</v>
+        <v>-0.08380648961905734</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.551818227831788</v>
+        <v>-0.04563463352291564</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.4698699548451017</v>
+        <v>-0.02319744447824945</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.4079181814028416</v>
+        <v>0.04400726376704256</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.2882843532291517</v>
+        <v>0.1712451991375161</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.3667945950267821</v>
+        <v>0.06074916927083507</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.1842805533916945</v>
+        <v>0.1739542160737813</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.2365076157761479</v>
+        <v>0.09355397830901779</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1990672262038515</v>
+        <v>0.1298161465941448</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.2898655720471339</v>
+        <v>0.06717305698710163</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.08612305416989585</v>
+        <v>0.310706653173412</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.2744071713181242</v>
+        <v>0.123269822383044</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.2116185075707335</v>
+        <v>0.2215525900416182</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.3670016812540169</v>
+        <v>0.04602268914746332</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01559</t>
+          <t>X &gt; -0.01558</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2957</v>
+        <v>2959</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1509142275259236</v>
+        <v>0.01203457302957389</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.3670304240342119</v>
+        <v>-0.1488153484504977</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.5110237532909423</v>
+        <v>-0.0767847126859138</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.8360360128386546</v>
+        <v>-0.3821891125840864</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5820111087167632</v>
+        <v>-0.06834045592320592</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.7123960566213725</v>
+        <v>-0.1949665249171701</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.028540091819693</v>
+        <v>-0.500949314074056</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.9179123741581137</v>
+        <v>-0.4845089550971977</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.857445492034401</v>
+        <v>-0.3712506076527831</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9718533765120156</v>
+        <v>-0.4756253193750055</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.7795832439416941</v>
+        <v>-0.2851376957126561</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.8033635106421784</v>
+        <v>-0.2732763628296979</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.7616811246208925</v>
+        <v>-0.2914501469414716</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.6597323028561632</v>
+        <v>-0.183217327825524</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.5563293400553349</v>
+        <v>-0.07065923153310649</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.5826817926311989</v>
+        <v>-0.1296783176312459</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.4605641741508251</v>
+        <v>-0.07884496516071948</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.5116947699961258</v>
+        <v>-0.1580913845320282</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.410861876566571</v>
+        <v>-0.05864623699018523</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.5080141410487329</v>
+        <v>-0.1279023977447835</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2198854091909226</v>
+        <v>0.2022528700738491</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.3769654434697856</v>
+        <v>0.04589754708437255</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.3528128593496263</v>
+        <v>0.1069330199765091</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.3747740195133318</v>
+        <v>0.0324332025455476</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.01331</t>
+          <t>X &gt; -0.0133</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.02361971532801732</v>
+        <v>0.1752328966288061</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2230179354093025</v>
+        <v>-0.05200245502058465</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4605668398534419</v>
+        <v>-0.07104407738894736</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8762492751094726</v>
+        <v>-0.4356298645142687</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5667352788897375</v>
+        <v>-0.0656765223589133</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.7430621852857797</v>
+        <v>-0.2373730898790143</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.043193131939297</v>
+        <v>-0.5256595306254042</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.058171924596742</v>
+        <v>-0.6369109817385734</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.9970862022881875</v>
+        <v>-0.5242373522382522</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.15805518563787</v>
+        <v>-0.6733031065749344</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.177861366165445</v>
+        <v>-0.6950537696786867</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.192801463866878</v>
+        <v>-0.6728721766593964</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.17997856449108</v>
+        <v>-0.7211718816178561</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.031900119530434</v>
+        <v>-0.5652452287000003</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.041396282564918</v>
+        <v>-0.5636270521598306</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.054892500423229</v>
+        <v>-0.6104234944340305</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.9588359019940356</v>
+        <v>-0.5890766946191519</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.008245166889751</v>
+        <v>-0.6665516747759597</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.7368835973448071</v>
+        <v>-0.3966415749855301</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.8791441930298447</v>
+        <v>-0.5113183815402707</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.5967772538162421</v>
+        <v>-0.1486344363203145</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.7918494270749719</v>
+        <v>-0.3430698918313055</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.6016826388764613</v>
+        <v>-0.1487638533674271</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.6568398387392307</v>
+        <v>-0.2902133108964833</v>
       </c>
     </row>
     <row r="15">
@@ -3922,79 +3922,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2759</v>
+        <v>2756</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3685020415482541</v>
+        <v>0.5250478579225231</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.285433261896749</v>
+        <v>0.4426511679104124</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1618966075325474</v>
+        <v>0.5403458213256513</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2791698481936251</v>
+        <v>0.1481539192695109</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.08908842912666159</v>
+        <v>0.6136858237930198</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2077223109978092</v>
+        <v>0.3221970979585862</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.707312313708151</v>
+        <v>-0.16405502556686</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.965221034988474</v>
+        <v>-0.5208032274073418</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.01156357176145</v>
+        <v>-0.5169416629843013</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.151131779120817</v>
+        <v>-0.6426394614605684</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.072993537351984</v>
+        <v>-0.5666184136270616</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.006484926830311</v>
+        <v>-0.461312574093462</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.026016952269849</v>
+        <v>-0.5432815484474887</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.9371793083967077</v>
+        <v>-0.4450062655953744</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.8877833136052828</v>
+        <v>-0.3824266220488255</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.9225339772864203</v>
+        <v>-0.4511661861758256</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.818364648973791</v>
+        <v>-0.4252277938691762</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.8657784994648878</v>
+        <v>-0.5006365801102888</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.7009570619880847</v>
+        <v>-0.3373530374361167</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.601410706827302</v>
+        <v>-0.1739823762938002</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.3623839903209287</v>
+        <v>0.1137741507482346</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.4891224255448634</v>
+        <v>0.02392161697517281</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.4105046017137468</v>
+        <v>0.07143307881618455</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.4648656224488761</v>
+        <v>-0.09070591547327922</v>
       </c>
     </row>
     <row r="16">
@@ -4004,1637 +4004,1637 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2644</v>
+        <v>2641</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4679708978250616</v>
+        <v>0.5896046768480758</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4333817167360436</v>
+        <v>0.5519399423862126</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.233636588905803</v>
+        <v>0.5958700786548476</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.04551589917442556</v>
+        <v>0.3252576871968955</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3532340267315774</v>
+        <v>0.8231987523465136</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.03950841922231518</v>
+        <v>0.4745751083472172</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3393654410128946</v>
+        <v>0.1901214204770625</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.5962580870781622</v>
+        <v>-0.168757795876445</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.7214766880486465</v>
+        <v>-0.2455442218900075</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.8711558638874735</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.7637556669549141</v>
+        <v>-0.2742771552028387</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.7951333856964595</v>
+        <v>-0.2653155912773144</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.8044474049951091</v>
+        <v>-0.3397317046569981</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6644183634640655</v>
+        <v>-0.1884558050510492</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.7350224517605781</v>
+        <v>-0.2442123784944599</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.7215823392293927</v>
+        <v>-0.2649530160548679</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.6070090519781033</v>
+        <v>-0.233253023431601</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.8027944331371302</v>
+        <v>-0.4194901228049517</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.6024162042032373</v>
+        <v>-0.2205997650556739</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.4310952631078067</v>
+        <v>0.01623881978625263</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.1202698321480682</v>
+        <v>0.3794660283169762</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.135749960618611</v>
+        <v>0.3647977620587639</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1411284202392622</v>
+        <v>0.3433811303360059</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.2322751565880026</v>
+        <v>0.1812421360465422</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.006473</t>
+          <t>X &gt; -0.006475</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2506</v>
+        <v>2502</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3575693552932862</v>
+        <v>0.4621314003588708</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3790870937605746</v>
+        <v>0.4756473167884607</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1287165007865951</v>
+        <v>0.472645350166971</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.0695898543647786</v>
+        <v>0.2992649350093473</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1712759135338402</v>
+        <v>0.6416316935595461</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0241032974784261</v>
+        <v>0.5429247829498394</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.09136519435318746</v>
+        <v>0.4458941137940542</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3073419028825413</v>
+        <v>0.1238743584668001</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.6002386005820881</v>
+        <v>-0.1233048737692499</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.7157400482007858</v>
+        <v>-0.2203499929158426</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.8158998304766172</v>
+        <v>-0.3233928328310753</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.635170659493788</v>
+        <v>-0.09940658674786107</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.7025414951257289</v>
+        <v>-0.2352439951177914</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.7016480662374605</v>
+        <v>-0.2210602109941107</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.6207439314013854</v>
+        <v>-0.1222461748777519</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.5198163014392065</v>
+        <v>-0.05577671498686954</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.311930859559439</v>
+        <v>0.1032937616387386</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.711639523871419</v>
+        <v>-0.2853915901915371</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.5917271093801375</v>
+        <v>-0.1671905148635418</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.4610961056590455</v>
+        <v>0.03096197681809087</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.02363246034730082</v>
+        <v>0.4862390504745662</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.07562490049355119</v>
+        <v>0.4510445540988215</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.09638413900931653</v>
+        <v>0.4149028603204457</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.18835635596065</v>
+        <v>0.2527638660309819</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004195</t>
+          <t>X &gt; -0.004199</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2340</v>
+        <v>2336</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.5770418225578524</v>
+        <v>0.6399635054350483</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.242265024208038</v>
+        <v>0.3321121456162928</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.05120124822268934</v>
+        <v>0.2478900563508972</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1706834575764091</v>
+        <v>0.1466830606557892</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2989520978542686</v>
+        <v>0.7880888988317309</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2109598587325507</v>
+        <v>0.2457456013844848</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.02573227558514901</v>
+        <v>0.538786194515751</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.1948513444150493</v>
+        <v>0.258179261586406</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.596196124262157</v>
+        <v>-0.1008486092510665</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.8352596770661975</v>
+        <v>-0.3186283741484388</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.089367586875206</v>
+        <v>-0.576370437980934</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.9613595147022735</v>
+        <v>-0.4021530008194603</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.124461887753178</v>
+        <v>-0.5963773532771341</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.150621445123235</v>
+        <v>-0.6063341981671826</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.9325385531980643</v>
+        <v>-0.3665391916026977</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.207346032729333</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.9329707321537697</v>
+        <v>-0.4570373735214517</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.098054128483696</v>
+        <v>-0.6503759072716733</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.9424568197631942</v>
+        <v>-0.4964198454955095</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.8586186434940615</v>
+        <v>-0.3423913690299045</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.6506538857340445</v>
+        <v>-0.1392879252051529</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.7012233271167503</v>
+        <v>-0.1716422279823604</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.5723176507637504</v>
+        <v>-0.05643240023823637</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.8365784008307315</v>
+        <v>-0.3469960520619466</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001917</t>
+          <t>X &gt; -0.001922</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2182</v>
+        <v>2176</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8136983411134864</v>
+        <v>0.8992867115249368</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.9789215427636719</v>
+        <v>1.04282468595764</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8136297664599539</v>
+        <v>1.135522904289388</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7370393833808464</v>
+        <v>1.070574515047767</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9921580017426734</v>
+        <v>1.45987543673737</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.5427605514764124</v>
+        <v>1.003736468964391</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8880552426739072</v>
+        <v>1.422340153793144</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9091774763527098</v>
+        <v>1.326730348668193</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.476488399219491</v>
+        <v>0.9782902538726077</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1790499623303674</v>
+        <v>0.3458730762188864</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.425319267809833</v>
+        <v>0.09539333224931568</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.4044526133820341</v>
+        <v>0.1655813126486336</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.589330481862703</v>
+        <v>-0.05252092496140648</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.6924369444243652</v>
+        <v>-0.1364153449773937</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.5022399847481296</v>
+        <v>0.07952905223592666</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.6112494811124947</v>
+        <v>-0.06574879316796256</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.4898635356374399</v>
+        <v>-0.004899992351234062</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.8419100207332804</v>
+        <v>-0.3402130766951146</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.8277257523879413</v>
+        <v>-0.3283657993142555</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.7055346369866129</v>
+        <v>-0.1327570015842952</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.4889960530155264</v>
+        <v>0.08104849703497052</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.6292379541066069</v>
+        <v>-0.04006990727325643</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.6024522605000158</v>
+        <v>-0.02621483375958178</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.6053939624968905</v>
+        <v>-0.09644206334316863</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.0003613</t>
+          <t>X &gt; 0.0003539</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8382181251269429</v>
+        <v>0.8741619492930184</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.428465669522993</v>
+        <v>1.436075811185532</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.207583913578652</v>
+        <v>1.527363443233867</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.127541286540982</v>
+        <v>1.451369157968628</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.716775156739573</v>
+        <v>2.13282177533749</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.31951544215535</v>
+        <v>1.779992176726942</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.695932533573753</v>
+        <v>2.236762463356364</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.690013146561498</v>
+        <v>2.107545300493385</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.223950642733584</v>
+        <v>1.725411398886337</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.7234779154074218</v>
+        <v>1.252130364129478</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.4893777175522089</v>
+        <v>1.013710405611654</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4343940992433062</v>
+        <v>1.060123473137807</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.3657000801400017</v>
+        <v>0.9558287292033825</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2714787607793099</v>
+        <v>0.8842142390994994</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.2293146413673739</v>
+        <v>0.8702535018324511</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.02742691098855232</v>
+        <v>0.5763177273592177</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.06354203625262755</v>
+        <v>0.6001239957370004</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.3548798839530178</v>
+        <v>0.2013514591428631</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.7958461341278849</v>
+        <v>-0.2442312083949503</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.8253254627405227</v>
+        <v>-0.2265920799287784</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.7506669263628325</v>
+        <v>-0.1539578023828767</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.9937859020696607</v>
+        <v>-0.3768308117827672</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.9358402402273214</v>
+        <v>-0.3301436430972018</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.031950590309016</v>
+        <v>-0.4922826373866656</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.002639</t>
+          <t>X &gt; 0.00263</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.6808159062616923</v>
+        <v>0.7196683538566191</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.385426416445789</v>
+        <v>1.323549541707678</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.260317651878694</v>
+        <v>1.411914566241435</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.039704989109914</v>
+        <v>1.233554590877084</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.633892634724567</v>
+        <v>1.974901809187052</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.054994488218007</v>
+        <v>1.341636012343379</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.267728517675572</v>
+        <v>1.564698676871053</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.295108259823571</v>
+        <v>1.456220381069528</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.149640726324911</v>
+        <v>1.4514986196424</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.847099699570478</v>
+        <v>1.18162934658902</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9341550158491998</v>
+        <v>1.266339091295762</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.9618878423864743</v>
+        <v>1.406753554370631</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.9139308180622692</v>
+        <v>1.314377102450131</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.7258551225798087</v>
+        <v>1.154176060059164</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.430421602865529</v>
+        <v>0.8905481256512999</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.3163159911373228</v>
+        <v>0.1077543786671598</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.5827120164654147</v>
+        <v>-0.1840430907754538</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.26046361621934</v>
+        <v>-0.8911519393222989</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.5630480110691</v>
+        <v>-1.228261692319933</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.509574368914571</v>
+        <v>-1.123989643289619</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.248484294735789</v>
+        <v>-0.8640761744552563</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.567794249805765</v>
+        <v>-1.159867488467903</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.537052255039391</v>
+        <v>-1.13686179524688</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.580795837483294</v>
+        <v>-1.243843591522008</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.004918</t>
+          <t>X &gt; 0.004907</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1545</v>
+        <v>1554</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9395500678620721</v>
+        <v>1.00861451950238</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.014126248371966</v>
+        <v>1.880256245102728</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.241706174356992</v>
+        <v>2.254414144364063</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.169367145305024</v>
+        <v>2.208757890587776</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.986683655461142</v>
+        <v>3.118805613765467</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.02054285885513</v>
+        <v>2.10015173165268</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.273578159590024</v>
+        <v>2.364401608321089</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.059428213876025</v>
+        <v>2.097149795359506</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.626162196822278</v>
+        <v>1.750959323501469</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.532470546706413</v>
+        <v>1.632550137672695</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.65222305179271</v>
+        <v>1.750496189802639</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.797002982512417</v>
+        <v>1.960453107520436</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.997657562592849</v>
+        <v>2.166591894166636</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.88023303938111</v>
+        <v>2.021572345179784</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.776327948771872</v>
+        <v>1.892347587510358</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.315879334230914</v>
+        <v>1.464875484561333</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.092262181985348</v>
+        <v>1.206960075026785</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.3173350025282318</v>
+        <v>0.4050422140147205</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.2493720542996698</v>
+        <v>0.233404055060106</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.4102281518621922</v>
+        <v>0.44799050011909</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.7460514579087345</v>
+        <v>0.7814468996392492</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.3861682083583773</v>
+        <v>0.4488841202837079</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.8290195560004108</v>
+        <v>0.8855687986122831</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.5981573057496377</v>
+        <v>0.5947296756226876</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.007196</t>
+          <t>X &gt; 0.007183</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1280</v>
+        <v>1293</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.725948253363399</v>
+        <v>1.613981369673965</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.858352922195046</v>
+        <v>2.709937384197765</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.350835803665994</v>
+        <v>3.258226045082019</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.560661707003177</v>
+        <v>2.557325725072253</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.305952315536985</v>
+        <v>3.245900117991752</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.489057497773359</v>
+        <v>2.451267073777117</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.566529663303854</v>
+        <v>2.54506113328069</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.59719852743109</v>
+        <v>2.592747754038072</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.098145168805246</v>
+        <v>2.228322324451071</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.298476972971422</v>
+        <v>2.40069748328483</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.000499095305386</v>
+        <v>2.10320430460439</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.15501861549717</v>
+        <v>2.25755713343802</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.39530869292166</v>
+        <v>2.499476337123021</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.454524522219671</v>
+        <v>2.529900527876812</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.921951794938785</v>
+        <v>1.972394603973548</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.47750799924713</v>
+        <v>1.499343446243294</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.624047120986781</v>
+        <v>1.674279775715384</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.100254365243103</v>
+        <v>1.077358547583955</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.363467698833368</v>
+        <v>1.291820774729729</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.364064311860901</v>
+        <v>1.274388658303785</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.648228807910044</v>
+        <v>1.480339361872787</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.386342669118328</v>
+        <v>1.250497798927555</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.177062855775318</v>
+        <v>2.03550892767074</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.837032710280376</v>
+        <v>1.641351371896363</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.009474</t>
+          <t>X &gt; 0.009459</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1038</v>
+        <v>1048</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.847702504888652</v>
+        <v>2.672062537426122</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.612162347760204</v>
+        <v>4.403556831665753</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.98712039796586</v>
+        <v>4.900221910165776</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.27416637852312</v>
+        <v>4.175690890202709</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.083414073914774</v>
+        <v>4.995327576122932</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4.316181786729707</v>
+        <v>4.264649193066894</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.925912492152328</v>
+        <v>3.904779010154598</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.411059826025209</v>
+        <v>4.414682539682531</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.166287465955179</v>
+        <v>4.316326083863267</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.442990110529379</v>
+        <v>4.621833083927079</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.953690974065346</v>
+        <v>4.193350351640355</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.579521723289112</v>
+        <v>3.880117726804826</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.601397824371922</v>
+        <v>3.87027493771415</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.094059405940598</v>
+        <v>3.491099822409446</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.782143424501399</v>
+        <v>3.154399160620628</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.57619213164147</v>
+        <v>2.916777994422205</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.693036611028909</v>
+        <v>3.003737277353693</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.168939825519701</v>
+        <v>2.393753935550869</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.444157567552388</v>
+        <v>2.608216162696642</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.882382188458152</v>
+        <v>3.013642302412116</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.879882225879307</v>
+        <v>2.923297037672597</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.056659481790824</v>
+        <v>3.038974210373802</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.680490083811641</v>
+        <v>3.66428808496515</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.472991284461493</v>
+        <v>3.406729243347449</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.01175</t>
+          <t>X &gt; 0.01174</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.893399461910498</v>
+        <v>3.705530520046651</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.932221667296673</v>
+        <v>3.45962368434278</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.237664635700305</v>
+        <v>3.924831302352921</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.275644613766907</v>
+        <v>3.086728857844456</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.185184153672928</v>
+        <v>3.867409781364252</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.874018334788985</v>
+        <v>3.605351512714527</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.85300364840797</v>
+        <v>2.636853478177656</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.820122216108203</v>
+        <v>3.639570306236969</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.110675400513564</v>
+        <v>4.089494057899437</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.832155739421033</v>
+        <v>4.853858183970289</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.234484372865651</v>
+        <v>4.335977012234792</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.457602964436333</v>
+        <v>3.639526722077925</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.9533699137695</v>
+        <v>4.215524360033029</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.607758036077584</v>
+        <v>3.921092715088911</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.696812745969005</v>
+        <v>3.985206989920265</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.672270651722712</v>
+        <v>2.929595585854358</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.285551522217212</v>
+        <v>3.571983830845774</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.80711181466004</v>
+        <v>3.065965397325954</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.272069198075023</v>
+        <v>3.529183843377204</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.661863427778279</v>
+        <v>3.992526507341665</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.44761636224343</v>
+        <v>3.673838224866401</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.575890251021598</v>
+        <v>3.723053812363851</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.4304650886601</v>
+        <v>4.464200735453176</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.184307146370607</v>
+        <v>4.17768363171097</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.01403</t>
+          <t>X &gt; 0.01401</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.346373333852384</v>
+        <v>4.18607989649508</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.331085353393931</v>
+        <v>3.7824443541666</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.650254802765502</v>
+        <v>4.262766025145687</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.458067556485702</v>
+        <v>3.197177706463648</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.19895440023236</v>
+        <v>4.972092752484187</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.107965314764236</v>
+        <v>3.961385411811015</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.697038995091141</v>
+        <v>2.627878779025181</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.016271639794937</v>
+        <v>4.001527614839816</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.738270003818272</v>
+        <v>3.908592690347881</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.042031644075706</v>
+        <v>5.275712770064828</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.836858059400569</v>
+        <v>5.170237740417335</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.078875429115513</v>
+        <v>4.514740924966148</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.872646269607635</v>
+        <v>5.415889490110622</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.491822984215354</v>
+        <v>5.007911019731822</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.271379367145975</v>
+        <v>5.763456318357946</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.789088972795042</v>
+        <v>4.248083020883684</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.134405062654629</v>
+        <v>4.623435835995735</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.230842314105011</v>
+        <v>3.691829686105699</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.925966921866397</v>
+        <v>4.385525140088532</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.793323913943055</v>
+        <v>4.280622767256148</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.41052215492271</v>
+        <v>3.872922674821098</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.2758902510216</v>
+        <v>3.638015743920128</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>4.132416245554928</v>
+        <v>4.360883456035573</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.998449243185675</v>
+        <v>4.039000052800411</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01631</t>
+          <t>X &gt; 0.01629</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.168483515371278</v>
+        <v>4.17280413361285</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.428027203836876</v>
+        <v>2.92489328989295</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.00420693776735</v>
+        <v>2.672203196017399</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.494092674916892</v>
+        <v>2.280201798812385</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.389539524884846</v>
+        <v>4.209052476348319</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.56230692802076</v>
+        <v>3.363982074330373</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.9931980007227</v>
+        <v>2.888414593167816</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.946223878484837</v>
+        <v>4.916366888197871</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.582031547214953</v>
+        <v>4.765607539298209</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.243192950285973</v>
+        <v>6.518024600611952</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.300214052894148</v>
+        <v>5.70532116185678</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.6015863533001</v>
+        <v>4.136559624397741</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.709661608959195</v>
+        <v>5.252904829462182</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.082903219328017</v>
+        <v>4.598991254844485</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>5.250317731078091</v>
+        <v>5.742394682290062</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>3.81630708709816</v>
+        <v>4.275301135186801</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.696588733082152</v>
+        <v>5.185619506423258</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.780389002891795</v>
+        <v>4.241376374892482</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.807639410185296</v>
+        <v>5.26719762840743</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4.994485220153322</v>
+        <v>5.481784073466414</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>4.249099295595009</v>
+        <v>4.711499815493397</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.767573821001314</v>
+        <v>4.230657780353518</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>4.984511304967072</v>
+        <v>5.285651292001056</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>5.243982812113366</v>
+        <v>5.326352054303889</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.01859</t>
+          <t>X &gt; 0.01856</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.009399191986752</v>
+        <v>2.968429782945911</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.413538649794575</v>
+        <v>3.45962368434278</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.438573787955697</v>
+        <v>4.661932039453653</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.464536024670601</v>
+        <v>4.806630577746169</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.099188901877014</v>
+        <v>6.496674403248804</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.315711738220706</v>
+        <v>4.688006043644918</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.282679310487985</v>
+        <v>4.630024768512939</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.974911215488596</v>
+        <v>6.290706290706282</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.52378755996488</v>
+        <v>5.927234708989907</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.475009814962874</v>
+        <v>6.851084933672283</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.76384778224795</v>
+        <v>6.140518965475636</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.007265866484687</v>
+        <v>4.389735536802867</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.347157986820683</v>
+        <v>5.731845876354548</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.140857435497246</v>
+        <v>4.500810832120457</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>5.206852068951171</v>
+        <v>5.538558170137115</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>3.830795641140462</v>
+        <v>4.134260223354815</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.68210017903985</v>
+        <v>5.013180794430788</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.345732381622604</v>
+        <v>3.897495706468206</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.793150856142994</v>
+        <v>5.340459162115209</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5.47260750354944</v>
+        <v>6.046446098574691</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>5.42267217302183</v>
+        <v>5.97040208859444</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>5.100520792893512</v>
+        <v>5.649539320938906</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>6.113911761533217</v>
+        <v>6.630274543318031</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>6.038079508309941</v>
+        <v>6.468135549028567</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.02086</t>
+          <t>X &gt; 0.02084</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.692486219901369</v>
+        <v>4.561348807057598</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.357709421551554</v>
+        <v>4.009631573800206</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.462900249063772</v>
+        <v>4.283989459676214</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.367230180238316</v>
+        <v>4.609018453528542</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.88329155954289</v>
+        <v>6.168322698750309</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.835689844405707</v>
+        <v>4.796204316980813</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.681025111132634</v>
+        <v>4.612743099855116</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.637381567614128</v>
+        <v>6.142685041767599</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.752942823602908</v>
+        <v>5.047372361237642</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.831878999418265</v>
+        <v>6.086183251339406</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.180012715654264</v>
+        <v>5.440987073283196</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.358053435663052</v>
+        <v>3.329542733490797</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.395385195967442</v>
+        <v>4.661133796468157</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.248380393594921</v>
+        <v>3.495468542374503</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4.442088947866218</v>
+        <v>4.342366148257028</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.567340067340069</v>
+        <v>2.457186986648551</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.35934885628852</v>
+        <v>3.270737767584102</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>2.328582226541414</v>
+        <v>2.220422469761942</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.470399533391664</v>
+        <v>3.352315889568274</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>3.657245343359691</v>
+        <v>3.566902334627258</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>3.731983126010952</v>
+        <v>3.611078628353546</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>3.347495189293205</v>
+        <v>3.230105708844754</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>4.547895827701183</v>
+        <v>4.391171386783675</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>4.163421599169261</v>
+        <v>3.923221994940697</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.02314</t>
+          <t>X &gt; 0.02312</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.699812227227376</v>
+        <v>5.581460863130282</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.632434696276832</v>
+        <v>4.60562702012713</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.6596171124473</v>
+        <v>4.810786932834105</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.045564191905662</v>
+        <v>5.313275244974776</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.907575917160578</v>
+        <v>7.227498126773249</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.995641004356862</v>
+        <v>6.289541221822439</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.956293053067242</v>
+        <v>6.224386216888988</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.044381974614531</v>
+        <v>6.284429277129995</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.25436732502741</v>
+        <v>4.952504172215569</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.045554213093482</v>
+        <v>6.711197202543673</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.220712756354303</v>
+        <v>5.888541706199099</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.110461521404481</v>
+        <v>3.787142233479635</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.185101652350554</v>
+        <v>4.49706763427703</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.062923874805065</v>
+        <v>5.343724083792829</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>4.771080943524872</v>
+        <v>5.026533205557421</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>3.533966033966031</v>
+        <v>3.763019706128901</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.49894999588966</v>
+        <v>4.754029805352801</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.661508559467741</v>
+        <v>3.891218692891918</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.976301039293169</v>
+        <v>5.200571430986599</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>6.262047948162291</v>
+        <v>6.510048386994498</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>6.085802146496626</v>
+        <v>6.307567389263397</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>5.277355452486795</v>
+        <v>5.502477860008831</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>6.650731263869943</v>
+        <v>6.841002856236123</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>7.043827365596293</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.02542</t>
+          <t>X &gt; 0.02539</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>221</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.087659673898351</v>
+        <v>6.18588005921972</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.847905499982929</v>
+        <v>5.034995847950242</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.862375138734741</v>
+        <v>4.232790433841465</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.149421119292001</v>
+        <v>3.640388235033242</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.981051461224361</v>
+        <v>6.532250909413541</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.45308552062491</v>
+        <v>3.974252388714795</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.133625524517363</v>
+        <v>3.63165906426488</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.117857518678314</v>
+        <v>5.589182059770287</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.25436732502741</v>
+        <v>4.812133593888788</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.291406400122135</v>
+        <v>5.826036849800666</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.37542079341528</v>
+        <v>7.908226615536222</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.191694014401676</v>
+        <v>6.726667285499317</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.330975386459578</v>
+        <v>7.874218606962565</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>8.014873885578609</v>
+        <v>8.530961921095077</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>8.714196651346462</v>
+        <v>9.206273602558433</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>6.593651446592617</v>
+        <v>7.052645494681258</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>7.817200372963569</v>
+        <v>8.306231146304675</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>5.902404918011158</v>
+        <v>6.363392290011845</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>6.570784986718287</v>
+        <v>7.030343204940422</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>7.210119484469118</v>
+        <v>7.69741833778221</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>7.57255069206871</v>
+        <v>8.034951211967098</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>7.949193418442412</v>
+        <v>8.412277377794616</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>10.03362288205568</v>
+        <v>10.46586661420421</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>9.052813253266798</v>
+        <v>9.398750244349138</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.0277</t>
+          <t>X &gt; 0.02767</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>166</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.202526380543937</v>
+        <v>7.300746765865306</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.662930305085688</v>
+        <v>5.850020653053001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.634549810271572</v>
+        <v>7.004965105378297</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.319186152274604</v>
+        <v>5.810153268015846</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.20026314960684</v>
+        <v>9.751462597796021</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>5.772771504378937</v>
+        <v>6.293938372468823</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.000822820488587</v>
+        <v>5.498856360236104</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.529840291398145</v>
+        <v>7.001164832490119</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.968917834758642</v>
+        <v>6.52668410362002</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.810459990047448</v>
+        <v>9.345090439725979</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.89174854787202</v>
+        <v>11.42455436999296</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.805770228761375</v>
+        <v>9.340743499859016</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>9.489837077567906</v>
+        <v>10.03308029807089</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>12.28080639389241</v>
+        <v>12.79689442940887</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>13.42989201197449</v>
+        <v>13.92196896318647</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>10.40982110259219</v>
+        <v>10.86881515068083</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>11.48072324272314</v>
+        <v>11.96975401606425</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>9.568653623239314</v>
+        <v>10.02964099524</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>9.182135365609419</v>
+        <v>9.641693583831554</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>9.971390814131667</v>
+        <v>10.45868966744476</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>10.63366392327408</v>
+        <v>11.09606444317247</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>11.16022760041918</v>
+        <v>11.62331155977139</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>11.43470231290124</v>
+        <v>11.86694604504977</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>10.15405078256953</v>
+        <v>10.49998777365187</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.02998</t>
+          <t>X &gt; 0.02995</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.959152886568035</v>
+        <v>8.057373271889404</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>6.024376088218219</v>
+        <v>6.211466436185532</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.78635703918723</v>
+        <v>8.156772334293954</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.473403019744488</v>
+        <v>5.96437013548573</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>12.33761254719721</v>
+        <v>12.88881199538639</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.324578733294601</v>
+        <v>9.845745601384486</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.552630049404243</v>
+        <v>5.05066358915176</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.874418604651169</v>
+        <v>6.345743145743143</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.115905786565868</v>
+        <v>5.673672055427247</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.142990110529382</v>
+        <v>9.677620560207913</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.61704975269129</v>
+        <v>13.14985557481224</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9.938300349243306</v>
+        <v>10.47327362034095</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.81513828238719</v>
+        <v>13.35838150289018</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>14.9940594059406</v>
+        <v>15.51014744145707</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>16.73591610836004</v>
+        <v>17.22799305957201</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>15.73030303030303</v>
+        <v>16.18929707839168</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>17.19638589332556</v>
+        <v>17.68541666666666</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>15.49154518950438</v>
+        <v>15.95253256150507</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>14.90743657042871</v>
+        <v>15.36699478865084</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>15.09428238039673</v>
+        <v>15.58158123370983</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>15.3517362124307</v>
+        <v>15.81413673232909</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>16.87589025102159</v>
+        <v>17.3389742103738</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>17.95036496350366</v>
+        <v>18.38260869565219</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>15.47453271028038</v>
+        <v>15.82046970136272</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.03226</t>
+          <t>X &gt; 0.03222</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>8.359152886568033</v>
+        <v>8.457373271889402</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.024376088218212</v>
+        <v>4.211466436185525</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.586357039187227</v>
+        <v>6.956772334293952</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.873403019744487</v>
+        <v>4.364370135485728</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.53761254719721</v>
+        <v>12.08881199538639</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.724578733294592</v>
+        <v>8.245745601384478</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.952630049404242</v>
+        <v>4.450663589151759</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.674418604651166</v>
+        <v>4.14574314574314</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.71590578656587</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.942990110529379</v>
+        <v>5.47762056020791</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.217049752691302</v>
+        <v>9.749855574812244</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.938300349243306</v>
+        <v>9.473273620340947</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.81513828238719</v>
+        <v>11.35838150289018</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.5940594059406</v>
+        <v>13.11014744145707</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>13.93591610836004</v>
+        <v>14.42799305957201</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>13.53030303030303</v>
+        <v>13.98929707839167</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>17.39638589332556</v>
+        <v>17.88541666666666</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>17.29154518950438</v>
+        <v>17.75253256150506</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>14.5074365704287</v>
+        <v>14.96699478865084</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>15.69428238039673</v>
+        <v>16.18158123370982</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>15.1517362124307</v>
+        <v>15.61413673232909</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>17.0758902510216</v>
+        <v>17.5389742103738</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>19.35036496350365</v>
+        <v>19.78260869565218</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>17.27453271028038</v>
+        <v>17.62046970136272</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.03453</t>
+          <t>X &gt; 0.0345</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>6.653270533626852</v>
+        <v>7.326938489280714</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-1.034447441193542</v>
+        <v>-1.61462052033621</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.001878254930425</v>
+        <v>0.0292361024098966</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-1.714832274373165</v>
+        <v>-2.012441458717163</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.243494900138387</v>
+        <v>9.306203299734221</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>6.95987285094165</v>
+        <v>6.564586181094619</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>3.246747696463061</v>
+        <v>2.87095344422422</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>5.909712722298224</v>
+        <v>5.464583725453281</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.53943519833058</v>
+        <v>2.693961910499709</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.178284228176437</v>
+        <v>6.245736502236888</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2.511167399750121</v>
+        <v>3.619420792203556</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2.232417996302125</v>
+        <v>1.893563475413409</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>2.57984416474013</v>
+        <v>2.227946720281487</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>8.241118229470018</v>
+        <v>7.776814108123723</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>9.053563167183562</v>
+        <v>9.993210450876354</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>9.647950089126553</v>
+        <v>10.55451446969602</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>12.45520942273733</v>
+        <v>13.3491847826087</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>13.82095695421026</v>
+        <v>13.21630067744709</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>9.625083629252224</v>
+        <v>10.53221217995518</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>12.7531059098085</v>
+        <v>13.64534934965185</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>13.68114797713658</v>
+        <v>14.52718021058995</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>15.0758902510216</v>
+        <v>15.90129305095352</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>16.82095319879777</v>
+        <v>16.1449275362319</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>15.27453271028038</v>
+        <v>14.53351317962358</v>
       </c>
     </row>
   </sheetData>
@@ -5824,493 +5824,493 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.03153</t>
+          <t>X &lt; -0.03151</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.6996706428437278</v>
+        <v>0.08056167768651079</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-5.446212147075897</v>
+        <v>-4.513171244973883</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.939298215657814</v>
+        <v>2.927786827047576</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.579285372685661</v>
+        <v>9.581761439833556</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8905537236678001</v>
+        <v>2.059826488140018</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.077519909765179</v>
+        <v>2.216760094138102</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.246747696463061</v>
+        <v>4.320228806543071</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.909712722298224</v>
+        <v>6.913859087772117</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.421788139507044</v>
+        <v>8.491063359775076</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.5900489340588</v>
+        <v>10.59356258919343</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.45234387033836</v>
+        <v>6.517971516841222</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.52653564336096</v>
+        <v>13.48776637396413</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>15.81513828238719</v>
+        <v>16.72070034346989</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.5940594059406</v>
+        <v>16.47246628203678</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>11.99473963777181</v>
+        <v>12.89176117551404</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>11.11853832442068</v>
+        <v>12.00378983201486</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>8.043444716854978</v>
+        <v>9.001358695652179</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>12.35036871891614</v>
+        <v>13.21630067744709</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>15.5074365704287</v>
+        <v>16.32931362923055</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>20.10604708627908</v>
+        <v>20.89172616124605</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>21.03408915360718</v>
+        <v>21.77355702218416</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>26.84059613337454</v>
+        <v>27.49549594950424</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>27.11507084585659</v>
+        <v>27.73913043478262</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>27.03923859263332</v>
+        <v>27.57699144049315</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02925</t>
+          <t>X &lt; -0.02924</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.4493577517298419</v>
+        <v>-1.459293394777262</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.91179412454774</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.096995337059568</v>
+        <v>2.248439000960616</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.703190253787042</v>
+        <v>6.864370135485728</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.112080632303595</v>
+        <v>2.422145328719729</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.299046818400974</v>
+        <v>3.620745601384478</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.654757708978707</v>
+        <v>4.908996922485095</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.376546264225631</v>
+        <v>4.604076479076475</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.3542036589063</v>
+        <v>4.732005388760584</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.708947557337886</v>
+        <v>6.019287226874575</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.791517837797684</v>
+        <v>2.124855574812244</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.768087583285862</v>
+        <v>7.05660695367429</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.900244665365911</v>
+        <v>10.10838150289018</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>10.8068253633874</v>
+        <v>11.94348077479041</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>9.084852278572818</v>
+        <v>10.21965972623867</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>9.679239200515809</v>
+        <v>10.78096374505833</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>6.353832701836197</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>8.376651572483098</v>
+        <v>9.502532561505063</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>9.65637274064148</v>
+        <v>10.75866145531749</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>13.03470791231163</v>
+        <v>14.09824790037648</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>13.55599153157963</v>
+        <v>14.57247006566243</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>17.73546471910669</v>
+        <v>18.6639742103738</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>19.0737692188228</v>
+        <v>19.94927536231884</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>18.99793696559953</v>
+        <v>19.78713636802937</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.02698</t>
+          <t>X &lt; -0.02696</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>132</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.9046074320225728</v>
+        <v>1.002827817343942</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.490775426933297</v>
+        <v>-5.303685078965984</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1106126577824753</v>
+        <v>0.259802637324249</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.96431211065358</v>
+        <v>3.455279226394822</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.3557943653790332</v>
+        <v>0.9069938135682136</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.30033630905217</v>
+        <v>1.821503177142056</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.801114897889093</v>
+        <v>3.29914843763661</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.280479210711775</v>
+        <v>3.751803751803749</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.806814877474963</v>
+        <v>2.364581146336342</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2763234438627151</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-5.510222974581424</v>
+        <v>-4.977417152460482</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.001093590150639</v>
+        <v>-1.466120319052997</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.09395262670371807</v>
+        <v>0.4492905937992688</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.200120012001207</v>
+        <v>1.716208047517675</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.2155990431551089</v>
+        <v>0.2764779080568616</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.3787878787878824</v>
+        <v>0.8377819268765236</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-1.270280773341106</v>
+        <v>-0.78125</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.1400300379892272</v>
+        <v>0.6010174099899146</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.113497176489311</v>
+        <v>1.573055394711446</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>2.815494501608853</v>
+        <v>3.302793354921945</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2.272948333642823</v>
+        <v>2.735348853541211</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>7.50013267526402</v>
+        <v>7.963216634616224</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>8.532183145321824</v>
+        <v>8.964426877470352</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>9.213926649674313</v>
+        <v>9.559863640756653</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.0247</t>
+          <t>X &lt; -0.02469</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>174</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.7672838950411602</v>
+        <v>-0.6690635097197912</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.8159418113874821</v>
+        <v>-0.4455265162807578</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.494092674916892</v>
+        <v>2.985059790658134</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.434164271335149</v>
+        <v>0.9853637195243294</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.345268388466998</v>
+        <v>2.866435256556883</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.596308210323777</v>
+        <v>6.094341750071294</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.318096765570701</v>
+        <v>5.789421306662675</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.635446016450928</v>
+        <v>4.193212285312306</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.862530340414438</v>
+        <v>3.397160790092968</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.8863985231707616</v>
+        <v>-0.3535927010498199</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.5589900044157119</v>
+        <v>1.093963275513353</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.309391155950401</v>
+        <v>2.852634376453388</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.513599635825656</v>
+        <v>2.029687671342124</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.8554563382450979</v>
+        <v>1.347533289457068</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.449843260188089</v>
+        <v>1.90883730827673</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.9829244515020363</v>
+        <v>-0.49389367816093</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.5130525116450499</v>
+        <v>-0.05206513964436255</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-1.446586418077047</v>
+        <v>-0.9870281998549117</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.4643973229254712</v>
+        <v>0.9516961762385634</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.07814884504055897</v>
+        <v>0.3842516748578291</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>3.868993699297462</v>
+        <v>4.332077658649666</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>5.867606342814</v>
+        <v>6.299850074962528</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>7.515912020625201</v>
+        <v>7.861849011707541</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.02242</t>
+          <t>X &lt; -0.02241</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.9046074320225728</v>
+        <v>0.8142197449184465</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.16177109792897</v>
+        <v>-0.26156260945762</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.8634133162435091</v>
+        <v>0.9733698446673955</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.180762327103793</v>
+        <v>2.455656442539677</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.113370122954791</v>
+        <v>0.9352850244320337</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.897738906454769</v>
+        <v>3.166907427110623</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6.15609325286745</v>
+        <v>6.106265248902794</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.579180509413071</v>
+        <v>5.386407046158077</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.754866825526904</v>
+        <v>4.269522677833891</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.981951149490413</v>
+        <v>3.888408941950651</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.091508627150183</v>
+        <v>2.085955159874487</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.111460522403483</v>
+        <v>3.46912424274759</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.152800620049526</v>
+        <v>4.843858681313407</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.065920877802064</v>
+        <v>4.180686860544199</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.5419767144206489</v>
+        <v>2.668656959986947</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.2705627705627691</v>
+        <v>2.400085460134413</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-2.893657396717728</v>
+        <v>-0.6083592669432889</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.431398533439342</v>
+        <v>-1.156181131440988</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-4.514208451216319</v>
+        <v>-2.186532182303523</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-3.461561775447429</v>
+        <v>-1.142070218572343</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-4.437008376313891</v>
+        <v>-2.124452479289175</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.049650874519521</v>
+        <v>1.119887073444339</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.5235251366638281</v>
+        <v>2.608334836731018</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>2.179294615042281</v>
+        <v>4.105946879785947</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.02014</t>
+          <t>X &lt; -0.02013</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3536498815980593</v>
+        <v>-0.7373462000578002</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.034447441193542</v>
+        <v>-0.9832530357616704</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.05032116150481158</v>
+        <v>-0.2577491178512687</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.696932431509197</v>
+        <v>2.120145713043485</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4070241310034746</v>
+        <v>-0.4656434501581543</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.1259628163395732</v>
+        <v>0.02132315914025185</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.160242506151647</v>
+        <v>3.186637186511497</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.18998953890722</v>
+        <v>2.881716743102878</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.8473936758392284</v>
+        <v>1.35948063628534</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.458561044785434</v>
+        <v>2.213594157567648</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.3485376419646613</v>
+        <v>1.165697158970659</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.7618297610080162</v>
+        <v>1.879214214400349</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.022750739134594</v>
+        <v>2.414487113451223</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1096303401966523</v>
+        <v>1.836220048717792</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.2024921961382375</v>
+        <v>1.814131673433394</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.3001467966865903</v>
+        <v>2.04540268895272</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-3.894271546120812</v>
+        <v>-1.35880775577558</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.653091488696312</v>
+        <v>-1.161658857636844</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.783220869017669</v>
+        <v>-1.277229633791407</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-3.250354297803959</v>
+        <v>-0.7326101854320868</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-4.138921227015672</v>
+        <v>-1.630087690113157</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.792621859705044</v>
+        <v>0.6049808110338759</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.172126385977322</v>
+        <v>1.178648299612576</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.482145167027781</v>
+        <v>2.666674321824757</v>
       </c>
     </row>
     <row r="12">
@@ -6320,243 +6320,243 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6493941219789718</v>
+        <v>-0.9819798278410587</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.6992706354285119</v>
+        <v>-0.6888031055934363</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1419125947427844</v>
+        <v>-0.05670475465483094</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.132662279003739</v>
+        <v>2.585394394245839</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.517669527254192</v>
+        <v>0.423043801316318</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.4197354284512826</v>
+        <v>0.3104356283386593</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.781689878464071</v>
+        <v>2.749854963814833</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.933677863910418</v>
+        <v>2.444934520406214</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.975165045825122</v>
+        <v>2.30332165111458</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.911651079190349</v>
+        <v>3.394062608725427</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.761209296850851</v>
+        <v>2.318588728451054</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.052260463203424</v>
+        <v>2.850632110906986</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.06869953594844</v>
+        <v>3.083448888334921</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.562720374601568</v>
+        <v>2.835214826901812</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.9045770770210098</v>
+        <v>2.422602223992499</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.498963998964001</v>
+        <v>3.253448021787896</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.3443548474151896</v>
+        <v>1.532316936208446</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1642952663360759</v>
+        <v>2.208058167974073</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.3364963994885315</v>
+        <v>2.692062174095582</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.5233422094565583</v>
+        <v>2.906648619154566</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.5890045283100491</v>
+        <v>1.800120559822346</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.4747506498819973</v>
+        <v>3.072666932745769</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.7492253623640508</v>
+        <v>3.046759639048403</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.812994248741916</v>
+        <v>4.232329539637647</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01559</t>
+          <t>X &lt; -0.01558</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5307992665420116</v>
+        <v>-0.7081596079291899</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.8090650834335307</v>
+        <v>0.8599925132830322</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.524156082249426</v>
+        <v>1.192599998693048</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.682015459935876</v>
+        <v>3.094528865644463</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.671583839063238</v>
+        <v>1.45842650785805</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.09778447492139</v>
+        <v>1.842117483470652</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.196649188160222</v>
+        <v>3.994881276226593</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.439968843885609</v>
+        <v>3.689960832817974</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.481456025800313</v>
+        <v>3.591132372887564</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.143947048328428</v>
+        <v>4.382382464969815</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.982599991925746</v>
+        <v>3.294073261887078</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.421553937760059</v>
+        <v>3.924520785873831</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.733798569468526</v>
+        <v>4.396930255724641</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.034250793500405</v>
+        <v>3.921938824677014</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2.615341945680619</v>
+        <v>3.693299182020993</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>2.73125996810208</v>
+        <v>4.027845831226138</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>1.640405032081539</v>
+        <v>3.01693594104308</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.774798778021129</v>
+        <v>3.564323944725011</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.751455709184683</v>
+        <v>3.552028802256281</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.938301519152709</v>
+        <v>3.766615247315265</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.4388175521436182</v>
+        <v>2.292141267476474</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.080674940016813</v>
+        <v>3.124008223979246</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>1.594384102259632</v>
+        <v>3.367642709257623</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.518551849036356</v>
+        <v>3.659018454197181</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.01331</t>
+          <t>X &lt; -0.0133</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.425047498788423</v>
+        <v>-1.432534984991328</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2183984782557715</v>
+        <v>0.156420564625904</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8483994283972507</v>
+        <v>0.9200750865875236</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.025618819359124</v>
+        <v>2.712993988696738</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.148402527929392</v>
+        <v>1.153032178872628</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.720725168747379</v>
+        <v>1.676938261934936</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.260915213180738</v>
+        <v>3.267177350619654</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.368060223148277</v>
+        <v>3.696201861339475</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.40954740506298</v>
+        <v>3.640644532491464</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.178057547908956</v>
+        <v>4.495969184061124</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.452117190070879</v>
+        <v>4.768204198665458</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.751402468703802</v>
+        <v>5.225567198322601</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.169666220730157</v>
+        <v>5.762051227660812</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.370552662202641</v>
+        <v>5.14684468916348</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4.67580050142363</v>
+        <v>5.565607738471094</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>4.692152741285682</v>
+        <v>5.759939280226533</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.980200922227297</v>
+        <v>5.105600152905204</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>4.068038445766419</v>
+        <v>5.523174763339924</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3.127860462528901</v>
+        <v>4.636719559293034</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>3.507384499857224</v>
+        <v>5.034792242884137</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.386803649810275</v>
+        <v>3.733402787374963</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>3.081670597842404</v>
+        <v>4.575671458080215</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.585432400883228</v>
+        <v>4.085360989230161</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.702278375020263</v>
+        <v>4.657166949069129</v>
       </c>
     </row>
     <row r="15">
@@ -6566,79 +6566,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.749437064809605</v>
+        <v>-2.689913549816026</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.514584950742815</v>
+        <v>-2.00558782738036</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.166889714059529</v>
+        <v>-1.864933092062635</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2824411360996706</v>
+        <v>-0.2867926552119471</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.07927056968591</v>
+        <v>-1.95769963252058</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.080616071900209</v>
+        <v>-1.025572228072889</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.069513166287365</v>
+        <v>1.125082193802925</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.252340682573241</v>
+        <v>2.525588106983456</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.780840851500933</v>
+        <v>2.963594536047395</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3.306626474165746</v>
+        <v>3.56289187803737</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.093673129314674</v>
+        <v>3.370010613571935</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.97726138820434</v>
+        <v>3.403506178480477</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3.477475944724851</v>
+        <v>3.994040417618862</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3.094059405940598</v>
+        <v>3.745806356185753</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>3.085266757710684</v>
+        <v>3.838845772750297</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>3.192640692640694</v>
+        <v>4.090072272190127</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.571710568650232</v>
+        <v>3.521075581395351</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.629207527166713</v>
+        <v>3.853307755303518</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.358085921078057</v>
+        <v>3.602653703379524</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.5709057570201</v>
+        <v>2.731968830609048</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.8660219267164067</v>
+        <v>2.009485569538391</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.114851289982631</v>
+        <v>2.244400566962945</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.226988340127022</v>
+        <v>2.488035052241322</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.31349374924141</v>
+        <v>3.042829949809921</v>
       </c>
     </row>
     <row r="16">
@@ -6648,1637 +6648,1637 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>731</v>
+        <v>759</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.617654753268248</v>
+        <v>-2.425675348347134</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.609503693202548</v>
+        <v>-2.014551960660725</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.062069773398271</v>
+        <v>-1.692373526415643</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.133436925535953</v>
+        <v>-0.8393092337652561</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.700417548562015</v>
+        <v>-2.297521775967091</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.555859023203354</v>
+        <v>-1.352151901900676</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5494219341798896</v>
+        <v>-0.3075492886406224</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4035567715458299</v>
+        <v>0.8329967594093759</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.12903848150431</v>
+        <v>1.486549847805698</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.587312955946622</v>
+        <v>2.004558799366912</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.314176975673519</v>
+        <v>1.751169635259032</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.582623194660549</v>
+        <v>2.131617904178007</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.964249089500726</v>
+        <v>2.59359832286389</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.469572401836629</v>
+        <v>2.213958216752729</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1.90582034912611</v>
+        <v>2.714458236970174</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.816212743025332</v>
+        <v>2.750138077077615</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.271898889221589</v>
+        <v>2.252039531318438</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.851052713444183</v>
+        <v>2.907591694225168</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.519748471933489</v>
+        <v>2.596429742658728</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.6122030370314775</v>
+        <v>1.628361785615212</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2039409421520588</v>
+        <v>0.7981051948783602</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.4165858091699235</v>
+        <v>0.7229426729230752</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.005312191079106299</v>
+        <v>1.177345537757446</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.1924533669151245</v>
+        <v>1.621787224419371</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.006473</t>
+          <t>X &lt; -0.006475</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>869</v>
+        <v>898</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.805984728110865</v>
+        <v>-1.60034037960893</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.96643906677604</v>
+        <v>-1.402296049940986</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.390654455065643</v>
+        <v>-0.992173281688288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.8906936430863581</v>
+        <v>-0.5856853584099397</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.686783310110037</v>
+        <v>-1.305194663881089</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.499817124012658</v>
+        <v>-1.259248849225962</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.236092620331085</v>
+        <v>-0.9444529480291521</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.5937056761313357</v>
+        <v>-0.13949547800825</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.4834546933552843</v>
+        <v>0.8763357624194796</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7462122048907176</v>
+        <v>1.190162180629663</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.135346645671738</v>
+        <v>1.573384986576954</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7415224436046444</v>
+        <v>1.296803032105657</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.229407557415954</v>
+        <v>1.846727784799164</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.238478278207566</v>
+        <v>1.931457097394919</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.155708973722525</v>
+        <v>1.91522946356757</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.8294975067126984</v>
+        <v>1.699618942986568</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.1202063766397075</v>
+        <v>0.9298117832038528</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.166113659009554</v>
+        <v>2.017793382814716</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.15185544269567</v>
+        <v>2.010280027274597</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.5331776623299831</v>
+        <v>1.336964141589952</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4696677001124527</v>
+        <v>0.4365562661803679</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.5455136615215537</v>
+        <v>0.4278630992626944</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.1559641504204023</v>
+        <v>0.8493495187889977</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.001646806405474877</v>
+        <v>1.199534289335993</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004195</t>
+          <t>X &lt; -0.004199</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1035</v>
+        <v>1064</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.956535275125901</v>
+        <v>-1.669967552080628</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.278128728737464</v>
+        <v>-0.792278882166535</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.736690212500335</v>
+        <v>-0.2679467668296454</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5281413817999123</v>
+        <v>-0.1112852952258834</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.679778757150615</v>
+        <v>-1.323173023340203</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7198657111498505</v>
+        <v>-0.323542788128627</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.201959322576435</v>
+        <v>-0.931358882758353</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.8038422649140529</v>
+        <v>-0.3935826969534872</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.3004468493678019</v>
+        <v>0.6706758007455988</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7835698206743018</v>
+        <v>1.185485728747238</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.444102892787924</v>
+        <v>1.832252578557565</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.261971846827848</v>
+        <v>1.742936541689254</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.877940214754339</v>
+        <v>2.313437682665459</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.946716410771508</v>
+        <v>2.439735456438342</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.57842818565473</v>
+        <v>2.132112909759279</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>2.172815107597721</v>
+        <v>2.787049887380434</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.459187825692709</v>
+        <v>2.02773876404494</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.740820551823219</v>
+        <v>2.456652411692332</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.666856860283772</v>
+        <v>2.390215762433606</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.27399252532426</v>
+        <v>1.949371495882104</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.02130142982201</v>
+        <v>1.813761849479974</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.9454554684129093</v>
+        <v>1.796009857653345</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.9300751084311827</v>
+        <v>1.815472545417443</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.433953000135446</v>
+        <v>2.368590002114587</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001917</t>
+          <t>X &lt; -0.001922</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1193</v>
+        <v>1224</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.054870485719107</v>
+        <v>-1.83252900824089</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.430093418882862</v>
+        <v>-1.915569394433362</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.236385435729161</v>
+        <v>-1.78589867547803</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.151701582765973</v>
+        <v>-1.726835076240654</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.693543231697262</v>
+        <v>-2.246692890607093</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.042395281793418</v>
+        <v>-1.601159936074801</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.730521668952839</v>
+        <v>-2.31480872355182</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.75726622351312</v>
+        <v>-2.212563043181937</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.793733777558188</v>
+        <v>-1.351735110696531</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6387366287832705</v>
+        <v>-0.1933892117790563</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.1132100964285669</v>
+        <v>0.3231454770923747</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.05667031295283209</v>
+        <v>0.4537296463995801</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.496613554809656</v>
+        <v>0.9675020240628172</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6946461620177118</v>
+        <v>1.207867311163909</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.4556143480918067</v>
+        <v>1.014312277813055</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.6308897863801448</v>
+        <v>1.249883397609921</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.3293280559408132</v>
+        <v>0.9017033116178084</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.895065725967072</v>
+        <v>1.501718229257513</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.110957106891398</v>
+        <v>1.716180456403286</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.7110468397429131</v>
+        <v>1.279301103416664</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.5037898587006069</v>
+        <v>1.168333961342938</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.5955884907533644</v>
+        <v>1.305695254419483</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.7862409065044886</v>
+        <v>1.517302573203196</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.7104086532812133</v>
+        <v>1.568182119663376</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.0003613</t>
+          <t>X &lt; 0.0003539</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1339</v>
+        <v>1369</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.780728065812923</v>
+        <v>-1.504781022142623</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.747031208877843</v>
+        <v>-2.187369080553914</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.507532677653302</v>
+        <v>-2.059239310538651</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.435321812470278</v>
+        <v>-1.996619675285743</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.402685960265472</v>
+        <v>-2.854419445661648</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.95204561323267</v>
+        <v>-2.479145228309847</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.574629099214128</v>
+        <v>-3.12866683297343</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.554110148149434</v>
+        <v>-2.996906053674621</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.691114377735843</v>
+        <v>-2.213955309929375</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.97037807468346</v>
+        <v>-1.481622525672726</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.546953234612658</v>
+        <v>-1.06382710349925</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.377607044333999</v>
+        <v>-0.9037278352631333</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.081799731055675</v>
+        <v>-0.6357960808070615</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.9294656127300485</v>
+        <v>-0.4473489195327431</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.7661003218117344</v>
+        <v>-0.2561408560029506</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.3957611967320673</v>
+        <v>0.159602755247569</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.6043609326639867</v>
+        <v>-0.08983806404658878</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.03705824589518159</v>
+        <v>0.5050798686375302</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.8509765256191386</v>
+        <v>1.374563929844435</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.7390919397693949</v>
+        <v>1.268981088043397</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.79400656343892</v>
+        <v>1.401308743990889</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.01689099784759</v>
+        <v>1.66224189819291</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.142000512420751</v>
+        <v>1.80450650587116</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.215533457106368</v>
+        <v>1.97912565461327</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.002639</t>
+          <t>X &lt; 0.00263</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1564</v>
+        <v>1587</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.220464947826869</v>
+        <v>-1.00025384675466</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.095445454165457</v>
+        <v>-1.560033877687665</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.033540919996447</v>
+        <v>-1.433685920571079</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.819002851346774</v>
+        <v>-1.2727924508294</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.567112867873035</v>
+        <v>-1.987773064249517</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.026219988750135</v>
+        <v>-1.39141698493065</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.315912150084252</v>
+        <v>-1.621527245750947</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.338369119134001</v>
+        <v>-1.549799854884604</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.041127461515977</v>
+        <v>-1.359096306154676</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.727086615813334</v>
+        <v>-1.025204298549149</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.77272006828057</v>
+        <v>-1.06684247917395</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.731776377099408</v>
+        <v>-1.029551238416111</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.512227446513066</v>
+        <v>-0.8261759359045513</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.285735990478841</v>
+        <v>-0.5722128849710586</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.8569227663202668</v>
+        <v>-0.1244237640312562</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.006781368673955512</v>
+        <v>0.750753450017541</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.2429332079035618</v>
+        <v>0.897971594475834</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.9692945501181853</v>
+        <v>1.706707075001617</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.50487902567167</v>
+        <v>2.273527451967418</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.308093122084706</v>
+        <v>2.0866723713591</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.149178667673667</v>
+        <v>1.997784531071225</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.393025800893724</v>
+        <v>2.275915682998097</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.539623275524107</v>
+        <v>2.432482751067802</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.527729641226671</v>
+        <v>2.498226475149735</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.004918</t>
+          <t>X &lt; 0.004907</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1830</v>
+        <v>1846</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.163982660519615</v>
+        <v>-1.004829751868698</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.123772059929934</v>
+        <v>-1.628706349991575</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.389119800049833</v>
+        <v>-1.749491164626136</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.364328714170455</v>
+        <v>-1.747940879633063</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.107231969987737</v>
+        <v>-2.401468782151404</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.399875415177021</v>
+        <v>-1.650582692352025</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.65086530832378</v>
+        <v>-1.85171222078344</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.462193417206763</v>
+        <v>-1.670671541081916</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.9835477653467</v>
+        <v>-1.218768549324366</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.936791310235648</v>
+        <v>-1.096893478668974</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.990600520532738</v>
+        <v>-1.148632546138074</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.050770689008061</v>
+        <v>-1.155236098881517</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.081036581000795</v>
+        <v>-1.244210289766407</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.974246604988359</v>
+        <v>-1.060478908434938</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.812717771421376</v>
+        <v>-0.8247067244452637</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.436910084451064</v>
+        <v>-0.4793854270078981</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.297603177712695</v>
+        <v>-0.4212787976961891</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.6920613678726752</v>
+        <v>0.255772302325795</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.4761699869483493</v>
+        <v>0.5564059177702347</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.7264826469256747</v>
+        <v>0.3167163688449506</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.8865151536895155</v>
+        <v>0.2139203991760255</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.6891370713827669</v>
+        <v>0.4415716129712024</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.9064656375892497</v>
+        <v>0.2303618088086452</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.7637186558398383</v>
+        <v>0.4254534500084404</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.007196</t>
+          <t>X &lt; 0.007183</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2095</v>
+        <v>2107</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.382169034497117</v>
+        <v>-1.130138554033024</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.120248079241343</v>
+        <v>-1.707171217551462</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.486465426305401</v>
+        <v>-1.873880456623745</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.031358885017418</v>
+        <v>-1.472905171988252</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.531944384675114</v>
+        <v>-1.795767001775381</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.128614784341259</v>
+        <v>-1.402314947338326</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.207121977300574</v>
+        <v>-1.440537924566314</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.220619563287762</v>
+        <v>-1.508939919535948</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.81870041868472</v>
+        <v>-1.144492561412868</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.971091035055345</v>
+        <v>-1.23098871131527</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.744764089790799</v>
+        <v>-1.00605738639873</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.784850008751917</v>
+        <v>-0.9515135130554526</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.81016004696842</v>
+        <v>-1.025724457374729</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.840308135825509</v>
+        <v>-0.990136380681065</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.44833210166383</v>
+        <v>-0.5370022100590219</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.188074058002464</v>
+        <v>-0.2595203293661399</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.321991194979937</v>
+        <v>-0.5053118101545309</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.044970323622117</v>
+        <v>-0.1371976798579269</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.067742427184662</v>
+        <v>-0.1314900598340145</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.167292798600883</v>
+        <v>-0.1732269140874294</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.232511997593171</v>
+        <v>-0.1441571065334699</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.165159868310148</v>
+        <v>-0.04898216705625202</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.511210215493961</v>
+        <v>-0.3938618925831108</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.348378984230372</v>
+        <v>-0.1958568292495286</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.009474</t>
+          <t>X &lt; 0.009459</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2337</v>
+        <v>2352</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.555740730453245</v>
+        <v>-1.318992674743377</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.379199901564668</v>
+        <v>-2.008872546865319</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.602740064731002</v>
+        <v>-2.077125970790789</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.313218198832416</v>
+        <v>-1.779697661124438</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.711321809154022</v>
+        <v>-2.055255801223772</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.458790136641447</v>
+        <v>-1.813576432513834</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.31187507004968</v>
+        <v>-1.634082173560103</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.524044903671495</v>
+        <v>-1.896629735612791</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.331062616508426</v>
+        <v>-1.726327944572745</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.482469094938367</v>
+        <v>-1.844413338097169</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.22739469175314</v>
+        <v>-1.614551204848773</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.012105807233823</v>
+        <v>-1.340285701692956</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.913689775782188</v>
+        <v>-1.268737141177624</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.682363358287041</v>
+        <v>-1.050869507695474</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.484708624203073</v>
+        <v>-0.8008204997500172</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.403800521258802</v>
+        <v>-0.7056181758456148</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.494927756653041</v>
+        <v>-0.8695642574537246</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.300239149391643</v>
+        <v>-0.5960679474007904</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.298297276383451</v>
+        <v>-0.5688558689647749</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.582140383830911</v>
+        <v>-0.796347458989672</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.482838028048555</v>
+        <v>-0.617285772978768</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.644263792624102</v>
+        <v>-0.7099637675361379</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.797688095974316</v>
+        <v>-0.8663500803784174</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.745150644447911</v>
+        <v>-0.7910949244876235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.01175</t>
+          <t>X &lt; 0.01174</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2577</v>
+        <v>2596</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.463583144260483</v>
+        <v>-1.262059460958433</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.508391837764812</v>
+        <v>-1.104484484059867</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.653519551634211</v>
+        <v>-1.111505379553385</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.38122660988514</v>
+        <v>-0.8773796726493401</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.695888031729844</v>
+        <v>-1.037818856493885</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.680826672110818</v>
+        <v>-1.034377192168854</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.388814523790046</v>
+        <v>-0.7166426272718809</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.68415944789907</v>
+        <v>-1.059936056098771</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.698473803693119</v>
+        <v>-1.085499088087715</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.947187770367762</v>
+        <v>-1.305955802033075</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.728791639958594</v>
+        <v>-1.110466758265275</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.444052591933165</v>
+        <v>-0.773080946044324</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.49999915470147</v>
+        <v>-0.8902754426201867</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.388899540612464</v>
+        <v>-0.7547796498706418</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.365904891252505</v>
+        <v>-0.6852507024241561</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.058844256518675</v>
+        <v>-0.3701499262166266</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.286436906209147</v>
+        <v>-0.682005538481242</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.174707719727586</v>
+        <v>-0.5234090218923271</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.207736110983795</v>
+        <v>-0.5554965608301359</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.408938418982395</v>
+        <v>-0.741495689367099</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.252997974608498</v>
+        <v>-0.5170675770206614</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.367648747814265</v>
+        <v>-0.5695708242682258</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.520026965095497</v>
+        <v>-0.6883192981868689</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.479444782928788</v>
+        <v>-0.6353084188221914</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.01403</t>
+          <t>X &lt; 0.01401</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2752</v>
+        <v>2774</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.223819696404547</v>
+        <v>-1.050694135783601</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.2509757703166</v>
+        <v>-0.8832250989651129</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.370321661173783</v>
+        <v>-0.8631056707293681</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.124791274224457</v>
+        <v>-0.6463979908602866</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.549092655114926</v>
+        <v>-0.9740246293891914</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.378420905303173</v>
+        <v>-0.8170910233911073</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.082077108947161</v>
+        <v>-0.4990671110277773</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.37621430674124</v>
+        <v>-0.8398941971652931</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.242126051350198</v>
+        <v>-0.7119652874811848</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.560448181182522</v>
+        <v>-1.005323784495857</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.483167481197178</v>
+        <v>-0.9485286262649595</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.270681903563641</v>
+        <v>-0.6865109398026732</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.358774761091077</v>
+        <v>-0.8319237035730183</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.268934432406631</v>
+        <v>-0.7001973861291404</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.39838410918891</v>
+        <v>-0.786523649015848</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.072888844923668</v>
+        <v>-0.4557065161446303</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.185617009432065</v>
+        <v>-0.6464064185544771</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.015169874016493</v>
+        <v>-0.4345177982071675</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.068453044676595</v>
+        <v>-0.4867655567971596</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.114653326105262</v>
+        <v>-0.503083993072039</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.9456475084995404</v>
+        <v>-0.293317354815315</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.9851562606063098</v>
+        <v>-0.2751468270901753</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.074053641147508</v>
+        <v>-0.334508421464939</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.077211475766134</v>
+        <v>-0.2951755762147883</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01631</t>
+          <t>X &lt; 0.01629</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2884</v>
+        <v>2907</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9386095919173414</v>
+        <v>-0.8066486159354866</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.8420150963547783</v>
+        <v>-0.5213423219396773</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.8149519515120502</v>
+        <v>-0.3546581927423276</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7509939478640604</v>
+        <v>-0.3121105218234064</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.102166839221262</v>
+        <v>-0.5687222511889516</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.034041956360582</v>
+        <v>-0.4956041759365277</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.9590636380741984</v>
+        <v>-0.399970189539566</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.286934052353658</v>
+        <v>-0.7734072482274001</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.157066253475556</v>
+        <v>-0.6454783385432918</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.461706022067311</v>
+        <v>-0.9276552191685852</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.271723995149799</v>
+        <v>-0.7581951274830629</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.9435241151658147</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.044522968909043</v>
+        <v>-0.5196171263078995</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9342946742807001</v>
+        <v>-0.3708261615597337</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.087951065628197</v>
+        <v>-0.4842154452290828</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.8537800146796712</v>
+        <v>-0.2456943452789915</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.036635913528031</v>
+        <v>-0.5009937657286727</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.9134409600801092</v>
+        <v>-0.3391255229439594</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.988926436152525</v>
+        <v>-0.4134997168436669</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.093659407545054</v>
+        <v>-0.4879481376402381</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.8881251393890608</v>
+        <v>-0.2449697968805324</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.8741790971060084</v>
+        <v>-0.1966737786258577</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.9811190864270074</v>
+        <v>-0.2765384845403887</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.056951339650283</v>
+        <v>-0.3152028132571658</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.01859</t>
+          <t>X &lt; 0.01856</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2969</v>
+        <v>2993</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6328257230576426</v>
+        <v>-0.4922288501265086</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7158445737677326</v>
+        <v>-0.4883677263351913</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.8985927935886977</v>
+        <v>-0.5309516205832807</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.9241881478701046</v>
+        <v>-0.5742292671030569</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.174569514382441</v>
+        <v>-0.7319051360877182</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.002572254318395</v>
+        <v>-0.556645630764308</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.019238671292342</v>
+        <v>-0.5360473743033864</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.245179385298577</v>
+        <v>-0.7891189346822429</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.117874374292036</v>
+        <v>-0.6425513488280714</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.268541904220875</v>
+        <v>-0.7548370387279064</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.143111213103467</v>
+        <v>-0.6300512781485068</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8661276950371359</v>
+        <v>-0.2887896076124576</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.9633852075456986</v>
+        <v>-0.4192483240072917</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7956686907361359</v>
+        <v>-0.2151938838842611</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.8968575652464068</v>
+        <v>-0.2782028098483806</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.7192770839059079</v>
+        <v>-0.09700748675327731</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.8670549668894907</v>
+        <v>-0.3145833333333385</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.7168581718401583</v>
+        <v>-0.1611053177880351</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.817378493458321</v>
+        <v>-0.2604902013424848</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.9807933007334384</v>
+        <v>-0.3933270078650821</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.8980619033162753</v>
+        <v>-0.2737137349606371</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.9204072918932411</v>
+        <v>-0.2623613488916376</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.9627663496276639</v>
+        <v>-0.2995556330051343</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.9851506848021501</v>
+        <v>-0.3083642445109973</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.02086</t>
+          <t>X &lt; 0.02084</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3051</v>
+        <v>3073</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7130657211092668</v>
+        <v>-0.5710505007204176</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.7052041265556142</v>
+        <v>-0.4444301712458127</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7586950441461084</v>
+        <v>-0.3567376850984232</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7700355995977475</v>
+        <v>-0.414162033929081</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.9575014593174416</v>
+        <v>-0.5101530757649613</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9153691324597233</v>
+        <v>-0.4323521016242537</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.9195994160455641</v>
+        <v>-0.4004690969323761</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.016484558048532</v>
+        <v>-0.5900936946582789</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.8587843634667465</v>
+        <v>-0.3791776855053968</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.9933883560285324</v>
+        <v>-0.4767040267697311</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.8965272708073897</v>
+        <v>-0.3804101413251502</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.6669885831758862</v>
+        <v>-0.05508942666067185</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6936794837787161</v>
+        <v>-0.1461580561240865</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5689592154249681</v>
+        <v>0.01381270256636924</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.6523191857576052</v>
+        <v>-0.0003002564565406374</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.4634857895727436</v>
+        <v>0.190855014126825</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.5781072394409534</v>
+        <v>0.008793290043286106</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.5000805874010865</v>
+        <v>0.1224578619272734</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.5265948431838652</v>
+        <v>0.09629953199066676</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.6150465885067078</v>
+        <v>0.03760983299483911</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.5489841543014577</v>
+        <v>0.139494339611268</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.5726521662728672</v>
+        <v>0.1487303079347768</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.6063847088423557</v>
+        <v>0.1189782467256961</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.5973125863436763</v>
+        <v>0.138855643438859</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.02314</t>
+          <t>X &lt; 0.02312</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3102</v>
+        <v>3126</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.7128471134319696</v>
+        <v>-0.573430157770801</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6465586108854993</v>
+        <v>-0.4213162830012536</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6906202262626664</v>
+        <v>-0.3244478754295983</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7454310609729973</v>
+        <v>-0.3908746197590318</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9353127972436681</v>
+        <v>-0.4898843480158277</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.9228571641413055</v>
+        <v>-0.4743561797860067</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.9396431150715543</v>
+        <v>-0.4564315428876924</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9432850515387017</v>
+        <v>-0.4888844799729668</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.7232985766038453</v>
+        <v>-0.279336540561296</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.9003988496760087</v>
+        <v>-0.4204686117666085</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.8006067481112709</v>
+        <v>-0.3211861582237532</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5793618215980558</v>
+        <v>-0.03787998067880949</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5918646087146442</v>
+        <v>-0.05060797750510915</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6655806968871687</v>
+        <v>-0.08883215037967318</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.5976743770144424</v>
+        <v>0.01332001332001909</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.4986358764493772</v>
+        <v>0.1150150107464896</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.6135851584595855</v>
+        <v>-0.06574835088839137</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.5707456727864866</v>
+        <v>0.01179182076431573</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.5933036934914782</v>
+        <v>-0.01032875015464896</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.7738438269438959</v>
+        <v>-0.1602718014339501</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.6856228857979687</v>
+        <v>-0.03782875185116552</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.6779757283598471</v>
+        <v>0.001889811396814878</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.7066766091679568</v>
+        <v>-0.023275538438007</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.7635072639298102</v>
+        <v>-0.07050918539351869</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.02542</t>
+          <t>X &lt; 0.02539</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3154</v>
+        <v>3179</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.6348666286979423</v>
+        <v>-0.5132700760181592</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.5751201334442513</v>
+        <v>-0.367727565688881</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5475012285293062</v>
+        <v>-0.1994776657060484</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5185314478043495</v>
+        <v>-0.180800230253567</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.7422487827744249</v>
+        <v>-0.3139397244385052</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6322939022665679</v>
+        <v>-0.2021743235451439</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.6298360496181488</v>
+        <v>-0.1663576874439912</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.7640671997652362</v>
+        <v>-0.3284352580127319</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.6416202468831642</v>
+        <v>-0.182808846263427</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.7337775662383024</v>
+        <v>-0.2408260417338397</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.8521008630333569</v>
+        <v>-0.357913848746648</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.7338411542311079</v>
+        <v>-0.1779328979918589</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.7330449719572059</v>
+        <v>-0.2090166162320841</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.7776220099886118</v>
+        <v>-0.2194229567869002</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.7849185422880822</v>
+        <v>-0.1930859868520827</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.6461675579322588</v>
+        <v>-0.05243495800620224</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.7614755429287925</v>
+        <v>-0.2319719083490241</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.6578218991032116</v>
+        <v>-0.09519114336148959</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.6131712168457497</v>
+        <v>-0.05059315104765716</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.7243369989572983</v>
+        <v>-0.1316452821557093</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.6781655930808625</v>
+        <v>-0.05211091066274065</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.7669487857337884</v>
+        <v>-0.108620885507996</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.8223767163695612</v>
+        <v>-0.1607875307629172</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.7844400227570389</v>
+        <v>-0.115610827105364</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.0277</t>
+          <t>X &lt; 0.02767</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3209</v>
+        <v>3234</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.5777283015507706</v>
+        <v>-0.4569650762837654</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.524679931589894</v>
+        <v>-0.3180175932984923</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6148813509056552</v>
+        <v>-0.2659619206983734</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5676003868829582</v>
+        <v>-0.2269021447847024</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.793242471390144</v>
+        <v>-0.3624637500793284</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.6819908359647755</v>
+        <v>-0.2499493555650929</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.6617530876075364</v>
+        <v>-0.1974446852253564</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.7364341085271278</v>
+        <v>-0.3004107004107084</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.6463770918460341</v>
+        <v>-0.1858539525752079</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.8122069108792545</v>
+        <v>-0.3179459422551432</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.8928198934911933</v>
+        <v>-0.3976652136078371</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.7503056737309208</v>
+        <v>-0.1946253322160487</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.7066008480476</v>
+        <v>-0.1824505464164545</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.8473820355008428</v>
+        <v>-0.2893593402938635</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.8658241029513363</v>
+        <v>-0.2750596693826566</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.7193084089260608</v>
+        <v>-0.1272976162412718</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.8038628628933466</v>
+        <v>-0.2747190939010622</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.7348933797024699</v>
+        <v>-0.1733933644208605</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.6251085446926439</v>
+        <v>-0.06418767507253165</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.7311766921211742</v>
+        <v>-0.1402223487484875</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.6950881960375455</v>
+        <v>-0.07168347156341071</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.783655061965014</v>
+        <v>-0.1285165189216286</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.7088250676489949</v>
+        <v>-0.05201263355957053</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.6728029082923896</v>
+        <v>-0.01032807229219657</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.02998</t>
+          <t>X &lt; 0.02995</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3250</v>
+        <v>3275</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.5091636426100905</v>
+        <v>-0.3892004091293941</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4609539851314111</v>
+        <v>-0.2550182468596631</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.5680299984159589</v>
+        <v>-0.21919853949246</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.4996856652708104</v>
+        <v>-0.1576328994156384</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.7878692515179893</v>
+        <v>-0.3556324490580494</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.7368655751509365</v>
+        <v>-0.3032978240634421</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.5735407494938229</v>
+        <v>-0.1094822188676901</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.620131303493352</v>
+        <v>-0.1845515974959966</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.5306485779058008</v>
+        <v>-0.06979299016546037</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.7040687130000336</v>
+        <v>-0.2101264753652075</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.8108386935238343</v>
+        <v>-0.3158378558446913</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.6735941939817067</v>
+        <v>-0.1187555856219404</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.7058675440464199</v>
+        <v>-0.1814845957099465</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.7863086922189169</v>
+        <v>-0.2292741719371421</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.812779810633522</v>
+        <v>-0.223651276603384</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.7833863496846973</v>
+        <v>-0.1925487942857558</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.8685818684183744</v>
+        <v>-0.3394462218159617</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.8325334345742448</v>
+        <v>-0.2715454634873211</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.7214420778047881</v>
+        <v>-0.1610539918369653</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.7931177425289064</v>
+        <v>-0.2029872322859063</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.733600399927127</v>
+        <v>-0.1119157386898308</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.8527690355712636</v>
+        <v>-0.1995061069896451</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.8062022465855492</v>
+        <v>-0.1514572384137551</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.7408519051042433</v>
+        <v>-0.0818203749731623</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.03226</t>
+          <t>X &lt; 0.03222</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3275</v>
+        <v>3300</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.4570993875374825</v>
+        <v>-0.3376914286823762</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.351116784089939</v>
+        <v>-0.1461494578542073</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.4682546112982067</v>
+        <v>-0.1200117668803955</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.4058079059004314</v>
+        <v>-0.06334070788776103</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.6639660806109191</v>
+        <v>-0.2317664921098412</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.6118925694688429</v>
+        <v>-0.1786064179042484</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.5163857464645289</v>
+        <v>-0.05250192185215496</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.503946633878158</v>
+        <v>-0.06897338019172139</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4147933015800263</v>
+        <v>0.0459194159098999</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5015218992000143</v>
+        <v>-0.008800683002718301</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.6053346755325464</v>
+        <v>-0.1115992999236468</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.5624602227067967</v>
+        <v>-0.008610437630075296</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5421349981971062</v>
+        <v>-0.01884592084887515</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.5931552059315521</v>
+        <v>-0.03788881231936614</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.593925548156399</v>
+        <v>-0.007183730999159366</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.590622952030202</v>
+        <v>-0.002238592708692977</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.7370693169120983</v>
+        <v>-0.2092310502973547</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.7630113481365868</v>
+        <v>-0.2033053090333539</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.5901244051810579</v>
+        <v>-0.03149235204507761</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.6902860855989985</v>
+        <v>-0.1017117444984095</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.6048226649335504</v>
+        <v>0.01468169145714882</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.723621497528903</v>
+        <v>-0.0727762438963353</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.705801092662405</v>
+        <v>-0.0535015739630893</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.6720321752158114</v>
+        <v>-0.01589393500092484</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.03453</t>
+          <t>X &lt; 0.0345</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3307</v>
+        <v>3331</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.3375438101286576</v>
+        <v>-0.23314551165263</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2057230406493105</v>
+        <v>0.01403130346856329</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2453737300435463</v>
+        <v>0.08803725076173663</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2504322673009014</v>
+        <v>0.1089240000037819</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4792244942940727</v>
+        <v>-0.06044173595689273</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.5160227704648079</v>
+        <v>-0.06598924483827062</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4589222971661471</v>
+        <v>0.02175080540026642</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.509451392339507</v>
+        <v>-0.05712509447197789</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3605541773113075</v>
+        <v>0.08777845112359728</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.4538783025991933</v>
+        <v>0.02620053031253633</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3733116930918285</v>
+        <v>0.1063149049557808</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3334682557581985</v>
+        <v>0.2357624028716074</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2638249484747774</v>
+        <v>0.2751977805682131</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3766973019279618</v>
+        <v>0.1942539963807448</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.3535893198667424</v>
+        <v>0.2184122212486557</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3746743452625765</v>
+        <v>0.1986411933961634</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.4605845351596614</v>
+        <v>0.05258263431196042</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.5173893109483885</v>
+        <v>0.05729732027042189</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.3440127049336184</v>
+        <v>0.1996086975237361</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.4715285528560571</v>
+        <v>0.1021209638447544</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4222819144575212</v>
+        <v>0.1822231150525369</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.5103895918312276</v>
+        <v>0.1249328062333888</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4597922311759106</v>
+        <v>0.2063782034553086</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.4572483601762301</v>
+        <v>0.212183901302673</v>
       </c>
     </row>
   </sheetData>
